--- a/uploadfile.xlsx
+++ b/uploadfile.xlsx
@@ -20,1507 +20,1507 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>814390233017</t>
-  </si>
-  <si>
-    <t>056</t>
-  </si>
-  <si>
-    <t>977381672754</t>
-  </si>
-  <si>
-    <t>443505668747</t>
-  </si>
-  <si>
-    <t>049367969109</t>
-  </si>
-  <si>
-    <t>896352091660</t>
-  </si>
-  <si>
-    <t>759129960643</t>
-  </si>
-  <si>
-    <t>976471822211</t>
-  </si>
-  <si>
-    <t>936274200742</t>
-  </si>
-  <si>
-    <t>430446636042</t>
-  </si>
-  <si>
-    <t>766396601454</t>
-  </si>
-  <si>
-    <t>327913405793</t>
-  </si>
-  <si>
-    <t>947354753133</t>
-  </si>
-  <si>
-    <t>409117100403</t>
-  </si>
-  <si>
-    <t>629877442693</t>
-  </si>
-  <si>
-    <t>458215326682</t>
-  </si>
-  <si>
-    <t>652674550334</t>
-  </si>
-  <si>
-    <t>285276511617</t>
-  </si>
-  <si>
-    <t>304899706058</t>
-  </si>
-  <si>
-    <t>575168917729</t>
-  </si>
-  <si>
-    <t>105628323719</t>
-  </si>
-  <si>
-    <t>380617171281</t>
-  </si>
-  <si>
-    <t>465916018456</t>
-  </si>
-  <si>
-    <t>175777464058</t>
-  </si>
-  <si>
-    <t>625395723013</t>
-  </si>
-  <si>
-    <t>403759963555</t>
-  </si>
-  <si>
-    <t>709058253863</t>
-  </si>
-  <si>
-    <t>287908785655</t>
-  </si>
-  <si>
-    <t>021399195619</t>
-  </si>
-  <si>
-    <t>977664170117</t>
-  </si>
-  <si>
-    <t>226599975974</t>
-  </si>
-  <si>
-    <t>321111125233</t>
-  </si>
-  <si>
-    <t>411735660838</t>
-  </si>
-  <si>
-    <t>206509583825</t>
-  </si>
-  <si>
-    <t>930499574044</t>
-  </si>
-  <si>
-    <t>966880660164</t>
-  </si>
-  <si>
-    <t>758722487707</t>
-  </si>
-  <si>
-    <t>699057735584</t>
-  </si>
-  <si>
-    <t>977341113661</t>
-  </si>
-  <si>
-    <t>411294725749</t>
-  </si>
-  <si>
-    <t>401756327848</t>
-  </si>
-  <si>
-    <t>285332411626</t>
-  </si>
-  <si>
-    <t>245308834759</t>
-  </si>
-  <si>
-    <t>771978101276</t>
-  </si>
-  <si>
-    <t>999431329246</t>
-  </si>
-  <si>
-    <t>961416660756</t>
-  </si>
-  <si>
-    <t>387275906008</t>
-  </si>
-  <si>
-    <t>837760918299</t>
-  </si>
-  <si>
-    <t>607036214810</t>
-  </si>
-  <si>
-    <t>498769970512</t>
-  </si>
-  <si>
-    <t>981760253484</t>
-  </si>
-  <si>
-    <t>313052019840</t>
-  </si>
-  <si>
-    <t>167758525287</t>
-  </si>
-  <si>
-    <t>941435522049</t>
-  </si>
-  <si>
-    <t>725582313377</t>
-  </si>
-  <si>
-    <t>990044362492</t>
-  </si>
-  <si>
-    <t>144545783295</t>
-  </si>
-  <si>
-    <t>707547336993</t>
-  </si>
-  <si>
-    <t>379662989308</t>
-  </si>
-  <si>
-    <t>884563833282</t>
-  </si>
-  <si>
-    <t>410369081371</t>
-  </si>
-  <si>
-    <t>748163518255</t>
-  </si>
-  <si>
-    <t>241133516184</t>
-  </si>
-  <si>
-    <t>629804223921</t>
-  </si>
-  <si>
-    <t>605644213910</t>
-  </si>
-  <si>
-    <t>059837639337</t>
-  </si>
-  <si>
-    <t>299380702813</t>
-  </si>
-  <si>
-    <t>245491325859</t>
-  </si>
-  <si>
-    <t>461891762292</t>
-  </si>
-  <si>
-    <t>937654703827</t>
-  </si>
-  <si>
-    <t>635728023009</t>
-  </si>
-  <si>
-    <t>760295497684</t>
-  </si>
-  <si>
-    <t>542410678216</t>
-  </si>
-  <si>
-    <t>364304333106</t>
-  </si>
-  <si>
-    <t>818121834081</t>
-  </si>
-  <si>
-    <t>368779180640</t>
-  </si>
-  <si>
-    <t>811267697456</t>
-  </si>
-  <si>
-    <t>644102037908</t>
-  </si>
-  <si>
-    <t>496531611951</t>
-  </si>
-  <si>
-    <t>668945603753</t>
-  </si>
-  <si>
-    <t>772118287242</t>
-  </si>
-  <si>
-    <t>601653478342</t>
-  </si>
-  <si>
-    <t>320803025272</t>
-  </si>
-  <si>
-    <t>506669034086</t>
-  </si>
-  <si>
-    <t>498811132468</t>
-  </si>
-  <si>
-    <t>484203126163</t>
-  </si>
-  <si>
-    <t>089838464064</t>
-  </si>
-  <si>
-    <t>022850207013</t>
-  </si>
-  <si>
-    <t>507235394532</t>
-  </si>
-  <si>
-    <t>506153851876</t>
-  </si>
-  <si>
-    <t>992352422168</t>
-  </si>
-  <si>
-    <t>990516529725</t>
-  </si>
-  <si>
-    <t>162023646328</t>
-  </si>
-  <si>
-    <t>827254909983</t>
-  </si>
-  <si>
-    <t>877948748543</t>
-  </si>
-  <si>
-    <t>249879893745</t>
-  </si>
-  <si>
-    <t>995258044309</t>
-  </si>
-  <si>
-    <t>231708341148</t>
-  </si>
-  <si>
-    <t>556436253667</t>
-  </si>
-  <si>
-    <t>415277535300</t>
-  </si>
-  <si>
-    <t>183760929053</t>
-  </si>
-  <si>
-    <t>432129608994</t>
-  </si>
-  <si>
-    <t>115435175817</t>
-  </si>
-  <si>
-    <t>484598875890</t>
-  </si>
-  <si>
-    <t>724486194663</t>
-  </si>
-  <si>
-    <t>853824825052</t>
-  </si>
-  <si>
-    <t>711389724359</t>
-  </si>
-  <si>
-    <t>041709546835</t>
-  </si>
-  <si>
-    <t>737484363248</t>
-  </si>
-  <si>
-    <t>042188164628</t>
-  </si>
-  <si>
-    <t>969433452506</t>
-  </si>
-  <si>
-    <t>965283662430</t>
-  </si>
-  <si>
-    <t>988576000645</t>
-  </si>
-  <si>
-    <t>217112075563</t>
-  </si>
-  <si>
-    <t>322501281326</t>
-  </si>
-  <si>
-    <t>846317789931</t>
-  </si>
-  <si>
-    <t>924128515926</t>
-  </si>
-  <si>
-    <t>156365839432</t>
-  </si>
-  <si>
-    <t>843113693893</t>
-  </si>
-  <si>
-    <t>257030443676</t>
-  </si>
-  <si>
-    <t>334429362050</t>
-  </si>
-  <si>
-    <t>574060169542</t>
-  </si>
-  <si>
-    <t>391482441047</t>
-  </si>
-  <si>
-    <t>143911159137</t>
-  </si>
-  <si>
-    <t>768171564310</t>
-  </si>
-  <si>
-    <t>070560753791</t>
-  </si>
-  <si>
-    <t>073075371704</t>
-  </si>
-  <si>
-    <t>083430456446</t>
-  </si>
-  <si>
-    <t>593436157750</t>
-  </si>
-  <si>
-    <t>467397315362</t>
-  </si>
-  <si>
-    <t>167067574803</t>
-  </si>
-  <si>
-    <t>312979942850</t>
-  </si>
-  <si>
-    <t>610582376424</t>
-  </si>
-  <si>
-    <t>208125449531</t>
-  </si>
-  <si>
-    <t>742898856587</t>
-  </si>
-  <si>
-    <t>399000286046</t>
-  </si>
-  <si>
-    <t>462854452310</t>
-  </si>
-  <si>
-    <t>432230344850</t>
-  </si>
-  <si>
-    <t>950944170309</t>
-  </si>
-  <si>
-    <t>693983684477</t>
-  </si>
-  <si>
-    <t>070383124782</t>
-  </si>
-  <si>
-    <t>710915364130</t>
-  </si>
-  <si>
-    <t>068383185804</t>
-  </si>
-  <si>
-    <t>974048733544</t>
-  </si>
-  <si>
-    <t>194948941641</t>
-  </si>
-  <si>
-    <t>214852606584</t>
-  </si>
-  <si>
-    <t>864979780151</t>
-  </si>
-  <si>
-    <t>952538854821</t>
-  </si>
-  <si>
-    <t>724646574932</t>
-  </si>
-  <si>
-    <t>508500718033</t>
-  </si>
-  <si>
-    <t>841293594688</t>
-  </si>
-  <si>
-    <t>300853105612</t>
-  </si>
-  <si>
-    <t>746342729395</t>
-  </si>
-  <si>
-    <t>017200600826</t>
-  </si>
-  <si>
-    <t>388628801633</t>
-  </si>
-  <si>
-    <t>103599490176</t>
-  </si>
-  <si>
-    <t>255788428763</t>
-  </si>
-  <si>
-    <t>251169181203</t>
-  </si>
-  <si>
-    <t>149254224239</t>
-  </si>
-  <si>
-    <t>406432852631</t>
-  </si>
-  <si>
-    <t>106262518614</t>
-  </si>
-  <si>
-    <t>338429515855</t>
-  </si>
-  <si>
-    <t>155704707684</t>
-  </si>
-  <si>
-    <t>407532340135</t>
-  </si>
-  <si>
-    <t>588347029636</t>
-  </si>
-  <si>
-    <t>192807899804</t>
-  </si>
-  <si>
-    <t>585784153068</t>
-  </si>
-  <si>
-    <t>485600048145</t>
-  </si>
-  <si>
-    <t>713817640179</t>
-  </si>
-  <si>
-    <t>412361401776</t>
-  </si>
-  <si>
-    <t>275463051963</t>
-  </si>
-  <si>
-    <t>572055804354</t>
-  </si>
-  <si>
-    <t>267017413864</t>
-  </si>
-  <si>
-    <t>833332905094</t>
-  </si>
-  <si>
-    <t>502259720986</t>
-  </si>
-  <si>
-    <t>208259519629</t>
-  </si>
-  <si>
-    <t>669646812738</t>
-  </si>
-  <si>
-    <t>367573376443</t>
-  </si>
-  <si>
-    <t>388928590181</t>
-  </si>
-  <si>
-    <t>236352262543</t>
-  </si>
-  <si>
-    <t>553220548284</t>
-  </si>
-  <si>
-    <t>567977692945</t>
-  </si>
-  <si>
-    <t>403481729287</t>
-  </si>
-  <si>
-    <t>916097058377</t>
-  </si>
-  <si>
-    <t>796189291057</t>
-  </si>
-  <si>
-    <t>045762437672</t>
-  </si>
-  <si>
-    <t>176504717240</t>
-  </si>
-  <si>
-    <t>478136878992</t>
-  </si>
-  <si>
-    <t>796757716067</t>
-  </si>
-  <si>
-    <t>706325960368</t>
-  </si>
-  <si>
-    <t>741718258392</t>
-  </si>
-  <si>
-    <t>919812755696</t>
-  </si>
-  <si>
-    <t>861471831249</t>
-  </si>
-  <si>
-    <t>887874545789</t>
-  </si>
-  <si>
-    <t>420580906411</t>
-  </si>
-  <si>
-    <t>515998855119</t>
-  </si>
-  <si>
-    <t>760083426096</t>
-  </si>
-  <si>
-    <t>788841421989</t>
-  </si>
-  <si>
-    <t>079376422415</t>
-  </si>
-  <si>
-    <t>331180615599</t>
-  </si>
-  <si>
-    <t>496890942636</t>
-  </si>
-  <si>
-    <t>060322999992</t>
-  </si>
-  <si>
-    <t>039538289279</t>
-  </si>
-  <si>
-    <t>239448447224</t>
-  </si>
-  <si>
-    <t>113656670685</t>
-  </si>
-  <si>
-    <t>841952089293</t>
-  </si>
-  <si>
-    <t>325944476719</t>
-  </si>
-  <si>
-    <t>631529387157</t>
-  </si>
-  <si>
-    <t>964219109444</t>
-  </si>
-  <si>
-    <t>085570447891</t>
-  </si>
-  <si>
-    <t>810967903025</t>
-  </si>
-  <si>
-    <t>086731926178</t>
-  </si>
-  <si>
-    <t>590458066308</t>
-  </si>
-  <si>
-    <t>953185398019</t>
-  </si>
-  <si>
-    <t>131143844213</t>
-  </si>
-  <si>
-    <t>709439813846</t>
-  </si>
-  <si>
-    <t>216378868381</t>
-  </si>
-  <si>
-    <t>120659519952</t>
-  </si>
-  <si>
-    <t>067912233219</t>
-  </si>
-  <si>
-    <t>221318098868</t>
-  </si>
-  <si>
-    <t>613854260483</t>
-  </si>
-  <si>
-    <t>679949877092</t>
-  </si>
-  <si>
-    <t>894708719668</t>
-  </si>
-  <si>
-    <t>085293112369</t>
-  </si>
-  <si>
-    <t>931429465504</t>
-  </si>
-  <si>
-    <t>137633430737</t>
-  </si>
-  <si>
-    <t>971560818884</t>
-  </si>
-  <si>
-    <t>244970410335</t>
-  </si>
-  <si>
-    <t>307878207336</t>
-  </si>
-  <si>
-    <t>541341874733</t>
-  </si>
-  <si>
-    <t>934051475494</t>
-  </si>
-  <si>
-    <t>550601049436</t>
-  </si>
-  <si>
-    <t>218521619062</t>
-  </si>
-  <si>
-    <t>298292089694</t>
-  </si>
-  <si>
-    <t>174628416131</t>
-  </si>
-  <si>
-    <t>714025213218</t>
-  </si>
-  <si>
-    <t>526807055410</t>
-  </si>
-  <si>
-    <t>370498862903</t>
-  </si>
-  <si>
-    <t>972824654566</t>
-  </si>
-  <si>
-    <t>262811645919</t>
-  </si>
-  <si>
-    <t>548059141192</t>
-  </si>
-  <si>
-    <t>173987376134</t>
-  </si>
-  <si>
-    <t>357552633730</t>
-  </si>
-  <si>
-    <t>415772938769</t>
-  </si>
-  <si>
-    <t>207941057819</t>
-  </si>
-  <si>
-    <t>868305268779</t>
-  </si>
-  <si>
-    <t>041178661932</t>
-  </si>
-  <si>
-    <t>813399493216</t>
-  </si>
-  <si>
-    <t>968144685104</t>
-  </si>
-  <si>
-    <t>665384617906</t>
-  </si>
-  <si>
-    <t>914761782254</t>
-  </si>
-  <si>
-    <t>781075513007</t>
-  </si>
-  <si>
-    <t>567310653540</t>
-  </si>
-  <si>
-    <t>133165701266</t>
-  </si>
-  <si>
-    <t>378278145020</t>
-  </si>
-  <si>
-    <t>464101403717</t>
-  </si>
-  <si>
-    <t>658160138953</t>
-  </si>
-  <si>
-    <t>383013293312</t>
-  </si>
-  <si>
-    <t>116822016164</t>
-  </si>
-  <si>
-    <t>301748166738</t>
-  </si>
-  <si>
-    <t>128773846842</t>
-  </si>
-  <si>
-    <t>044809509005</t>
-  </si>
-  <si>
-    <t>309718568086</t>
-  </si>
-  <si>
-    <t>332884409517</t>
-  </si>
-  <si>
-    <t>564448608007</t>
-  </si>
-  <si>
-    <t>369025758656</t>
-  </si>
-  <si>
-    <t>119070601063</t>
-  </si>
-  <si>
-    <t>602808636938</t>
-  </si>
-  <si>
-    <t>342322825302</t>
-  </si>
-  <si>
-    <t>554961426074</t>
-  </si>
-  <si>
-    <t>612821218975</t>
-  </si>
-  <si>
-    <t>654930793039</t>
-  </si>
-  <si>
-    <t>770937585904</t>
-  </si>
-  <si>
-    <t>364952686678</t>
-  </si>
-  <si>
-    <t>569941543680</t>
-  </si>
-  <si>
-    <t>798078737680</t>
-  </si>
-  <si>
-    <t>235416327532</t>
-  </si>
-  <si>
-    <t>346152088743</t>
-  </si>
-  <si>
-    <t>016271932294</t>
-  </si>
-  <si>
-    <t>964375005467</t>
-  </si>
-  <si>
-    <t>728277090503</t>
-  </si>
-  <si>
-    <t>670352696961</t>
-  </si>
-  <si>
-    <t>917126602889</t>
-  </si>
-  <si>
-    <t>709321815985</t>
-  </si>
-  <si>
-    <t>236464255895</t>
-  </si>
-  <si>
-    <t>059879479724</t>
-  </si>
-  <si>
-    <t>586022112784</t>
-  </si>
-  <si>
-    <t>215104722298</t>
-  </si>
-  <si>
-    <t>407940221724</t>
-  </si>
-  <si>
-    <t>546026548223</t>
-  </si>
-  <si>
-    <t>536759797894</t>
-  </si>
-  <si>
-    <t>036129487032</t>
-  </si>
-  <si>
-    <t>613091115109</t>
-  </si>
-  <si>
-    <t>799108090095</t>
-  </si>
-  <si>
-    <t>058499334405</t>
-  </si>
-  <si>
-    <t>351346780943</t>
-  </si>
-  <si>
-    <t>801574465502</t>
-  </si>
-  <si>
-    <t>765339016080</t>
-  </si>
-  <si>
-    <t>856257933357</t>
-  </si>
-  <si>
-    <t>791397267289</t>
-  </si>
-  <si>
-    <t>139073132814</t>
-  </si>
-  <si>
-    <t>013300309455</t>
-  </si>
-  <si>
-    <t>487271468721</t>
-  </si>
-  <si>
-    <t>482817444732</t>
-  </si>
-  <si>
-    <t>741111856950</t>
-  </si>
-  <si>
-    <t>135774179377</t>
-  </si>
-  <si>
-    <t>015193428490</t>
-  </si>
-  <si>
-    <t>108414607319</t>
-  </si>
-  <si>
-    <t>524116581916</t>
-  </si>
-  <si>
-    <t>389560962559</t>
-  </si>
-  <si>
-    <t>421093815942</t>
-  </si>
-  <si>
-    <t>188704973314</t>
-  </si>
-  <si>
-    <t>586029362728</t>
-  </si>
-  <si>
-    <t>900635516016</t>
-  </si>
-  <si>
-    <t>452013151944</t>
-  </si>
-  <si>
-    <t>593544760389</t>
-  </si>
-  <si>
-    <t>632720493866</t>
-  </si>
-  <si>
-    <t>283186947205</t>
-  </si>
-  <si>
-    <t>119292123466</t>
-  </si>
-  <si>
-    <t>181840859726</t>
-  </si>
-  <si>
-    <t>470132258511</t>
-  </si>
-  <si>
-    <t>924137751476</t>
-  </si>
-  <si>
-    <t>259856872495</t>
-  </si>
-  <si>
-    <t>044417193854</t>
-  </si>
-  <si>
-    <t>950935311565</t>
-  </si>
-  <si>
-    <t>828751977592</t>
-  </si>
-  <si>
-    <t>148346340164</t>
-  </si>
-  <si>
-    <t>163990479115</t>
-  </si>
-  <si>
-    <t>043292895038</t>
-  </si>
-  <si>
-    <t>392737359147</t>
-  </si>
-  <si>
-    <t>876967793870</t>
-  </si>
-  <si>
-    <t>825904944899</t>
-  </si>
-  <si>
-    <t>411642929484</t>
-  </si>
-  <si>
-    <t>497533735419</t>
-  </si>
-  <si>
-    <t>115252267026</t>
-  </si>
-  <si>
-    <t>489396998426</t>
-  </si>
-  <si>
-    <t>825232842231</t>
-  </si>
-  <si>
-    <t>497856052524</t>
-  </si>
-  <si>
-    <t>324570246328</t>
-  </si>
-  <si>
-    <t>177975299758</t>
-  </si>
-  <si>
-    <t>525943206124</t>
-  </si>
-  <si>
-    <t>458357550543</t>
-  </si>
-  <si>
-    <t>006905176804</t>
-  </si>
-  <si>
-    <t>874485916926</t>
-  </si>
-  <si>
-    <t>750946008349</t>
-  </si>
-  <si>
-    <t>393799761904</t>
-  </si>
-  <si>
-    <t>838721984221</t>
-  </si>
-  <si>
-    <t>721205897396</t>
-  </si>
-  <si>
-    <t>906550775616</t>
-  </si>
-  <si>
-    <t>978746687636</t>
-  </si>
-  <si>
-    <t>212669652415</t>
-  </si>
-  <si>
-    <t>378909853407</t>
-  </si>
-  <si>
-    <t>312003280106</t>
-  </si>
-  <si>
-    <t>360770279457</t>
-  </si>
-  <si>
-    <t>681885318174</t>
-  </si>
-  <si>
-    <t>352954687848</t>
-  </si>
-  <si>
-    <t>949060087629</t>
-  </si>
-  <si>
-    <t>836726761688</t>
-  </si>
-  <si>
-    <t>878692193313</t>
-  </si>
-  <si>
-    <t>583676662835</t>
-  </si>
-  <si>
-    <t>966835307901</t>
-  </si>
-  <si>
-    <t>287830740261</t>
-  </si>
-  <si>
-    <t>436979680827</t>
-  </si>
-  <si>
-    <t>322636179270</t>
-  </si>
-  <si>
-    <t>647198160177</t>
-  </si>
-  <si>
-    <t>965416396025</t>
-  </si>
-  <si>
-    <t>443934116215</t>
-  </si>
-  <si>
-    <t>311956883009</t>
-  </si>
-  <si>
-    <t>902155810044</t>
-  </si>
-  <si>
-    <t>861923305700</t>
-  </si>
-  <si>
-    <t>514628978079</t>
-  </si>
-  <si>
-    <t>307635354653</t>
-  </si>
-  <si>
-    <t>691076608586</t>
-  </si>
-  <si>
-    <t>952453775147</t>
-  </si>
-  <si>
-    <t>549322014397</t>
-  </si>
-  <si>
-    <t>102868219809</t>
-  </si>
-  <si>
-    <t>794786002217</t>
-  </si>
-  <si>
-    <t>234445432975</t>
-  </si>
-  <si>
-    <t>862230413669</t>
-  </si>
-  <si>
-    <t>280173127732</t>
-  </si>
-  <si>
-    <t>947242280464</t>
-  </si>
-  <si>
-    <t>663003522816</t>
-  </si>
-  <si>
-    <t>819461086145</t>
-  </si>
-  <si>
-    <t>267062769800</t>
-  </si>
-  <si>
-    <t>888764755851</t>
-  </si>
-  <si>
-    <t>233988778474</t>
-  </si>
-  <si>
-    <t>928697675688</t>
-  </si>
-  <si>
-    <t>974178533298</t>
-  </si>
-  <si>
-    <t>382564281316</t>
-  </si>
-  <si>
-    <t>827390553803</t>
-  </si>
-  <si>
-    <t>259967071441</t>
-  </si>
-  <si>
-    <t>044329156753</t>
-  </si>
-  <si>
-    <t>960767796382</t>
-  </si>
-  <si>
-    <t>426859346001</t>
-  </si>
-  <si>
-    <t>469190995450</t>
-  </si>
-  <si>
-    <t>593975399689</t>
-  </si>
-  <si>
-    <t>425235739214</t>
-  </si>
-  <si>
-    <t>546246720525</t>
-  </si>
-  <si>
-    <t>146106727090</t>
-  </si>
-  <si>
-    <t>805023333468</t>
-  </si>
-  <si>
-    <t>555917473664</t>
-  </si>
-  <si>
-    <t>200857587592</t>
-  </si>
-  <si>
-    <t>987266166216</t>
-  </si>
-  <si>
-    <t>700318856998</t>
-  </si>
-  <si>
-    <t>146741452555</t>
-  </si>
-  <si>
-    <t>321106188413</t>
-  </si>
-  <si>
-    <t>638641362046</t>
-  </si>
-  <si>
-    <t>409255078920</t>
-  </si>
-  <si>
-    <t>800094549950</t>
-  </si>
-  <si>
-    <t>865161380225</t>
-  </si>
-  <si>
-    <t>353681972025</t>
-  </si>
-  <si>
-    <t>608929921642</t>
-  </si>
-  <si>
-    <t>001227166568</t>
-  </si>
-  <si>
-    <t>264370311421</t>
-  </si>
-  <si>
-    <t>911907321418</t>
-  </si>
-  <si>
-    <t>581186308898</t>
-  </si>
-  <si>
-    <t>506164693701</t>
-  </si>
-  <si>
-    <t>173381178802</t>
-  </si>
-  <si>
-    <t>230785110558</t>
-  </si>
-  <si>
-    <t>960397697510</t>
-  </si>
-  <si>
-    <t>262443667383</t>
-  </si>
-  <si>
-    <t>415052630222</t>
-  </si>
-  <si>
-    <t>232396383257</t>
-  </si>
-  <si>
-    <t>366327054091</t>
-  </si>
-  <si>
-    <t>166208633370</t>
-  </si>
-  <si>
-    <t>100002762699</t>
-  </si>
-  <si>
-    <t>014759791589</t>
-  </si>
-  <si>
-    <t>833824620153</t>
-  </si>
-  <si>
-    <t>189411891532</t>
-  </si>
-  <si>
-    <t>107277845776</t>
-  </si>
-  <si>
-    <t>410868299220</t>
-  </si>
-  <si>
-    <t>720398875168</t>
-  </si>
-  <si>
-    <t>013607179923</t>
-  </si>
-  <si>
-    <t>668669688487</t>
-  </si>
-  <si>
-    <t>828869195661</t>
-  </si>
-  <si>
-    <t>807332131781</t>
-  </si>
-  <si>
-    <t>916377304638</t>
-  </si>
-  <si>
-    <t>670787840081</t>
-  </si>
-  <si>
-    <t>327703372974</t>
-  </si>
-  <si>
-    <t>949768683413</t>
-  </si>
-  <si>
-    <t>628576215553</t>
-  </si>
-  <si>
-    <t>400026201491</t>
-  </si>
-  <si>
-    <t>705976191310</t>
-  </si>
-  <si>
-    <t>667985089248</t>
-  </si>
-  <si>
-    <t>557011583575</t>
-  </si>
-  <si>
-    <t>982868342396</t>
-  </si>
-  <si>
-    <t>110020054899</t>
-  </si>
-  <si>
-    <t>238946370687</t>
-  </si>
-  <si>
-    <t>339868558008</t>
-  </si>
-  <si>
-    <t>517769960045</t>
-  </si>
-  <si>
-    <t>732838409899</t>
-  </si>
-  <si>
-    <t>370886483319</t>
-  </si>
-  <si>
-    <t>496333578274</t>
-  </si>
-  <si>
-    <t>721405170151</t>
-  </si>
-  <si>
-    <t>643706573820</t>
-  </si>
-  <si>
-    <t>699352495870</t>
-  </si>
-  <si>
-    <t>326639475769</t>
-  </si>
-  <si>
-    <t>969582670392</t>
-  </si>
-  <si>
-    <t>264760688993</t>
-  </si>
-  <si>
-    <t>547720283884</t>
-  </si>
-  <si>
-    <t>381925753446</t>
-  </si>
-  <si>
-    <t>473506813235</t>
-  </si>
-  <si>
-    <t>874821583580</t>
-  </si>
-  <si>
-    <t>088457199489</t>
-  </si>
-  <si>
-    <t>380387310536</t>
-  </si>
-  <si>
-    <t>778432186901</t>
-  </si>
-  <si>
-    <t>757914205032</t>
-  </si>
-  <si>
-    <t>155742202696</t>
-  </si>
-  <si>
-    <t>552706837689</t>
-  </si>
-  <si>
-    <t>033669585209</t>
-  </si>
-  <si>
-    <t>375199845622</t>
-  </si>
-  <si>
-    <t>748081278856</t>
-  </si>
-  <si>
-    <t>572162712367</t>
-  </si>
-  <si>
-    <t>463156944633</t>
-  </si>
-  <si>
-    <t>801402532203</t>
-  </si>
-  <si>
-    <t>329383738550</t>
-  </si>
-  <si>
-    <t>464686310081</t>
-  </si>
-  <si>
-    <t>991717922876</t>
-  </si>
-  <si>
-    <t>489051249893</t>
-  </si>
-  <si>
-    <t>994590025572</t>
-  </si>
-  <si>
-    <t>516300516912</t>
-  </si>
-  <si>
-    <t>220334507574</t>
-  </si>
-  <si>
-    <t>582218710834</t>
-  </si>
-  <si>
-    <t>339365017578</t>
-  </si>
-  <si>
-    <t>322786397899</t>
-  </si>
-  <si>
-    <t>448739729042</t>
-  </si>
-  <si>
-    <t>256348488157</t>
-  </si>
-  <si>
-    <t>236540560612</t>
-  </si>
-  <si>
-    <t>455604676675</t>
-  </si>
-  <si>
-    <t>876720628370</t>
-  </si>
-  <si>
-    <t>448645203965</t>
-  </si>
-  <si>
-    <t>194803710067</t>
-  </si>
-  <si>
-    <t>736362147307</t>
-  </si>
-  <si>
-    <t>341376220335</t>
-  </si>
-  <si>
-    <t>789271773525</t>
-  </si>
-  <si>
-    <t>970126076690</t>
-  </si>
-  <si>
-    <t>804615047253</t>
-  </si>
-  <si>
-    <t>520455257891</t>
-  </si>
-  <si>
-    <t>905650880875</t>
-  </si>
-  <si>
-    <t>512866441176</t>
-  </si>
-  <si>
-    <t>063944009313</t>
+    <t>039115569810</t>
+  </si>
+  <si>
+    <t>661</t>
+  </si>
+  <si>
+    <t>620160127607</t>
+  </si>
+  <si>
+    <t>643076748863</t>
+  </si>
+  <si>
+    <t>014299417087</t>
+  </si>
+  <si>
+    <t>230734334348</t>
+  </si>
+  <si>
+    <t>425065949295</t>
+  </si>
+  <si>
+    <t>442639865214</t>
+  </si>
+  <si>
+    <t>821210172356</t>
+  </si>
+  <si>
+    <t>909729305604</t>
+  </si>
+  <si>
+    <t>823157130944</t>
+  </si>
+  <si>
+    <t>279908509703</t>
+  </si>
+  <si>
+    <t>175204920928</t>
+  </si>
+  <si>
+    <t>073062832282</t>
+  </si>
+  <si>
+    <t>582665528476</t>
+  </si>
+  <si>
+    <t>319534907127</t>
+  </si>
+  <si>
+    <t>245769043332</t>
+  </si>
+  <si>
+    <t>755227506860</t>
+  </si>
+  <si>
+    <t>514484040493</t>
+  </si>
+  <si>
+    <t>748452311075</t>
+  </si>
+  <si>
+    <t>147292177736</t>
+  </si>
+  <si>
+    <t>874322509714</t>
+  </si>
+  <si>
+    <t>588785036738</t>
+  </si>
+  <si>
+    <t>996592913384</t>
+  </si>
+  <si>
+    <t>263120787528</t>
+  </si>
+  <si>
+    <t>250770016397</t>
+  </si>
+  <si>
+    <t>052916581050</t>
+  </si>
+  <si>
+    <t>144515419100</t>
+  </si>
+  <si>
+    <t>250166808376</t>
+  </si>
+  <si>
+    <t>218614342471</t>
+  </si>
+  <si>
+    <t>034924712580</t>
+  </si>
+  <si>
+    <t>414189853806</t>
+  </si>
+  <si>
+    <t>970341896396</t>
+  </si>
+  <si>
+    <t>596253668270</t>
+  </si>
+  <si>
+    <t>604536843493</t>
+  </si>
+  <si>
+    <t>119852639443</t>
+  </si>
+  <si>
+    <t>650246693229</t>
+  </si>
+  <si>
+    <t>981335359595</t>
+  </si>
+  <si>
+    <t>096662635511</t>
+  </si>
+  <si>
+    <t>212253540832</t>
+  </si>
+  <si>
+    <t>625690659095</t>
+  </si>
+  <si>
+    <t>970827899134</t>
+  </si>
+  <si>
+    <t>943832601278</t>
+  </si>
+  <si>
+    <t>577161902558</t>
+  </si>
+  <si>
+    <t>395590989439</t>
+  </si>
+  <si>
+    <t>572164041233</t>
+  </si>
+  <si>
+    <t>263688052570</t>
+  </si>
+  <si>
+    <t>234920315763</t>
+  </si>
+  <si>
+    <t>053716318967</t>
+  </si>
+  <si>
+    <t>663888910277</t>
+  </si>
+  <si>
+    <t>584180605410</t>
+  </si>
+  <si>
+    <t>131065701287</t>
+  </si>
+  <si>
+    <t>861130916884</t>
+  </si>
+  <si>
+    <t>796998723010</t>
+  </si>
+  <si>
+    <t>646226860514</t>
+  </si>
+  <si>
+    <t>665180511214</t>
+  </si>
+  <si>
+    <t>098143877441</t>
+  </si>
+  <si>
+    <t>426019596079</t>
+  </si>
+  <si>
+    <t>643720713001</t>
+  </si>
+  <si>
+    <t>819086228280</t>
+  </si>
+  <si>
+    <t>250109516845</t>
+  </si>
+  <si>
+    <t>805499248836</t>
+  </si>
+  <si>
+    <t>279156224329</t>
+  </si>
+  <si>
+    <t>854961585532</t>
+  </si>
+  <si>
+    <t>894149003844</t>
+  </si>
+  <si>
+    <t>487455304651</t>
+  </si>
+  <si>
+    <t>563293681247</t>
+  </si>
+  <si>
+    <t>396822694369</t>
+  </si>
+  <si>
+    <t>773530278961</t>
+  </si>
+  <si>
+    <t>041381565943</t>
+  </si>
+  <si>
+    <t>531249141408</t>
+  </si>
+  <si>
+    <t>552219280076</t>
+  </si>
+  <si>
+    <t>702943006347</t>
+  </si>
+  <si>
+    <t>241572944654</t>
+  </si>
+  <si>
+    <t>653812224222</t>
+  </si>
+  <si>
+    <t>277513356036</t>
+  </si>
+  <si>
+    <t>091487785741</t>
+  </si>
+  <si>
+    <t>346701415628</t>
+  </si>
+  <si>
+    <t>803175723022</t>
+  </si>
+  <si>
+    <t>908253091114</t>
+  </si>
+  <si>
+    <t>755887011597</t>
+  </si>
+  <si>
+    <t>025726843815</t>
+  </si>
+  <si>
+    <t>390467262891</t>
+  </si>
+  <si>
+    <t>698513710516</t>
+  </si>
+  <si>
+    <t>210225792096</t>
+  </si>
+  <si>
+    <t>027089092114</t>
+  </si>
+  <si>
+    <t>236081354779</t>
+  </si>
+  <si>
+    <t>031095037040</t>
+  </si>
+  <si>
+    <t>475238809382</t>
+  </si>
+  <si>
+    <t>375695730319</t>
+  </si>
+  <si>
+    <t>034116501112</t>
+  </si>
+  <si>
+    <t>539701831198</t>
+  </si>
+  <si>
+    <t>977418648860</t>
+  </si>
+  <si>
+    <t>522096545218</t>
+  </si>
+  <si>
+    <t>145122332355</t>
+  </si>
+  <si>
+    <t>027004432467</t>
+  </si>
+  <si>
+    <t>051082712360</t>
+  </si>
+  <si>
+    <t>107983374271</t>
+  </si>
+  <si>
+    <t>950555922941</t>
+  </si>
+  <si>
+    <t>402353158118</t>
+  </si>
+  <si>
+    <t>624523215289</t>
+  </si>
+  <si>
+    <t>039826392824</t>
+  </si>
+  <si>
+    <t>663351577324</t>
+  </si>
+  <si>
+    <t>012644982486</t>
+  </si>
+  <si>
+    <t>295925841014</t>
+  </si>
+  <si>
+    <t>725225980601</t>
+  </si>
+  <si>
+    <t>762184971138</t>
+  </si>
+  <si>
+    <t>918879926148</t>
+  </si>
+  <si>
+    <t>323762289750</t>
+  </si>
+  <si>
+    <t>821774640185</t>
+  </si>
+  <si>
+    <t>208575422759</t>
+  </si>
+  <si>
+    <t>092249060904</t>
+  </si>
+  <si>
+    <t>876040921209</t>
+  </si>
+  <si>
+    <t>649631514161</t>
+  </si>
+  <si>
+    <t>661888781378</t>
+  </si>
+  <si>
+    <t>440433199188</t>
+  </si>
+  <si>
+    <t>278812186425</t>
+  </si>
+  <si>
+    <t>325295136715</t>
+  </si>
+  <si>
+    <t>944402409944</t>
+  </si>
+  <si>
+    <t>127143604068</t>
+  </si>
+  <si>
+    <t>424994102575</t>
+  </si>
+  <si>
+    <t>582157245460</t>
+  </si>
+  <si>
+    <t>195758177378</t>
+  </si>
+  <si>
+    <t>850822333473</t>
+  </si>
+  <si>
+    <t>514825287460</t>
+  </si>
+  <si>
+    <t>524667680870</t>
+  </si>
+  <si>
+    <t>611151000079</t>
+  </si>
+  <si>
+    <t>798363936543</t>
+  </si>
+  <si>
+    <t>458310604356</t>
+  </si>
+  <si>
+    <t>425981845560</t>
+  </si>
+  <si>
+    <t>014727677685</t>
+  </si>
+  <si>
+    <t>929925092184</t>
+  </si>
+  <si>
+    <t>667449437627</t>
+  </si>
+  <si>
+    <t>463797731523</t>
+  </si>
+  <si>
+    <t>886438632489</t>
+  </si>
+  <si>
+    <t>554714269509</t>
+  </si>
+  <si>
+    <t>583361023840</t>
+  </si>
+  <si>
+    <t>881852990252</t>
+  </si>
+  <si>
+    <t>054668491179</t>
+  </si>
+  <si>
+    <t>086955035645</t>
+  </si>
+  <si>
+    <t>245159474413</t>
+  </si>
+  <si>
+    <t>811969398426</t>
+  </si>
+  <si>
+    <t>525272423914</t>
+  </si>
+  <si>
+    <t>458920638555</t>
+  </si>
+  <si>
+    <t>895046587528</t>
+  </si>
+  <si>
+    <t>072374533316</t>
+  </si>
+  <si>
+    <t>304716643275</t>
+  </si>
+  <si>
+    <t>469207750058</t>
+  </si>
+  <si>
+    <t>298013853796</t>
+  </si>
+  <si>
+    <t>282718551402</t>
+  </si>
+  <si>
+    <t>665227625969</t>
+  </si>
+  <si>
+    <t>628019185534</t>
+  </si>
+  <si>
+    <t>629300446424</t>
+  </si>
+  <si>
+    <t>767090977916</t>
+  </si>
+  <si>
+    <t>551886008840</t>
+  </si>
+  <si>
+    <t>844502949893</t>
+  </si>
+  <si>
+    <t>432361234757</t>
+  </si>
+  <si>
+    <t>789562191371</t>
+  </si>
+  <si>
+    <t>945204637714</t>
+  </si>
+  <si>
+    <t>563497930775</t>
+  </si>
+  <si>
+    <t>388175711453</t>
+  </si>
+  <si>
+    <t>522355840708</t>
+  </si>
+  <si>
+    <t>991142701489</t>
+  </si>
+  <si>
+    <t>371877098958</t>
+  </si>
+  <si>
+    <t>484123184595</t>
+  </si>
+  <si>
+    <t>690016901422</t>
+  </si>
+  <si>
+    <t>985594238884</t>
+  </si>
+  <si>
+    <t>145764126822</t>
+  </si>
+  <si>
+    <t>397136695067</t>
+  </si>
+  <si>
+    <t>615121245410</t>
+  </si>
+  <si>
+    <t>183132026019</t>
+  </si>
+  <si>
+    <t>812669240430</t>
+  </si>
+  <si>
+    <t>440894350989</t>
+  </si>
+  <si>
+    <t>494283461844</t>
+  </si>
+  <si>
+    <t>040437804523</t>
+  </si>
+  <si>
+    <t>352438318934</t>
+  </si>
+  <si>
+    <t>037872833852</t>
+  </si>
+  <si>
+    <t>157676201780</t>
+  </si>
+  <si>
+    <t>102981748849</t>
+  </si>
+  <si>
+    <t>836251215863</t>
+  </si>
+  <si>
+    <t>494709456452</t>
+  </si>
+  <si>
+    <t>755004704128</t>
+  </si>
+  <si>
+    <t>743027148075</t>
+  </si>
+  <si>
+    <t>488527881679</t>
+  </si>
+  <si>
+    <t>307009100998</t>
+  </si>
+  <si>
+    <t>979270662682</t>
+  </si>
+  <si>
+    <t>203256338150</t>
+  </si>
+  <si>
+    <t>855727555145</t>
+  </si>
+  <si>
+    <t>927141147484</t>
+  </si>
+  <si>
+    <t>818258507200</t>
+  </si>
+  <si>
+    <t>475451994031</t>
+  </si>
+  <si>
+    <t>502996149103</t>
+  </si>
+  <si>
+    <t>654591230654</t>
+  </si>
+  <si>
+    <t>530826966563</t>
+  </si>
+  <si>
+    <t>591831583134</t>
+  </si>
+  <si>
+    <t>996873237659</t>
+  </si>
+  <si>
+    <t>495698530095</t>
+  </si>
+  <si>
+    <t>263864324891</t>
+  </si>
+  <si>
+    <t>408891031937</t>
+  </si>
+  <si>
+    <t>982443410167</t>
+  </si>
+  <si>
+    <t>198379868723</t>
+  </si>
+  <si>
+    <t>652338819288</t>
+  </si>
+  <si>
+    <t>195005441641</t>
+  </si>
+  <si>
+    <t>266948833646</t>
+  </si>
+  <si>
+    <t>113953946546</t>
+  </si>
+  <si>
+    <t>357244102804</t>
+  </si>
+  <si>
+    <t>573490693400</t>
+  </si>
+  <si>
+    <t>355088889023</t>
+  </si>
+  <si>
+    <t>629356430780</t>
+  </si>
+  <si>
+    <t>279897419121</t>
+  </si>
+  <si>
+    <t>588671257487</t>
+  </si>
+  <si>
+    <t>910535498565</t>
+  </si>
+  <si>
+    <t>321424250510</t>
+  </si>
+  <si>
+    <t>098300597609</t>
+  </si>
+  <si>
+    <t>745752990079</t>
+  </si>
+  <si>
+    <t>095993445363</t>
+  </si>
+  <si>
+    <t>203126929517</t>
+  </si>
+  <si>
+    <t>217673852353</t>
+  </si>
+  <si>
+    <t>618517885285</t>
+  </si>
+  <si>
+    <t>572006200291</t>
+  </si>
+  <si>
+    <t>345055798972</t>
+  </si>
+  <si>
+    <t>060990634280</t>
+  </si>
+  <si>
+    <t>894995597010</t>
+  </si>
+  <si>
+    <t>917203711157</t>
+  </si>
+  <si>
+    <t>647834396516</t>
+  </si>
+  <si>
+    <t>941366001225</t>
+  </si>
+  <si>
+    <t>416960873577</t>
+  </si>
+  <si>
+    <t>524161613019</t>
+  </si>
+  <si>
+    <t>245270763123</t>
+  </si>
+  <si>
+    <t>139890925779</t>
+  </si>
+  <si>
+    <t>419268501611</t>
+  </si>
+  <si>
+    <t>479233229620</t>
+  </si>
+  <si>
+    <t>435959721079</t>
+  </si>
+  <si>
+    <t>974012936477</t>
+  </si>
+  <si>
+    <t>267079824606</t>
+  </si>
+  <si>
+    <t>160799841353</t>
+  </si>
+  <si>
+    <t>296131116952</t>
+  </si>
+  <si>
+    <t>468167727597</t>
+  </si>
+  <si>
+    <t>106384633707</t>
+  </si>
+  <si>
+    <t>244588146728</t>
+  </si>
+  <si>
+    <t>907727655261</t>
+  </si>
+  <si>
+    <t>909646671656</t>
+  </si>
+  <si>
+    <t>802248116249</t>
+  </si>
+  <si>
+    <t>235170899610</t>
+  </si>
+  <si>
+    <t>502185672388</t>
+  </si>
+  <si>
+    <t>633638416440</t>
+  </si>
+  <si>
+    <t>195213578898</t>
+  </si>
+  <si>
+    <t>962853315934</t>
+  </si>
+  <si>
+    <t>541060919084</t>
+  </si>
+  <si>
+    <t>204920699582</t>
+  </si>
+  <si>
+    <t>474687255192</t>
+  </si>
+  <si>
+    <t>670678232235</t>
+  </si>
+  <si>
+    <t>416716217335</t>
+  </si>
+  <si>
+    <t>856013233244</t>
+  </si>
+  <si>
+    <t>305800019680</t>
+  </si>
+  <si>
+    <t>300091001119</t>
+  </si>
+  <si>
+    <t>042123549022</t>
+  </si>
+  <si>
+    <t>911826287028</t>
+  </si>
+  <si>
+    <t>385230772616</t>
+  </si>
+  <si>
+    <t>693656394540</t>
+  </si>
+  <si>
+    <t>519321623802</t>
+  </si>
+  <si>
+    <t>243258878725</t>
+  </si>
+  <si>
+    <t>381113122791</t>
+  </si>
+  <si>
+    <t>338329699538</t>
+  </si>
+  <si>
+    <t>190291196812</t>
+  </si>
+  <si>
+    <t>101472731178</t>
+  </si>
+  <si>
+    <t>417328061338</t>
+  </si>
+  <si>
+    <t>698369238136</t>
+  </si>
+  <si>
+    <t>664555589289</t>
+  </si>
+  <si>
+    <t>697751250871</t>
+  </si>
+  <si>
+    <t>410415192665</t>
+  </si>
+  <si>
+    <t>453436200871</t>
+  </si>
+  <si>
+    <t>921096784507</t>
+  </si>
+  <si>
+    <t>500905115988</t>
+  </si>
+  <si>
+    <t>234173637602</t>
+  </si>
+  <si>
+    <t>800465383927</t>
+  </si>
+  <si>
+    <t>546638590163</t>
+  </si>
+  <si>
+    <t>644321740770</t>
+  </si>
+  <si>
+    <t>367007212469</t>
+  </si>
+  <si>
+    <t>608730421315</t>
+  </si>
+  <si>
+    <t>443297752738</t>
+  </si>
+  <si>
+    <t>418761308533</t>
+  </si>
+  <si>
+    <t>431488989388</t>
+  </si>
+  <si>
+    <t>823909417371</t>
+  </si>
+  <si>
+    <t>261776378820</t>
+  </si>
+  <si>
+    <t>297740611987</t>
+  </si>
+  <si>
+    <t>982018141902</t>
+  </si>
+  <si>
+    <t>354445794599</t>
+  </si>
+  <si>
+    <t>074827590199</t>
+  </si>
+  <si>
+    <t>300092406130</t>
+  </si>
+  <si>
+    <t>898248249628</t>
+  </si>
+  <si>
+    <t>762145687389</t>
+  </si>
+  <si>
+    <t>350758949055</t>
+  </si>
+  <si>
+    <t>745196631561</t>
+  </si>
+  <si>
+    <t>495141433060</t>
+  </si>
+  <si>
+    <t>360820207997</t>
+  </si>
+  <si>
+    <t>045101669962</t>
+  </si>
+  <si>
+    <t>671970439097</t>
+  </si>
+  <si>
+    <t>057008693518</t>
+  </si>
+  <si>
+    <t>506806447538</t>
+  </si>
+  <si>
+    <t>614074978437</t>
+  </si>
+  <si>
+    <t>733648024301</t>
+  </si>
+  <si>
+    <t>726722132721</t>
+  </si>
+  <si>
+    <t>868286125027</t>
+  </si>
+  <si>
+    <t>833876204165</t>
+  </si>
+  <si>
+    <t>457014266126</t>
+  </si>
+  <si>
+    <t>692468292245</t>
+  </si>
+  <si>
+    <t>960475257430</t>
+  </si>
+  <si>
+    <t>103618244252</t>
+  </si>
+  <si>
+    <t>943435165855</t>
+  </si>
+  <si>
+    <t>823266320161</t>
+  </si>
+  <si>
+    <t>493089174899</t>
+  </si>
+  <si>
+    <t>672986731530</t>
+  </si>
+  <si>
+    <t>457464450746</t>
+  </si>
+  <si>
+    <t>431480755437</t>
+  </si>
+  <si>
+    <t>787556080335</t>
+  </si>
+  <si>
+    <t>122514405571</t>
+  </si>
+  <si>
+    <t>278183288003</t>
+  </si>
+  <si>
+    <t>533121739038</t>
+  </si>
+  <si>
+    <t>658520711375</t>
+  </si>
+  <si>
+    <t>583308830116</t>
+  </si>
+  <si>
+    <t>166610522756</t>
+  </si>
+  <si>
+    <t>374102152501</t>
+  </si>
+  <si>
+    <t>986232061132</t>
+  </si>
+  <si>
+    <t>681972712071</t>
+  </si>
+  <si>
+    <t>017253319382</t>
+  </si>
+  <si>
+    <t>223137278414</t>
+  </si>
+  <si>
+    <t>323694855482</t>
+  </si>
+  <si>
+    <t>061940067840</t>
+  </si>
+  <si>
+    <t>493038653137</t>
+  </si>
+  <si>
+    <t>279897701505</t>
+  </si>
+  <si>
+    <t>726630986630</t>
+  </si>
+  <si>
+    <t>195716506759</t>
+  </si>
+  <si>
+    <t>118771256698</t>
+  </si>
+  <si>
+    <t>470719467914</t>
+  </si>
+  <si>
+    <t>684439128445</t>
+  </si>
+  <si>
+    <t>351238049645</t>
+  </si>
+  <si>
+    <t>132557527443</t>
+  </si>
+  <si>
+    <t>405618138416</t>
+  </si>
+  <si>
+    <t>397514993932</t>
+  </si>
+  <si>
+    <t>096787095025</t>
+  </si>
+  <si>
+    <t>077711034522</t>
+  </si>
+  <si>
+    <t>908132246672</t>
+  </si>
+  <si>
+    <t>730263475228</t>
+  </si>
+  <si>
+    <t>794751734694</t>
+  </si>
+  <si>
+    <t>766732199597</t>
+  </si>
+  <si>
+    <t>980769853683</t>
+  </si>
+  <si>
+    <t>187605033478</t>
+  </si>
+  <si>
+    <t>471360173383</t>
+  </si>
+  <si>
+    <t>067690119617</t>
+  </si>
+  <si>
+    <t>850723880972</t>
+  </si>
+  <si>
+    <t>136162941149</t>
+  </si>
+  <si>
+    <t>766842213808</t>
+  </si>
+  <si>
+    <t>023050908183</t>
+  </si>
+  <si>
+    <t>644630987399</t>
+  </si>
+  <si>
+    <t>594095280065</t>
+  </si>
+  <si>
+    <t>286366040764</t>
+  </si>
+  <si>
+    <t>291355067361</t>
+  </si>
+  <si>
+    <t>506448021449</t>
+  </si>
+  <si>
+    <t>377466780553</t>
+  </si>
+  <si>
+    <t>899293293072</t>
+  </si>
+  <si>
+    <t>454611223808</t>
+  </si>
+  <si>
+    <t>013669511502</t>
+  </si>
+  <si>
+    <t>314002471878</t>
+  </si>
+  <si>
+    <t>715839835585</t>
+  </si>
+  <si>
+    <t>802442261460</t>
+  </si>
+  <si>
+    <t>939025519243</t>
+  </si>
+  <si>
+    <t>588065142449</t>
+  </si>
+  <si>
+    <t>473938735257</t>
+  </si>
+  <si>
+    <t>407389263574</t>
+  </si>
+  <si>
+    <t>210415150001</t>
+  </si>
+  <si>
+    <t>552092857990</t>
+  </si>
+  <si>
+    <t>778082929259</t>
+  </si>
+  <si>
+    <t>096799894016</t>
+  </si>
+  <si>
+    <t>469464157800</t>
+  </si>
+  <si>
+    <t>990767516645</t>
+  </si>
+  <si>
+    <t>945013845094</t>
+  </si>
+  <si>
+    <t>852993434386</t>
+  </si>
+  <si>
+    <t>055488820553</t>
+  </si>
+  <si>
+    <t>478508661653</t>
+  </si>
+  <si>
+    <t>060937638596</t>
+  </si>
+  <si>
+    <t>566440242507</t>
+  </si>
+  <si>
+    <t>143381070724</t>
+  </si>
+  <si>
+    <t>870972267838</t>
+  </si>
+  <si>
+    <t>631562083298</t>
+  </si>
+  <si>
+    <t>899255297331</t>
+  </si>
+  <si>
+    <t>263171750456</t>
+  </si>
+  <si>
+    <t>338782285708</t>
+  </si>
+  <si>
+    <t>721029522534</t>
+  </si>
+  <si>
+    <t>370165267392</t>
+  </si>
+  <si>
+    <t>033846833269</t>
+  </si>
+  <si>
+    <t>362768922677</t>
+  </si>
+  <si>
+    <t>792407033575</t>
+  </si>
+  <si>
+    <t>214254128288</t>
+  </si>
+  <si>
+    <t>411656944495</t>
+  </si>
+  <si>
+    <t>720392027361</t>
+  </si>
+  <si>
+    <t>146118882142</t>
+  </si>
+  <si>
+    <t>127540916329</t>
+  </si>
+  <si>
+    <t>814692123568</t>
+  </si>
+  <si>
+    <t>327216875925</t>
+  </si>
+  <si>
+    <t>244134337443</t>
+  </si>
+  <si>
+    <t>090736666151</t>
+  </si>
+  <si>
+    <t>103198540603</t>
+  </si>
+  <si>
+    <t>754429328657</t>
+  </si>
+  <si>
+    <t>814046914013</t>
+  </si>
+  <si>
+    <t>223824978034</t>
+  </si>
+  <si>
+    <t>608294797014</t>
+  </si>
+  <si>
+    <t>312667076078</t>
+  </si>
+  <si>
+    <t>934505734561</t>
+  </si>
+  <si>
+    <t>017540689149</t>
+  </si>
+  <si>
+    <t>949064105187</t>
+  </si>
+  <si>
+    <t>248282501282</t>
+  </si>
+  <si>
+    <t>871910853894</t>
+  </si>
+  <si>
+    <t>467417835032</t>
+  </si>
+  <si>
+    <t>716827613312</t>
+  </si>
+  <si>
+    <t>117419703741</t>
+  </si>
+  <si>
+    <t>530308721743</t>
+  </si>
+  <si>
+    <t>745566326860</t>
+  </si>
+  <si>
+    <t>790645216279</t>
+  </si>
+  <si>
+    <t>371658785422</t>
+  </si>
+  <si>
+    <t>828646824605</t>
+  </si>
+  <si>
+    <t>140785481470</t>
+  </si>
+  <si>
+    <t>640542708088</t>
+  </si>
+  <si>
+    <t>052916906165</t>
+  </si>
+  <si>
+    <t>062074295529</t>
+  </si>
+  <si>
+    <t>026561610911</t>
+  </si>
+  <si>
+    <t>614337112839</t>
+  </si>
+  <si>
+    <t>597790312022</t>
+  </si>
+  <si>
+    <t>757816051461</t>
+  </si>
+  <si>
+    <t>311009201771</t>
+  </si>
+  <si>
+    <t>560838889933</t>
+  </si>
+  <si>
+    <t>182623155689</t>
+  </si>
+  <si>
+    <t>856325997994</t>
+  </si>
+  <si>
+    <t>206717076732</t>
+  </si>
+  <si>
+    <t>556019829784</t>
+  </si>
+  <si>
+    <t>320983170200</t>
+  </si>
+  <si>
+    <t>962550102984</t>
+  </si>
+  <si>
+    <t>760860528283</t>
+  </si>
+  <si>
+    <t>030273806994</t>
+  </si>
+  <si>
+    <t>706027556187</t>
+  </si>
+  <si>
+    <t>739833517115</t>
+  </si>
+  <si>
+    <t>862819688916</t>
+  </si>
+  <si>
+    <t>213962636683</t>
+  </si>
+  <si>
+    <t>920449917316</t>
+  </si>
+  <si>
+    <t>368569663967</t>
+  </si>
+  <si>
+    <t>887113382819</t>
+  </si>
+  <si>
+    <t>616173705430</t>
+  </si>
+  <si>
+    <t>187188002916</t>
+  </si>
+  <si>
+    <t>757646636973</t>
+  </si>
+  <si>
+    <t>021841519558</t>
+  </si>
+  <si>
+    <t>347965150072</t>
+  </si>
+  <si>
+    <t>839484710019</t>
+  </si>
+  <si>
+    <t>734290765948</t>
+  </si>
+  <si>
+    <t>448902127191</t>
+  </si>
+  <si>
+    <t>157724903484</t>
+  </si>
+  <si>
+    <t>796505017981</t>
+  </si>
+  <si>
+    <t>266227284370</t>
+  </si>
+  <si>
+    <t>059642063878</t>
+  </si>
+  <si>
+    <t>244453568390</t>
+  </si>
+  <si>
+    <t>767959592972</t>
+  </si>
+  <si>
+    <t>351372261035</t>
+  </si>
+  <si>
+    <t>809495131697</t>
+  </si>
+  <si>
+    <t>235402872613</t>
+  </si>
+  <si>
+    <t>107290020647</t>
+  </si>
+  <si>
+    <t>378709599898</t>
+  </si>
+  <si>
+    <t>151605557371</t>
+  </si>
+  <si>
+    <t>470712054778</t>
+  </si>
+  <si>
+    <t>888172063678</t>
+  </si>
+  <si>
+    <t>302747242343</t>
+  </si>
+  <si>
+    <t>198630010231</t>
+  </si>
+  <si>
+    <t>103226002370</t>
+  </si>
+  <si>
+    <t>504958172586</t>
+  </si>
+  <si>
+    <t>008881919995</t>
+  </si>
+  <si>
+    <t>208367645377</t>
+  </si>
+  <si>
+    <t>628425976691</t>
+  </si>
+  <si>
+    <t>203432133655</t>
+  </si>
+  <si>
+    <t>446417709373</t>
+  </si>
+  <si>
+    <t>628457429554</t>
+  </si>
+  <si>
+    <t>619525546501</t>
+  </si>
+  <si>
+    <t>393619605560</t>
+  </si>
+  <si>
+    <t>548169883122</t>
+  </si>
+  <si>
+    <t>154910855236</t>
+  </si>
+  <si>
+    <t>305533047354</t>
+  </si>
+  <si>
+    <t>859480229937</t>
+  </si>
+  <si>
+    <t>546572380819</t>
+  </si>
+  <si>
+    <t>035038138815</t>
+  </si>
+  <si>
+    <t>232846795001</t>
+  </si>
+  <si>
+    <t>853195264149</t>
+  </si>
+  <si>
+    <t>856154334972</t>
+  </si>
+  <si>
+    <t>321194903244</t>
+  </si>
+  <si>
+    <t>952424639366</t>
+  </si>
+  <si>
+    <t>155347333156</t>
+  </si>
+  <si>
+    <t>342528626682</t>
+  </si>
+  <si>
+    <t>309990480873</t>
+  </si>
+  <si>
+    <t>696983346751</t>
+  </si>
+  <si>
+    <t>119728041598</t>
+  </si>
+  <si>
+    <t>999326578878</t>
+  </si>
+  <si>
+    <t>926183398206</t>
+  </si>
+  <si>
+    <t>620790364862</t>
+  </si>
+  <si>
+    <t>795318442708</t>
+  </si>
+  <si>
+    <t>298197775987</t>
   </si>
 </sst>
 </file>

--- a/uploadfile.xlsx
+++ b/uploadfile.xlsx
@@ -20,1507 +20,1507 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>771109346654</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>047062340964</t>
-  </si>
-  <si>
-    <t>709829563003</t>
-  </si>
-  <si>
-    <t>517488247868</t>
-  </si>
-  <si>
-    <t>361568447951</t>
-  </si>
-  <si>
-    <t>681023085848</t>
-  </si>
-  <si>
-    <t>273574235129</t>
-  </si>
-  <si>
-    <t>694765512512</t>
-  </si>
-  <si>
-    <t>976041914129</t>
-  </si>
-  <si>
-    <t>831673309084</t>
-  </si>
-  <si>
-    <t>846609966434</t>
-  </si>
-  <si>
-    <t>657231661264</t>
-  </si>
-  <si>
-    <t>130769731732</t>
-  </si>
-  <si>
-    <t>932241637972</t>
-  </si>
-  <si>
-    <t>688170987119</t>
-  </si>
-  <si>
-    <t>498208930975</t>
-  </si>
-  <si>
-    <t>296038545353</t>
-  </si>
-  <si>
-    <t>137759278898</t>
-  </si>
-  <si>
-    <t>283371889247</t>
-  </si>
-  <si>
-    <t>978309728205</t>
-  </si>
-  <si>
-    <t>449837529183</t>
-  </si>
-  <si>
-    <t>851792790477</t>
-  </si>
-  <si>
-    <t>330196736089</t>
-  </si>
-  <si>
-    <t>197273833775</t>
-  </si>
-  <si>
-    <t>583282828139</t>
-  </si>
-  <si>
-    <t>427424416439</t>
-  </si>
-  <si>
-    <t>219113815142</t>
-  </si>
-  <si>
-    <t>508885047797</t>
-  </si>
-  <si>
-    <t>370632604742</t>
-  </si>
-  <si>
-    <t>750177918160</t>
-  </si>
-  <si>
-    <t>177637202648</t>
-  </si>
-  <si>
-    <t>263026192562</t>
-  </si>
-  <si>
-    <t>244215122832</t>
-  </si>
-  <si>
-    <t>562572202921</t>
-  </si>
-  <si>
-    <t>773942246306</t>
-  </si>
-  <si>
-    <t>480342044039</t>
-  </si>
-  <si>
-    <t>768470196522</t>
-  </si>
-  <si>
-    <t>082114771588</t>
-  </si>
-  <si>
-    <t>669785157886</t>
-  </si>
-  <si>
-    <t>762669237281</t>
-  </si>
-  <si>
-    <t>343269942716</t>
-  </si>
-  <si>
-    <t>744183728315</t>
-  </si>
-  <si>
-    <t>548662557850</t>
-  </si>
-  <si>
-    <t>667676706279</t>
-  </si>
-  <si>
-    <t>286522558999</t>
-  </si>
-  <si>
-    <t>371273060935</t>
-  </si>
-  <si>
-    <t>109658068445</t>
-  </si>
-  <si>
-    <t>365795205193</t>
-  </si>
-  <si>
-    <t>588626049843</t>
-  </si>
-  <si>
-    <t>910788801776</t>
-  </si>
-  <si>
-    <t>538689162719</t>
-  </si>
-  <si>
-    <t>532266630388</t>
-  </si>
-  <si>
-    <t>010739356095</t>
-  </si>
-  <si>
-    <t>551199902204</t>
-  </si>
-  <si>
-    <t>905729164157</t>
-  </si>
-  <si>
-    <t>035126042386</t>
-  </si>
-  <si>
-    <t>891768870278</t>
-  </si>
-  <si>
-    <t>322922950636</t>
-  </si>
-  <si>
-    <t>669371749711</t>
-  </si>
-  <si>
-    <t>033104753896</t>
-  </si>
-  <si>
-    <t>585038259959</t>
-  </si>
-  <si>
-    <t>138572308189</t>
-  </si>
-  <si>
-    <t>132136025623</t>
-  </si>
-  <si>
-    <t>747220556809</t>
-  </si>
-  <si>
-    <t>242825615966</t>
-  </si>
-  <si>
-    <t>022249279686</t>
-  </si>
-  <si>
-    <t>507930177263</t>
-  </si>
-  <si>
-    <t>220710666240</t>
-  </si>
-  <si>
-    <t>999473572513</t>
-  </si>
-  <si>
-    <t>985323088623</t>
-  </si>
-  <si>
-    <t>039989169718</t>
-  </si>
-  <si>
-    <t>301975972356</t>
-  </si>
-  <si>
-    <t>866476347356</t>
-  </si>
-  <si>
-    <t>569815071872</t>
-  </si>
-  <si>
-    <t>079314235814</t>
-  </si>
-  <si>
-    <t>769630210473</t>
-  </si>
-  <si>
-    <t>102126619819</t>
-  </si>
-  <si>
-    <t>206391497577</t>
-  </si>
-  <si>
-    <t>713073757909</t>
-  </si>
-  <si>
-    <t>624752401806</t>
-  </si>
-  <si>
-    <t>173426798962</t>
-  </si>
-  <si>
-    <t>875196032061</t>
-  </si>
-  <si>
-    <t>938805144194</t>
-  </si>
-  <si>
-    <t>211779833947</t>
-  </si>
-  <si>
-    <t>787743417755</t>
-  </si>
-  <si>
-    <t>887043546763</t>
-  </si>
-  <si>
-    <t>467634692783</t>
-  </si>
-  <si>
-    <t>388121593357</t>
-  </si>
-  <si>
-    <t>532933056696</t>
-  </si>
-  <si>
-    <t>071596220608</t>
-  </si>
-  <si>
-    <t>695891177546</t>
-  </si>
-  <si>
-    <t>458513597097</t>
-  </si>
-  <si>
-    <t>103611424352</t>
-  </si>
-  <si>
-    <t>002911755731</t>
-  </si>
-  <si>
-    <t>448490069403</t>
-  </si>
-  <si>
-    <t>545579031819</t>
-  </si>
-  <si>
-    <t>055624265777</t>
-  </si>
-  <si>
-    <t>442971369897</t>
-  </si>
-  <si>
-    <t>534984673820</t>
-  </si>
-  <si>
-    <t>352905491577</t>
-  </si>
-  <si>
-    <t>411796390678</t>
-  </si>
-  <si>
-    <t>618278141008</t>
-  </si>
-  <si>
-    <t>314724845352</t>
-  </si>
-  <si>
-    <t>718177404174</t>
-  </si>
-  <si>
-    <t>625389230904</t>
-  </si>
-  <si>
-    <t>471226934431</t>
-  </si>
-  <si>
-    <t>610819296616</t>
-  </si>
-  <si>
-    <t>049562278942</t>
-  </si>
-  <si>
-    <t>377163630337</t>
-  </si>
-  <si>
-    <t>014362705475</t>
-  </si>
-  <si>
-    <t>066401855403</t>
-  </si>
-  <si>
-    <t>668376925793</t>
-  </si>
-  <si>
-    <t>018068726120</t>
-  </si>
-  <si>
-    <t>391320421594</t>
-  </si>
-  <si>
-    <t>111395919758</t>
-  </si>
-  <si>
-    <t>684262849752</t>
-  </si>
-  <si>
-    <t>395144953957</t>
-  </si>
-  <si>
-    <t>882393834267</t>
-  </si>
-  <si>
-    <t>576975441161</t>
-  </si>
-  <si>
-    <t>842925963022</t>
-  </si>
-  <si>
-    <t>148112057326</t>
-  </si>
-  <si>
-    <t>086628922998</t>
-  </si>
-  <si>
-    <t>414221895844</t>
-  </si>
-  <si>
-    <t>893557870946</t>
-  </si>
-  <si>
-    <t>780356585704</t>
-  </si>
-  <si>
-    <t>214546266190</t>
-  </si>
-  <si>
-    <t>344870015934</t>
-  </si>
-  <si>
-    <t>586430520408</t>
-  </si>
-  <si>
-    <t>205816896243</t>
-  </si>
-  <si>
-    <t>475198143279</t>
-  </si>
-  <si>
-    <t>347194231460</t>
-  </si>
-  <si>
-    <t>755310240589</t>
-  </si>
-  <si>
-    <t>840096266600</t>
-  </si>
-  <si>
-    <t>979121764975</t>
-  </si>
-  <si>
-    <t>565446424170</t>
-  </si>
-  <si>
-    <t>177645858411</t>
-  </si>
-  <si>
-    <t>622518995300</t>
-  </si>
-  <si>
-    <t>766297268585</t>
-  </si>
-  <si>
-    <t>438763789796</t>
-  </si>
-  <si>
-    <t>842922094527</t>
-  </si>
-  <si>
-    <t>883763402711</t>
-  </si>
-  <si>
-    <t>805198244102</t>
-  </si>
-  <si>
-    <t>074179388910</t>
-  </si>
-  <si>
-    <t>794812693734</t>
-  </si>
-  <si>
-    <t>073578540970</t>
-  </si>
-  <si>
-    <t>530979268856</t>
-  </si>
-  <si>
-    <t>583512342467</t>
-  </si>
-  <si>
-    <t>908480305464</t>
-  </si>
-  <si>
-    <t>224996662879</t>
-  </si>
-  <si>
-    <t>153665613864</t>
-  </si>
-  <si>
-    <t>468068956347</t>
-  </si>
-  <si>
-    <t>264251752158</t>
-  </si>
-  <si>
-    <t>376969861545</t>
-  </si>
-  <si>
-    <t>573246442746</t>
-  </si>
-  <si>
-    <t>222182706652</t>
-  </si>
-  <si>
-    <t>458413339484</t>
-  </si>
-  <si>
-    <t>807647622983</t>
-  </si>
-  <si>
-    <t>556827433388</t>
-  </si>
-  <si>
-    <t>224820286583</t>
-  </si>
-  <si>
-    <t>893749545542</t>
-  </si>
-  <si>
-    <t>648012963295</t>
-  </si>
-  <si>
-    <t>072069893242</t>
-  </si>
-  <si>
-    <t>577314833190</t>
-  </si>
-  <si>
-    <t>086417806358</t>
-  </si>
-  <si>
-    <t>205138093469</t>
-  </si>
-  <si>
-    <t>828283964497</t>
-  </si>
-  <si>
-    <t>965547713813</t>
-  </si>
-  <si>
-    <t>757853329667</t>
-  </si>
-  <si>
-    <t>176828539855</t>
-  </si>
-  <si>
-    <t>947258042362</t>
-  </si>
-  <si>
-    <t>308180222871</t>
-  </si>
-  <si>
-    <t>207208225165</t>
-  </si>
-  <si>
-    <t>361372553283</t>
-  </si>
-  <si>
-    <t>395947508225</t>
-  </si>
-  <si>
-    <t>016024945571</t>
-  </si>
-  <si>
-    <t>810316566805</t>
-  </si>
-  <si>
-    <t>993459659087</t>
-  </si>
-  <si>
-    <t>888308514804</t>
-  </si>
-  <si>
-    <t>645385349857</t>
-  </si>
-  <si>
-    <t>514050949185</t>
-  </si>
-  <si>
-    <t>520914342183</t>
-  </si>
-  <si>
-    <t>462978683260</t>
-  </si>
-  <si>
-    <t>795511893665</t>
-  </si>
-  <si>
-    <t>323484812923</t>
-  </si>
-  <si>
-    <t>304080533329</t>
-  </si>
-  <si>
-    <t>716978633511</t>
-  </si>
-  <si>
-    <t>008373051171</t>
-  </si>
-  <si>
-    <t>538421886929</t>
-  </si>
-  <si>
-    <t>633142456258</t>
-  </si>
-  <si>
-    <t>754474682416</t>
-  </si>
-  <si>
-    <t>586471090994</t>
-  </si>
-  <si>
-    <t>462504351135</t>
-  </si>
-  <si>
-    <t>971588820033</t>
-  </si>
-  <si>
-    <t>225149449516</t>
-  </si>
-  <si>
-    <t>050756433286</t>
-  </si>
-  <si>
-    <t>541488198632</t>
-  </si>
-  <si>
-    <t>356636936104</t>
-  </si>
-  <si>
-    <t>012246945771</t>
-  </si>
-  <si>
-    <t>166260299619</t>
-  </si>
-  <si>
-    <t>370440607362</t>
-  </si>
-  <si>
-    <t>329160597428</t>
-  </si>
-  <si>
-    <t>544182923306</t>
-  </si>
-  <si>
-    <t>120217614527</t>
-  </si>
-  <si>
-    <t>789552441682</t>
-  </si>
-  <si>
-    <t>822779229626</t>
-  </si>
-  <si>
-    <t>424971793240</t>
-  </si>
-  <si>
-    <t>721032447927</t>
-  </si>
-  <si>
-    <t>223613861536</t>
-  </si>
-  <si>
-    <t>493866014152</t>
-  </si>
-  <si>
-    <t>552317507563</t>
-  </si>
-  <si>
-    <t>501325420537</t>
-  </si>
-  <si>
-    <t>501545163042</t>
-  </si>
-  <si>
-    <t>775696629218</t>
-  </si>
-  <si>
-    <t>024734031157</t>
-  </si>
-  <si>
-    <t>409373587477</t>
-  </si>
-  <si>
-    <t>529462801173</t>
-  </si>
-  <si>
-    <t>639006959028</t>
-  </si>
-  <si>
-    <t>101152813392</t>
-  </si>
-  <si>
-    <t>664803296616</t>
-  </si>
-  <si>
-    <t>213690975475</t>
-  </si>
-  <si>
-    <t>232962687874</t>
-  </si>
-  <si>
-    <t>134409883511</t>
-  </si>
-  <si>
-    <t>262493492742</t>
-  </si>
-  <si>
-    <t>555635782712</t>
-  </si>
-  <si>
-    <t>153665810772</t>
-  </si>
-  <si>
-    <t>670333767695</t>
-  </si>
-  <si>
-    <t>545889078805</t>
-  </si>
-  <si>
-    <t>109041863122</t>
-  </si>
-  <si>
-    <t>463320731168</t>
-  </si>
-  <si>
-    <t>573305553956</t>
-  </si>
-  <si>
-    <t>979483313337</t>
-  </si>
-  <si>
-    <t>704601042073</t>
-  </si>
-  <si>
-    <t>394911173920</t>
-  </si>
-  <si>
-    <t>104381814673</t>
-  </si>
-  <si>
-    <t>869890811490</t>
-  </si>
-  <si>
-    <t>641671380746</t>
-  </si>
-  <si>
-    <t>841882896172</t>
-  </si>
-  <si>
-    <t>382100012419</t>
-  </si>
-  <si>
-    <t>651028896335</t>
-  </si>
-  <si>
-    <t>118755029658</t>
-  </si>
-  <si>
-    <t>745135933374</t>
-  </si>
-  <si>
-    <t>721802974156</t>
-  </si>
-  <si>
-    <t>453443932628</t>
-  </si>
-  <si>
-    <t>739431217355</t>
-  </si>
-  <si>
-    <t>917220768039</t>
-  </si>
-  <si>
-    <t>529393542660</t>
-  </si>
-  <si>
-    <t>934131122217</t>
-  </si>
-  <si>
-    <t>112274830637</t>
-  </si>
-  <si>
-    <t>675417166038</t>
-  </si>
-  <si>
-    <t>140714323899</t>
-  </si>
-  <si>
-    <t>380361986744</t>
-  </si>
-  <si>
-    <t>075945246898</t>
-  </si>
-  <si>
-    <t>204008805630</t>
-  </si>
-  <si>
-    <t>110836645239</t>
-  </si>
-  <si>
-    <t>069714341841</t>
-  </si>
-  <si>
-    <t>024591922173</t>
-  </si>
-  <si>
-    <t>048780402908</t>
-  </si>
-  <si>
-    <t>696180690887</t>
-  </si>
-  <si>
-    <t>427491718794</t>
-  </si>
-  <si>
-    <t>726439381493</t>
-  </si>
-  <si>
-    <t>483814932378</t>
-  </si>
-  <si>
-    <t>768336942362</t>
-  </si>
-  <si>
-    <t>951197252706</t>
-  </si>
-  <si>
-    <t>133772137512</t>
-  </si>
-  <si>
-    <t>386038380838</t>
-  </si>
-  <si>
-    <t>838996567115</t>
-  </si>
-  <si>
-    <t>551892195997</t>
-  </si>
-  <si>
-    <t>249179842900</t>
-  </si>
-  <si>
-    <t>027391928141</t>
-  </si>
-  <si>
-    <t>406968116939</t>
-  </si>
-  <si>
-    <t>471533703341</t>
-  </si>
-  <si>
-    <t>923433783591</t>
-  </si>
-  <si>
-    <t>283560412929</t>
-  </si>
-  <si>
-    <t>908573807073</t>
-  </si>
-  <si>
-    <t>859963928633</t>
-  </si>
-  <si>
-    <t>518122777036</t>
-  </si>
-  <si>
-    <t>961197516448</t>
-  </si>
-  <si>
-    <t>919720910204</t>
-  </si>
-  <si>
-    <t>378039802289</t>
-  </si>
-  <si>
-    <t>358663360173</t>
-  </si>
-  <si>
-    <t>903437275696</t>
-  </si>
-  <si>
-    <t>996070368608</t>
-  </si>
-  <si>
-    <t>526753709090</t>
-  </si>
-  <si>
-    <t>982078120878</t>
-  </si>
-  <si>
-    <t>871479838966</t>
-  </si>
-  <si>
-    <t>290954832512</t>
-  </si>
-  <si>
-    <t>434619178946</t>
-  </si>
-  <si>
-    <t>282715935261</t>
-  </si>
-  <si>
-    <t>973864436928</t>
-  </si>
-  <si>
-    <t>823119655299</t>
-  </si>
-  <si>
-    <t>298854708170</t>
-  </si>
-  <si>
-    <t>772932654316</t>
-  </si>
-  <si>
-    <t>799185054776</t>
-  </si>
-  <si>
-    <t>450400902531</t>
-  </si>
-  <si>
-    <t>767250238535</t>
-  </si>
-  <si>
-    <t>970305257941</t>
-  </si>
-  <si>
-    <t>171890551062</t>
-  </si>
-  <si>
-    <t>023878737803</t>
-  </si>
-  <si>
-    <t>830884866322</t>
-  </si>
-  <si>
-    <t>777283172734</t>
-  </si>
-  <si>
-    <t>716144541258</t>
-  </si>
-  <si>
-    <t>324687282490</t>
-  </si>
-  <si>
-    <t>959351656896</t>
-  </si>
-  <si>
-    <t>796861809871</t>
-  </si>
-  <si>
-    <t>024785320950</t>
-  </si>
-  <si>
-    <t>541427367821</t>
-  </si>
-  <si>
-    <t>689683490964</t>
-  </si>
-  <si>
-    <t>405881167038</t>
-  </si>
-  <si>
-    <t>820046622330</t>
-  </si>
-  <si>
-    <t>715842920194</t>
-  </si>
-  <si>
-    <t>959700850054</t>
-  </si>
-  <si>
-    <t>269579335076</t>
-  </si>
-  <si>
-    <t>453832860986</t>
-  </si>
-  <si>
-    <t>990287079210</t>
-  </si>
-  <si>
-    <t>212066248788</t>
-  </si>
-  <si>
-    <t>625727119233</t>
-  </si>
-  <si>
-    <t>015499730079</t>
-  </si>
-  <si>
-    <t>503253938318</t>
-  </si>
-  <si>
-    <t>192956783525</t>
-  </si>
-  <si>
-    <t>074188765012</t>
-  </si>
-  <si>
-    <t>041394838931</t>
-  </si>
-  <si>
-    <t>675388955305</t>
-  </si>
-  <si>
-    <t>479937272316</t>
-  </si>
-  <si>
-    <t>116725559845</t>
-  </si>
-  <si>
-    <t>400835298595</t>
-  </si>
-  <si>
-    <t>782095905433</t>
-  </si>
-  <si>
-    <t>505104689002</t>
-  </si>
-  <si>
-    <t>273550182077</t>
-  </si>
-  <si>
-    <t>103538937597</t>
-  </si>
-  <si>
-    <t>308630384041</t>
-  </si>
-  <si>
-    <t>983020652916</t>
-  </si>
-  <si>
-    <t>916077039554</t>
-  </si>
-  <si>
-    <t>478471059768</t>
-  </si>
-  <si>
-    <t>785313146402</t>
-  </si>
-  <si>
-    <t>257309165607</t>
-  </si>
-  <si>
-    <t>020900966643</t>
-  </si>
-  <si>
-    <t>886598120007</t>
-  </si>
-  <si>
-    <t>101577373058</t>
-  </si>
-  <si>
-    <t>467924075908</t>
-  </si>
-  <si>
-    <t>299130158240</t>
-  </si>
-  <si>
-    <t>180003995340</t>
-  </si>
-  <si>
-    <t>242019134686</t>
-  </si>
-  <si>
-    <t>830079334942</t>
-  </si>
-  <si>
-    <t>726243074403</t>
-  </si>
-  <si>
-    <t>607296214676</t>
-  </si>
-  <si>
-    <t>519012858486</t>
-  </si>
-  <si>
-    <t>742833967758</t>
-  </si>
-  <si>
-    <t>117006183554</t>
-  </si>
-  <si>
-    <t>824812157093</t>
-  </si>
-  <si>
-    <t>874547449888</t>
-  </si>
-  <si>
-    <t>937558611793</t>
-  </si>
-  <si>
-    <t>638214387441</t>
-  </si>
-  <si>
-    <t>065824901804</t>
-  </si>
-  <si>
-    <t>853924912587</t>
-  </si>
-  <si>
-    <t>710448901504</t>
-  </si>
-  <si>
-    <t>085865680372</t>
-  </si>
-  <si>
-    <t>430624365918</t>
-  </si>
-  <si>
-    <t>196139246682</t>
-  </si>
-  <si>
-    <t>778690655768</t>
-  </si>
-  <si>
-    <t>002633204590</t>
-  </si>
-  <si>
-    <t>315432272955</t>
-  </si>
-  <si>
-    <t>980072962578</t>
-  </si>
-  <si>
-    <t>784687396747</t>
-  </si>
-  <si>
-    <t>875768540892</t>
-  </si>
-  <si>
-    <t>554008422764</t>
-  </si>
-  <si>
-    <t>470885235739</t>
-  </si>
-  <si>
-    <t>434117543917</t>
-  </si>
-  <si>
-    <t>632300133687</t>
-  </si>
-  <si>
-    <t>965955272718</t>
-  </si>
-  <si>
-    <t>307362064901</t>
-  </si>
-  <si>
-    <t>095944037056</t>
-  </si>
-  <si>
-    <t>919368530794</t>
-  </si>
-  <si>
-    <t>783192687604</t>
-  </si>
-  <si>
-    <t>668050216046</t>
-  </si>
-  <si>
-    <t>210618761572</t>
-  </si>
-  <si>
-    <t>230788418877</t>
-  </si>
-  <si>
-    <t>779500626277</t>
-  </si>
-  <si>
-    <t>937368202142</t>
-  </si>
-  <si>
-    <t>914985143632</t>
-  </si>
-  <si>
-    <t>919159520130</t>
-  </si>
-  <si>
-    <t>644499417937</t>
-  </si>
-  <si>
-    <t>861546575728</t>
-  </si>
-  <si>
-    <t>185895981871</t>
-  </si>
-  <si>
-    <t>211172337837</t>
-  </si>
-  <si>
-    <t>357160076631</t>
-  </si>
-  <si>
-    <t>734177189075</t>
-  </si>
-  <si>
-    <t>218899139642</t>
-  </si>
-  <si>
-    <t>655535525812</t>
-  </si>
-  <si>
-    <t>223250302743</t>
-  </si>
-  <si>
-    <t>403910047352</t>
-  </si>
-  <si>
-    <t>034787302234</t>
-  </si>
-  <si>
-    <t>138785802503</t>
-  </si>
-  <si>
-    <t>761341304423</t>
-  </si>
-  <si>
-    <t>874270508464</t>
-  </si>
-  <si>
-    <t>718001144954</t>
-  </si>
-  <si>
-    <t>948851266198</t>
-  </si>
-  <si>
-    <t>677452040956</t>
-  </si>
-  <si>
-    <t>239847431255</t>
-  </si>
-  <si>
-    <t>212443588790</t>
-  </si>
-  <si>
-    <t>730811696284</t>
-  </si>
-  <si>
-    <t>516820923495</t>
-  </si>
-  <si>
-    <t>762635970678</t>
-  </si>
-  <si>
-    <t>485448793781</t>
-  </si>
-  <si>
-    <t>566368039073</t>
-  </si>
-  <si>
-    <t>997046174918</t>
-  </si>
-  <si>
-    <t>159812780358</t>
-  </si>
-  <si>
-    <t>717499914408</t>
-  </si>
-  <si>
-    <t>030830575781</t>
-  </si>
-  <si>
-    <t>527419865278</t>
-  </si>
-  <si>
-    <t>446010776336</t>
-  </si>
-  <si>
-    <t>959627478463</t>
-  </si>
-  <si>
-    <t>376034474252</t>
-  </si>
-  <si>
-    <t>745244044249</t>
-  </si>
-  <si>
-    <t>493326574013</t>
-  </si>
-  <si>
-    <t>774031204655</t>
-  </si>
-  <si>
-    <t>753367551705</t>
-  </si>
-  <si>
-    <t>082003081765</t>
-  </si>
-  <si>
-    <t>000540565519</t>
-  </si>
-  <si>
-    <t>701959047076</t>
-  </si>
-  <si>
-    <t>238186146004</t>
-  </si>
-  <si>
-    <t>048271254416</t>
-  </si>
-  <si>
-    <t>932535517283</t>
-  </si>
-  <si>
-    <t>187073042373</t>
-  </si>
-  <si>
-    <t>224246141823</t>
-  </si>
-  <si>
-    <t>174345247858</t>
-  </si>
-  <si>
-    <t>951941268190</t>
-  </si>
-  <si>
-    <t>709994472241</t>
-  </si>
-  <si>
-    <t>283694699644</t>
-  </si>
-  <si>
-    <t>451370354615</t>
-  </si>
-  <si>
-    <t>826430721202</t>
-  </si>
-  <si>
-    <t>106692368250</t>
-  </si>
-  <si>
-    <t>629220058656</t>
-  </si>
-  <si>
-    <t>023048557327</t>
-  </si>
-  <si>
-    <t>285214509606</t>
-  </si>
-  <si>
-    <t>763466761813</t>
-  </si>
-  <si>
-    <t>849831028001</t>
-  </si>
-  <si>
-    <t>310363013774</t>
-  </si>
-  <si>
-    <t>642955738153</t>
-  </si>
-  <si>
-    <t>870919746306</t>
-  </si>
-  <si>
-    <t>229783733936</t>
-  </si>
-  <si>
-    <t>777249035092</t>
-  </si>
-  <si>
-    <t>298405668855</t>
-  </si>
-  <si>
-    <t>050404896261</t>
-  </si>
-  <si>
-    <t>021098284426</t>
-  </si>
-  <si>
-    <t>624453270843</t>
-  </si>
-  <si>
-    <t>408432552091</t>
-  </si>
-  <si>
-    <t>623571682253</t>
-  </si>
-  <si>
-    <t>588564670683</t>
-  </si>
-  <si>
-    <t>367914268610</t>
-  </si>
-  <si>
-    <t>394661225616</t>
-  </si>
-  <si>
-    <t>339936928525</t>
-  </si>
-  <si>
-    <t>176351849436</t>
-  </si>
-  <si>
-    <t>814335512992</t>
-  </si>
-  <si>
-    <t>269944609216</t>
-  </si>
-  <si>
-    <t>595340928263</t>
-  </si>
-  <si>
-    <t>407956078475</t>
-  </si>
-  <si>
-    <t>965662540819</t>
-  </si>
-  <si>
-    <t>506923881084</t>
-  </si>
-  <si>
-    <t>692669195668</t>
-  </si>
-  <si>
-    <t>192505444521</t>
-  </si>
-  <si>
-    <t>083389688435</t>
-  </si>
-  <si>
-    <t>729897642853</t>
-  </si>
-  <si>
-    <t>126293695456</t>
-  </si>
-  <si>
-    <t>708198545420</t>
-  </si>
-  <si>
-    <t>377032838777</t>
-  </si>
-  <si>
-    <t>131302290997</t>
-  </si>
-  <si>
-    <t>415671794242</t>
-  </si>
-  <si>
-    <t>139227201548</t>
-  </si>
-  <si>
-    <t>584031426043</t>
-  </si>
-  <si>
-    <t>797640279123</t>
-  </si>
-  <si>
-    <t>664775283122</t>
-  </si>
-  <si>
-    <t>211226366363</t>
-  </si>
-  <si>
-    <t>849672851635</t>
-  </si>
-  <si>
-    <t>128510465511</t>
-  </si>
-  <si>
-    <t>025417552532</t>
-  </si>
-  <si>
-    <t>402630628418</t>
-  </si>
-  <si>
-    <t>209184849039</t>
-  </si>
-  <si>
-    <t>536714565874</t>
-  </si>
-  <si>
-    <t>177795089397</t>
-  </si>
-  <si>
-    <t>370743489613</t>
-  </si>
-  <si>
-    <t>823894401505</t>
-  </si>
-  <si>
-    <t>733930188458</t>
-  </si>
-  <si>
-    <t>529880974761</t>
-  </si>
-  <si>
-    <t>795489432307</t>
-  </si>
-  <si>
-    <t>422526534171</t>
-  </si>
-  <si>
-    <t>605714236976</t>
-  </si>
-  <si>
-    <t>133651232484</t>
-  </si>
-  <si>
-    <t>710509660098</t>
-  </si>
-  <si>
-    <t>574750730984</t>
-  </si>
-  <si>
-    <t>873793163833</t>
-  </si>
-  <si>
-    <t>885877362545</t>
-  </si>
-  <si>
-    <t>303957530393</t>
-  </si>
-  <si>
-    <t>638704456651</t>
-  </si>
-  <si>
-    <t>612263351355</t>
-  </si>
-  <si>
-    <t>868154537226</t>
-  </si>
-  <si>
-    <t>319346610908</t>
-  </si>
-  <si>
-    <t>624827307809</t>
-  </si>
-  <si>
-    <t>702871424696</t>
-  </si>
-  <si>
-    <t>456352952605</t>
-  </si>
-  <si>
-    <t>893835228850</t>
+    <t>039115569810</t>
+  </si>
+  <si>
+    <t>661</t>
+  </si>
+  <si>
+    <t>620160127607</t>
+  </si>
+  <si>
+    <t>643076748863</t>
+  </si>
+  <si>
+    <t>014299417087</t>
+  </si>
+  <si>
+    <t>230734334348</t>
+  </si>
+  <si>
+    <t>425065949295</t>
+  </si>
+  <si>
+    <t>442639865214</t>
+  </si>
+  <si>
+    <t>821210172356</t>
+  </si>
+  <si>
+    <t>909729305604</t>
+  </si>
+  <si>
+    <t>823157130944</t>
+  </si>
+  <si>
+    <t>279908509703</t>
+  </si>
+  <si>
+    <t>175204920928</t>
+  </si>
+  <si>
+    <t>073062832282</t>
+  </si>
+  <si>
+    <t>582665528476</t>
+  </si>
+  <si>
+    <t>319534907127</t>
+  </si>
+  <si>
+    <t>245769043332</t>
+  </si>
+  <si>
+    <t>755227506860</t>
+  </si>
+  <si>
+    <t>514484040493</t>
+  </si>
+  <si>
+    <t>748452311075</t>
+  </si>
+  <si>
+    <t>147292177736</t>
+  </si>
+  <si>
+    <t>874322509714</t>
+  </si>
+  <si>
+    <t>588785036738</t>
+  </si>
+  <si>
+    <t>996592913384</t>
+  </si>
+  <si>
+    <t>263120787528</t>
+  </si>
+  <si>
+    <t>250770016397</t>
+  </si>
+  <si>
+    <t>052916581050</t>
+  </si>
+  <si>
+    <t>144515419100</t>
+  </si>
+  <si>
+    <t>250166808376</t>
+  </si>
+  <si>
+    <t>218614342471</t>
+  </si>
+  <si>
+    <t>034924712580</t>
+  </si>
+  <si>
+    <t>414189853806</t>
+  </si>
+  <si>
+    <t>970341896396</t>
+  </si>
+  <si>
+    <t>596253668270</t>
+  </si>
+  <si>
+    <t>604536843493</t>
+  </si>
+  <si>
+    <t>119852639443</t>
+  </si>
+  <si>
+    <t>650246693229</t>
+  </si>
+  <si>
+    <t>981335359595</t>
+  </si>
+  <si>
+    <t>096662635511</t>
+  </si>
+  <si>
+    <t>212253540832</t>
+  </si>
+  <si>
+    <t>625690659095</t>
+  </si>
+  <si>
+    <t>970827899134</t>
+  </si>
+  <si>
+    <t>943832601278</t>
+  </si>
+  <si>
+    <t>577161902558</t>
+  </si>
+  <si>
+    <t>395590989439</t>
+  </si>
+  <si>
+    <t>572164041233</t>
+  </si>
+  <si>
+    <t>263688052570</t>
+  </si>
+  <si>
+    <t>234920315763</t>
+  </si>
+  <si>
+    <t>053716318967</t>
+  </si>
+  <si>
+    <t>663888910277</t>
+  </si>
+  <si>
+    <t>584180605410</t>
+  </si>
+  <si>
+    <t>131065701287</t>
+  </si>
+  <si>
+    <t>861130916884</t>
+  </si>
+  <si>
+    <t>796998723010</t>
+  </si>
+  <si>
+    <t>646226860514</t>
+  </si>
+  <si>
+    <t>665180511214</t>
+  </si>
+  <si>
+    <t>098143877441</t>
+  </si>
+  <si>
+    <t>426019596079</t>
+  </si>
+  <si>
+    <t>643720713001</t>
+  </si>
+  <si>
+    <t>819086228280</t>
+  </si>
+  <si>
+    <t>250109516845</t>
+  </si>
+  <si>
+    <t>805499248836</t>
+  </si>
+  <si>
+    <t>279156224329</t>
+  </si>
+  <si>
+    <t>854961585532</t>
+  </si>
+  <si>
+    <t>894149003844</t>
+  </si>
+  <si>
+    <t>487455304651</t>
+  </si>
+  <si>
+    <t>563293681247</t>
+  </si>
+  <si>
+    <t>396822694369</t>
+  </si>
+  <si>
+    <t>773530278961</t>
+  </si>
+  <si>
+    <t>041381565943</t>
+  </si>
+  <si>
+    <t>531249141408</t>
+  </si>
+  <si>
+    <t>552219280076</t>
+  </si>
+  <si>
+    <t>702943006347</t>
+  </si>
+  <si>
+    <t>241572944654</t>
+  </si>
+  <si>
+    <t>653812224222</t>
+  </si>
+  <si>
+    <t>277513356036</t>
+  </si>
+  <si>
+    <t>091487785741</t>
+  </si>
+  <si>
+    <t>346701415628</t>
+  </si>
+  <si>
+    <t>803175723022</t>
+  </si>
+  <si>
+    <t>908253091114</t>
+  </si>
+  <si>
+    <t>755887011597</t>
+  </si>
+  <si>
+    <t>025726843815</t>
+  </si>
+  <si>
+    <t>390467262891</t>
+  </si>
+  <si>
+    <t>698513710516</t>
+  </si>
+  <si>
+    <t>210225792096</t>
+  </si>
+  <si>
+    <t>027089092114</t>
+  </si>
+  <si>
+    <t>236081354779</t>
+  </si>
+  <si>
+    <t>031095037040</t>
+  </si>
+  <si>
+    <t>475238809382</t>
+  </si>
+  <si>
+    <t>375695730319</t>
+  </si>
+  <si>
+    <t>034116501112</t>
+  </si>
+  <si>
+    <t>539701831198</t>
+  </si>
+  <si>
+    <t>977418648860</t>
+  </si>
+  <si>
+    <t>522096545218</t>
+  </si>
+  <si>
+    <t>145122332355</t>
+  </si>
+  <si>
+    <t>027004432467</t>
+  </si>
+  <si>
+    <t>051082712360</t>
+  </si>
+  <si>
+    <t>107983374271</t>
+  </si>
+  <si>
+    <t>950555922941</t>
+  </si>
+  <si>
+    <t>402353158118</t>
+  </si>
+  <si>
+    <t>624523215289</t>
+  </si>
+  <si>
+    <t>039826392824</t>
+  </si>
+  <si>
+    <t>663351577324</t>
+  </si>
+  <si>
+    <t>012644982486</t>
+  </si>
+  <si>
+    <t>295925841014</t>
+  </si>
+  <si>
+    <t>725225980601</t>
+  </si>
+  <si>
+    <t>762184971138</t>
+  </si>
+  <si>
+    <t>918879926148</t>
+  </si>
+  <si>
+    <t>323762289750</t>
+  </si>
+  <si>
+    <t>821774640185</t>
+  </si>
+  <si>
+    <t>208575422759</t>
+  </si>
+  <si>
+    <t>092249060904</t>
+  </si>
+  <si>
+    <t>876040921209</t>
+  </si>
+  <si>
+    <t>649631514161</t>
+  </si>
+  <si>
+    <t>661888781378</t>
+  </si>
+  <si>
+    <t>440433199188</t>
+  </si>
+  <si>
+    <t>278812186425</t>
+  </si>
+  <si>
+    <t>325295136715</t>
+  </si>
+  <si>
+    <t>944402409944</t>
+  </si>
+  <si>
+    <t>127143604068</t>
+  </si>
+  <si>
+    <t>424994102575</t>
+  </si>
+  <si>
+    <t>582157245460</t>
+  </si>
+  <si>
+    <t>195758177378</t>
+  </si>
+  <si>
+    <t>850822333473</t>
+  </si>
+  <si>
+    <t>514825287460</t>
+  </si>
+  <si>
+    <t>524667680870</t>
+  </si>
+  <si>
+    <t>611151000079</t>
+  </si>
+  <si>
+    <t>798363936543</t>
+  </si>
+  <si>
+    <t>458310604356</t>
+  </si>
+  <si>
+    <t>425981845560</t>
+  </si>
+  <si>
+    <t>014727677685</t>
+  </si>
+  <si>
+    <t>929925092184</t>
+  </si>
+  <si>
+    <t>667449437627</t>
+  </si>
+  <si>
+    <t>463797731523</t>
+  </si>
+  <si>
+    <t>886438632489</t>
+  </si>
+  <si>
+    <t>554714269509</t>
+  </si>
+  <si>
+    <t>583361023840</t>
+  </si>
+  <si>
+    <t>881852990252</t>
+  </si>
+  <si>
+    <t>054668491179</t>
+  </si>
+  <si>
+    <t>086955035645</t>
+  </si>
+  <si>
+    <t>245159474413</t>
+  </si>
+  <si>
+    <t>811969398426</t>
+  </si>
+  <si>
+    <t>525272423914</t>
+  </si>
+  <si>
+    <t>458920638555</t>
+  </si>
+  <si>
+    <t>895046587528</t>
+  </si>
+  <si>
+    <t>072374533316</t>
+  </si>
+  <si>
+    <t>304716643275</t>
+  </si>
+  <si>
+    <t>469207750058</t>
+  </si>
+  <si>
+    <t>298013853796</t>
+  </si>
+  <si>
+    <t>282718551402</t>
+  </si>
+  <si>
+    <t>665227625969</t>
+  </si>
+  <si>
+    <t>628019185534</t>
+  </si>
+  <si>
+    <t>629300446424</t>
+  </si>
+  <si>
+    <t>767090977916</t>
+  </si>
+  <si>
+    <t>551886008840</t>
+  </si>
+  <si>
+    <t>844502949893</t>
+  </si>
+  <si>
+    <t>432361234757</t>
+  </si>
+  <si>
+    <t>789562191371</t>
+  </si>
+  <si>
+    <t>945204637714</t>
+  </si>
+  <si>
+    <t>563497930775</t>
+  </si>
+  <si>
+    <t>388175711453</t>
+  </si>
+  <si>
+    <t>522355840708</t>
+  </si>
+  <si>
+    <t>991142701489</t>
+  </si>
+  <si>
+    <t>371877098958</t>
+  </si>
+  <si>
+    <t>484123184595</t>
+  </si>
+  <si>
+    <t>690016901422</t>
+  </si>
+  <si>
+    <t>985594238884</t>
+  </si>
+  <si>
+    <t>145764126822</t>
+  </si>
+  <si>
+    <t>397136695067</t>
+  </si>
+  <si>
+    <t>615121245410</t>
+  </si>
+  <si>
+    <t>183132026019</t>
+  </si>
+  <si>
+    <t>812669240430</t>
+  </si>
+  <si>
+    <t>440894350989</t>
+  </si>
+  <si>
+    <t>494283461844</t>
+  </si>
+  <si>
+    <t>040437804523</t>
+  </si>
+  <si>
+    <t>352438318934</t>
+  </si>
+  <si>
+    <t>037872833852</t>
+  </si>
+  <si>
+    <t>157676201780</t>
+  </si>
+  <si>
+    <t>102981748849</t>
+  </si>
+  <si>
+    <t>836251215863</t>
+  </si>
+  <si>
+    <t>494709456452</t>
+  </si>
+  <si>
+    <t>755004704128</t>
+  </si>
+  <si>
+    <t>743027148075</t>
+  </si>
+  <si>
+    <t>488527881679</t>
+  </si>
+  <si>
+    <t>307009100998</t>
+  </si>
+  <si>
+    <t>979270662682</t>
+  </si>
+  <si>
+    <t>203256338150</t>
+  </si>
+  <si>
+    <t>855727555145</t>
+  </si>
+  <si>
+    <t>927141147484</t>
+  </si>
+  <si>
+    <t>818258507200</t>
+  </si>
+  <si>
+    <t>475451994031</t>
+  </si>
+  <si>
+    <t>502996149103</t>
+  </si>
+  <si>
+    <t>654591230654</t>
+  </si>
+  <si>
+    <t>530826966563</t>
+  </si>
+  <si>
+    <t>591831583134</t>
+  </si>
+  <si>
+    <t>996873237659</t>
+  </si>
+  <si>
+    <t>495698530095</t>
+  </si>
+  <si>
+    <t>263864324891</t>
+  </si>
+  <si>
+    <t>408891031937</t>
+  </si>
+  <si>
+    <t>982443410167</t>
+  </si>
+  <si>
+    <t>198379868723</t>
+  </si>
+  <si>
+    <t>652338819288</t>
+  </si>
+  <si>
+    <t>195005441641</t>
+  </si>
+  <si>
+    <t>266948833646</t>
+  </si>
+  <si>
+    <t>113953946546</t>
+  </si>
+  <si>
+    <t>357244102804</t>
+  </si>
+  <si>
+    <t>573490693400</t>
+  </si>
+  <si>
+    <t>355088889023</t>
+  </si>
+  <si>
+    <t>629356430780</t>
+  </si>
+  <si>
+    <t>279897419121</t>
+  </si>
+  <si>
+    <t>588671257487</t>
+  </si>
+  <si>
+    <t>910535498565</t>
+  </si>
+  <si>
+    <t>321424250510</t>
+  </si>
+  <si>
+    <t>098300597609</t>
+  </si>
+  <si>
+    <t>745752990079</t>
+  </si>
+  <si>
+    <t>095993445363</t>
+  </si>
+  <si>
+    <t>203126929517</t>
+  </si>
+  <si>
+    <t>217673852353</t>
+  </si>
+  <si>
+    <t>618517885285</t>
+  </si>
+  <si>
+    <t>572006200291</t>
+  </si>
+  <si>
+    <t>345055798972</t>
+  </si>
+  <si>
+    <t>060990634280</t>
+  </si>
+  <si>
+    <t>894995597010</t>
+  </si>
+  <si>
+    <t>917203711157</t>
+  </si>
+  <si>
+    <t>647834396516</t>
+  </si>
+  <si>
+    <t>941366001225</t>
+  </si>
+  <si>
+    <t>416960873577</t>
+  </si>
+  <si>
+    <t>524161613019</t>
+  </si>
+  <si>
+    <t>245270763123</t>
+  </si>
+  <si>
+    <t>139890925779</t>
+  </si>
+  <si>
+    <t>419268501611</t>
+  </si>
+  <si>
+    <t>479233229620</t>
+  </si>
+  <si>
+    <t>435959721079</t>
+  </si>
+  <si>
+    <t>974012936477</t>
+  </si>
+  <si>
+    <t>267079824606</t>
+  </si>
+  <si>
+    <t>160799841353</t>
+  </si>
+  <si>
+    <t>296131116952</t>
+  </si>
+  <si>
+    <t>468167727597</t>
+  </si>
+  <si>
+    <t>106384633707</t>
+  </si>
+  <si>
+    <t>244588146728</t>
+  </si>
+  <si>
+    <t>907727655261</t>
+  </si>
+  <si>
+    <t>909646671656</t>
+  </si>
+  <si>
+    <t>802248116249</t>
+  </si>
+  <si>
+    <t>235170899610</t>
+  </si>
+  <si>
+    <t>502185672388</t>
+  </si>
+  <si>
+    <t>633638416440</t>
+  </si>
+  <si>
+    <t>195213578898</t>
+  </si>
+  <si>
+    <t>962853315934</t>
+  </si>
+  <si>
+    <t>541060919084</t>
+  </si>
+  <si>
+    <t>204920699582</t>
+  </si>
+  <si>
+    <t>474687255192</t>
+  </si>
+  <si>
+    <t>670678232235</t>
+  </si>
+  <si>
+    <t>416716217335</t>
+  </si>
+  <si>
+    <t>856013233244</t>
+  </si>
+  <si>
+    <t>305800019680</t>
+  </si>
+  <si>
+    <t>300091001119</t>
+  </si>
+  <si>
+    <t>042123549022</t>
+  </si>
+  <si>
+    <t>911826287028</t>
+  </si>
+  <si>
+    <t>385230772616</t>
+  </si>
+  <si>
+    <t>693656394540</t>
+  </si>
+  <si>
+    <t>519321623802</t>
+  </si>
+  <si>
+    <t>243258878725</t>
+  </si>
+  <si>
+    <t>381113122791</t>
+  </si>
+  <si>
+    <t>338329699538</t>
+  </si>
+  <si>
+    <t>190291196812</t>
+  </si>
+  <si>
+    <t>101472731178</t>
+  </si>
+  <si>
+    <t>417328061338</t>
+  </si>
+  <si>
+    <t>698369238136</t>
+  </si>
+  <si>
+    <t>664555589289</t>
+  </si>
+  <si>
+    <t>697751250871</t>
+  </si>
+  <si>
+    <t>410415192665</t>
+  </si>
+  <si>
+    <t>453436200871</t>
+  </si>
+  <si>
+    <t>921096784507</t>
+  </si>
+  <si>
+    <t>500905115988</t>
+  </si>
+  <si>
+    <t>234173637602</t>
+  </si>
+  <si>
+    <t>800465383927</t>
+  </si>
+  <si>
+    <t>546638590163</t>
+  </si>
+  <si>
+    <t>644321740770</t>
+  </si>
+  <si>
+    <t>367007212469</t>
+  </si>
+  <si>
+    <t>608730421315</t>
+  </si>
+  <si>
+    <t>443297752738</t>
+  </si>
+  <si>
+    <t>418761308533</t>
+  </si>
+  <si>
+    <t>431488989388</t>
+  </si>
+  <si>
+    <t>823909417371</t>
+  </si>
+  <si>
+    <t>261776378820</t>
+  </si>
+  <si>
+    <t>297740611987</t>
+  </si>
+  <si>
+    <t>982018141902</t>
+  </si>
+  <si>
+    <t>354445794599</t>
+  </si>
+  <si>
+    <t>074827590199</t>
+  </si>
+  <si>
+    <t>300092406130</t>
+  </si>
+  <si>
+    <t>898248249628</t>
+  </si>
+  <si>
+    <t>762145687389</t>
+  </si>
+  <si>
+    <t>350758949055</t>
+  </si>
+  <si>
+    <t>745196631561</t>
+  </si>
+  <si>
+    <t>495141433060</t>
+  </si>
+  <si>
+    <t>360820207997</t>
+  </si>
+  <si>
+    <t>045101669962</t>
+  </si>
+  <si>
+    <t>671970439097</t>
+  </si>
+  <si>
+    <t>057008693518</t>
+  </si>
+  <si>
+    <t>506806447538</t>
+  </si>
+  <si>
+    <t>614074978437</t>
+  </si>
+  <si>
+    <t>733648024301</t>
+  </si>
+  <si>
+    <t>726722132721</t>
+  </si>
+  <si>
+    <t>868286125027</t>
+  </si>
+  <si>
+    <t>833876204165</t>
+  </si>
+  <si>
+    <t>457014266126</t>
+  </si>
+  <si>
+    <t>692468292245</t>
+  </si>
+  <si>
+    <t>960475257430</t>
+  </si>
+  <si>
+    <t>103618244252</t>
+  </si>
+  <si>
+    <t>943435165855</t>
+  </si>
+  <si>
+    <t>823266320161</t>
+  </si>
+  <si>
+    <t>493089174899</t>
+  </si>
+  <si>
+    <t>672986731530</t>
+  </si>
+  <si>
+    <t>457464450746</t>
+  </si>
+  <si>
+    <t>431480755437</t>
+  </si>
+  <si>
+    <t>787556080335</t>
+  </si>
+  <si>
+    <t>122514405571</t>
+  </si>
+  <si>
+    <t>278183288003</t>
+  </si>
+  <si>
+    <t>533121739038</t>
+  </si>
+  <si>
+    <t>658520711375</t>
+  </si>
+  <si>
+    <t>583308830116</t>
+  </si>
+  <si>
+    <t>166610522756</t>
+  </si>
+  <si>
+    <t>374102152501</t>
+  </si>
+  <si>
+    <t>986232061132</t>
+  </si>
+  <si>
+    <t>681972712071</t>
+  </si>
+  <si>
+    <t>017253319382</t>
+  </si>
+  <si>
+    <t>223137278414</t>
+  </si>
+  <si>
+    <t>323694855482</t>
+  </si>
+  <si>
+    <t>061940067840</t>
+  </si>
+  <si>
+    <t>493038653137</t>
+  </si>
+  <si>
+    <t>279897701505</t>
+  </si>
+  <si>
+    <t>726630986630</t>
+  </si>
+  <si>
+    <t>195716506759</t>
+  </si>
+  <si>
+    <t>118771256698</t>
+  </si>
+  <si>
+    <t>470719467914</t>
+  </si>
+  <si>
+    <t>684439128445</t>
+  </si>
+  <si>
+    <t>351238049645</t>
+  </si>
+  <si>
+    <t>132557527443</t>
+  </si>
+  <si>
+    <t>405618138416</t>
+  </si>
+  <si>
+    <t>397514993932</t>
+  </si>
+  <si>
+    <t>096787095025</t>
+  </si>
+  <si>
+    <t>077711034522</t>
+  </si>
+  <si>
+    <t>908132246672</t>
+  </si>
+  <si>
+    <t>730263475228</t>
+  </si>
+  <si>
+    <t>794751734694</t>
+  </si>
+  <si>
+    <t>766732199597</t>
+  </si>
+  <si>
+    <t>980769853683</t>
+  </si>
+  <si>
+    <t>187605033478</t>
+  </si>
+  <si>
+    <t>471360173383</t>
+  </si>
+  <si>
+    <t>067690119617</t>
+  </si>
+  <si>
+    <t>850723880972</t>
+  </si>
+  <si>
+    <t>136162941149</t>
+  </si>
+  <si>
+    <t>766842213808</t>
+  </si>
+  <si>
+    <t>023050908183</t>
+  </si>
+  <si>
+    <t>644630987399</t>
+  </si>
+  <si>
+    <t>594095280065</t>
+  </si>
+  <si>
+    <t>286366040764</t>
+  </si>
+  <si>
+    <t>291355067361</t>
+  </si>
+  <si>
+    <t>506448021449</t>
+  </si>
+  <si>
+    <t>377466780553</t>
+  </si>
+  <si>
+    <t>899293293072</t>
+  </si>
+  <si>
+    <t>454611223808</t>
+  </si>
+  <si>
+    <t>013669511502</t>
+  </si>
+  <si>
+    <t>314002471878</t>
+  </si>
+  <si>
+    <t>715839835585</t>
+  </si>
+  <si>
+    <t>802442261460</t>
+  </si>
+  <si>
+    <t>939025519243</t>
+  </si>
+  <si>
+    <t>588065142449</t>
+  </si>
+  <si>
+    <t>473938735257</t>
+  </si>
+  <si>
+    <t>407389263574</t>
+  </si>
+  <si>
+    <t>210415150001</t>
+  </si>
+  <si>
+    <t>552092857990</t>
+  </si>
+  <si>
+    <t>778082929259</t>
+  </si>
+  <si>
+    <t>096799894016</t>
+  </si>
+  <si>
+    <t>469464157800</t>
+  </si>
+  <si>
+    <t>990767516645</t>
+  </si>
+  <si>
+    <t>945013845094</t>
+  </si>
+  <si>
+    <t>852993434386</t>
+  </si>
+  <si>
+    <t>055488820553</t>
+  </si>
+  <si>
+    <t>478508661653</t>
+  </si>
+  <si>
+    <t>060937638596</t>
+  </si>
+  <si>
+    <t>566440242507</t>
+  </si>
+  <si>
+    <t>143381070724</t>
+  </si>
+  <si>
+    <t>870972267838</t>
+  </si>
+  <si>
+    <t>631562083298</t>
+  </si>
+  <si>
+    <t>899255297331</t>
+  </si>
+  <si>
+    <t>263171750456</t>
+  </si>
+  <si>
+    <t>338782285708</t>
+  </si>
+  <si>
+    <t>721029522534</t>
+  </si>
+  <si>
+    <t>370165267392</t>
+  </si>
+  <si>
+    <t>033846833269</t>
+  </si>
+  <si>
+    <t>362768922677</t>
+  </si>
+  <si>
+    <t>792407033575</t>
+  </si>
+  <si>
+    <t>214254128288</t>
+  </si>
+  <si>
+    <t>411656944495</t>
+  </si>
+  <si>
+    <t>720392027361</t>
+  </si>
+  <si>
+    <t>146118882142</t>
+  </si>
+  <si>
+    <t>127540916329</t>
+  </si>
+  <si>
+    <t>814692123568</t>
+  </si>
+  <si>
+    <t>327216875925</t>
+  </si>
+  <si>
+    <t>244134337443</t>
+  </si>
+  <si>
+    <t>090736666151</t>
+  </si>
+  <si>
+    <t>103198540603</t>
+  </si>
+  <si>
+    <t>754429328657</t>
+  </si>
+  <si>
+    <t>814046914013</t>
+  </si>
+  <si>
+    <t>223824978034</t>
+  </si>
+  <si>
+    <t>608294797014</t>
+  </si>
+  <si>
+    <t>312667076078</t>
+  </si>
+  <si>
+    <t>934505734561</t>
+  </si>
+  <si>
+    <t>017540689149</t>
+  </si>
+  <si>
+    <t>949064105187</t>
+  </si>
+  <si>
+    <t>248282501282</t>
+  </si>
+  <si>
+    <t>871910853894</t>
+  </si>
+  <si>
+    <t>467417835032</t>
+  </si>
+  <si>
+    <t>716827613312</t>
+  </si>
+  <si>
+    <t>117419703741</t>
+  </si>
+  <si>
+    <t>530308721743</t>
+  </si>
+  <si>
+    <t>745566326860</t>
+  </si>
+  <si>
+    <t>790645216279</t>
+  </si>
+  <si>
+    <t>371658785422</t>
+  </si>
+  <si>
+    <t>828646824605</t>
+  </si>
+  <si>
+    <t>140785481470</t>
+  </si>
+  <si>
+    <t>640542708088</t>
+  </si>
+  <si>
+    <t>052916906165</t>
+  </si>
+  <si>
+    <t>062074295529</t>
+  </si>
+  <si>
+    <t>026561610911</t>
+  </si>
+  <si>
+    <t>614337112839</t>
+  </si>
+  <si>
+    <t>597790312022</t>
+  </si>
+  <si>
+    <t>757816051461</t>
+  </si>
+  <si>
+    <t>311009201771</t>
+  </si>
+  <si>
+    <t>560838889933</t>
+  </si>
+  <si>
+    <t>182623155689</t>
+  </si>
+  <si>
+    <t>856325997994</t>
+  </si>
+  <si>
+    <t>206717076732</t>
+  </si>
+  <si>
+    <t>556019829784</t>
+  </si>
+  <si>
+    <t>320983170200</t>
+  </si>
+  <si>
+    <t>962550102984</t>
+  </si>
+  <si>
+    <t>760860528283</t>
+  </si>
+  <si>
+    <t>030273806994</t>
+  </si>
+  <si>
+    <t>706027556187</t>
+  </si>
+  <si>
+    <t>739833517115</t>
+  </si>
+  <si>
+    <t>862819688916</t>
+  </si>
+  <si>
+    <t>213962636683</t>
+  </si>
+  <si>
+    <t>920449917316</t>
+  </si>
+  <si>
+    <t>368569663967</t>
+  </si>
+  <si>
+    <t>887113382819</t>
+  </si>
+  <si>
+    <t>616173705430</t>
+  </si>
+  <si>
+    <t>187188002916</t>
+  </si>
+  <si>
+    <t>757646636973</t>
+  </si>
+  <si>
+    <t>021841519558</t>
+  </si>
+  <si>
+    <t>347965150072</t>
+  </si>
+  <si>
+    <t>839484710019</t>
+  </si>
+  <si>
+    <t>734290765948</t>
+  </si>
+  <si>
+    <t>448902127191</t>
+  </si>
+  <si>
+    <t>157724903484</t>
+  </si>
+  <si>
+    <t>796505017981</t>
+  </si>
+  <si>
+    <t>266227284370</t>
+  </si>
+  <si>
+    <t>059642063878</t>
+  </si>
+  <si>
+    <t>244453568390</t>
+  </si>
+  <si>
+    <t>767959592972</t>
+  </si>
+  <si>
+    <t>351372261035</t>
+  </si>
+  <si>
+    <t>809495131697</t>
+  </si>
+  <si>
+    <t>235402872613</t>
+  </si>
+  <si>
+    <t>107290020647</t>
+  </si>
+  <si>
+    <t>378709599898</t>
+  </si>
+  <si>
+    <t>151605557371</t>
+  </si>
+  <si>
+    <t>470712054778</t>
+  </si>
+  <si>
+    <t>888172063678</t>
+  </si>
+  <si>
+    <t>302747242343</t>
+  </si>
+  <si>
+    <t>198630010231</t>
+  </si>
+  <si>
+    <t>103226002370</t>
+  </si>
+  <si>
+    <t>504958172586</t>
+  </si>
+  <si>
+    <t>008881919995</t>
+  </si>
+  <si>
+    <t>208367645377</t>
+  </si>
+  <si>
+    <t>628425976691</t>
+  </si>
+  <si>
+    <t>203432133655</t>
+  </si>
+  <si>
+    <t>446417709373</t>
+  </si>
+  <si>
+    <t>628457429554</t>
+  </si>
+  <si>
+    <t>619525546501</t>
+  </si>
+  <si>
+    <t>393619605560</t>
+  </si>
+  <si>
+    <t>548169883122</t>
+  </si>
+  <si>
+    <t>154910855236</t>
+  </si>
+  <si>
+    <t>305533047354</t>
+  </si>
+  <si>
+    <t>859480229937</t>
+  </si>
+  <si>
+    <t>546572380819</t>
+  </si>
+  <si>
+    <t>035038138815</t>
+  </si>
+  <si>
+    <t>232846795001</t>
+  </si>
+  <si>
+    <t>853195264149</t>
+  </si>
+  <si>
+    <t>856154334972</t>
+  </si>
+  <si>
+    <t>321194903244</t>
+  </si>
+  <si>
+    <t>952424639366</t>
+  </si>
+  <si>
+    <t>155347333156</t>
+  </si>
+  <si>
+    <t>342528626682</t>
+  </si>
+  <si>
+    <t>309990480873</t>
+  </si>
+  <si>
+    <t>696983346751</t>
+  </si>
+  <si>
+    <t>119728041598</t>
+  </si>
+  <si>
+    <t>999326578878</t>
+  </si>
+  <si>
+    <t>926183398206</t>
+  </si>
+  <si>
+    <t>620790364862</t>
+  </si>
+  <si>
+    <t>795318442708</t>
+  </si>
+  <si>
+    <t>298197775987</t>
   </si>
 </sst>
 </file>

--- a/uploadfile.xlsx
+++ b/uploadfile.xlsx
@@ -20,1507 +20,1507 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>039115569810</t>
-  </si>
-  <si>
-    <t>661</t>
-  </si>
-  <si>
-    <t>620160127607</t>
-  </si>
-  <si>
-    <t>643076748863</t>
-  </si>
-  <si>
-    <t>014299417087</t>
-  </si>
-  <si>
-    <t>230734334348</t>
-  </si>
-  <si>
-    <t>425065949295</t>
-  </si>
-  <si>
-    <t>442639865214</t>
-  </si>
-  <si>
-    <t>821210172356</t>
-  </si>
-  <si>
-    <t>909729305604</t>
-  </si>
-  <si>
-    <t>823157130944</t>
-  </si>
-  <si>
-    <t>279908509703</t>
-  </si>
-  <si>
-    <t>175204920928</t>
-  </si>
-  <si>
-    <t>073062832282</t>
-  </si>
-  <si>
-    <t>582665528476</t>
-  </si>
-  <si>
-    <t>319534907127</t>
-  </si>
-  <si>
-    <t>245769043332</t>
-  </si>
-  <si>
-    <t>755227506860</t>
-  </si>
-  <si>
-    <t>514484040493</t>
-  </si>
-  <si>
-    <t>748452311075</t>
-  </si>
-  <si>
-    <t>147292177736</t>
-  </si>
-  <si>
-    <t>874322509714</t>
-  </si>
-  <si>
-    <t>588785036738</t>
-  </si>
-  <si>
-    <t>996592913384</t>
-  </si>
-  <si>
-    <t>263120787528</t>
-  </si>
-  <si>
-    <t>250770016397</t>
-  </si>
-  <si>
-    <t>052916581050</t>
-  </si>
-  <si>
-    <t>144515419100</t>
-  </si>
-  <si>
-    <t>250166808376</t>
-  </si>
-  <si>
-    <t>218614342471</t>
-  </si>
-  <si>
-    <t>034924712580</t>
-  </si>
-  <si>
-    <t>414189853806</t>
-  </si>
-  <si>
-    <t>970341896396</t>
-  </si>
-  <si>
-    <t>596253668270</t>
-  </si>
-  <si>
-    <t>604536843493</t>
-  </si>
-  <si>
-    <t>119852639443</t>
-  </si>
-  <si>
-    <t>650246693229</t>
-  </si>
-  <si>
-    <t>981335359595</t>
-  </si>
-  <si>
-    <t>096662635511</t>
-  </si>
-  <si>
-    <t>212253540832</t>
-  </si>
-  <si>
-    <t>625690659095</t>
-  </si>
-  <si>
-    <t>970827899134</t>
-  </si>
-  <si>
-    <t>943832601278</t>
-  </si>
-  <si>
-    <t>577161902558</t>
-  </si>
-  <si>
-    <t>395590989439</t>
-  </si>
-  <si>
-    <t>572164041233</t>
-  </si>
-  <si>
-    <t>263688052570</t>
-  </si>
-  <si>
-    <t>234920315763</t>
-  </si>
-  <si>
-    <t>053716318967</t>
-  </si>
-  <si>
-    <t>663888910277</t>
-  </si>
-  <si>
-    <t>584180605410</t>
-  </si>
-  <si>
-    <t>131065701287</t>
-  </si>
-  <si>
-    <t>861130916884</t>
-  </si>
-  <si>
-    <t>796998723010</t>
-  </si>
-  <si>
-    <t>646226860514</t>
-  </si>
-  <si>
-    <t>665180511214</t>
-  </si>
-  <si>
-    <t>098143877441</t>
-  </si>
-  <si>
-    <t>426019596079</t>
-  </si>
-  <si>
-    <t>643720713001</t>
-  </si>
-  <si>
-    <t>819086228280</t>
-  </si>
-  <si>
-    <t>250109516845</t>
-  </si>
-  <si>
-    <t>805499248836</t>
-  </si>
-  <si>
-    <t>279156224329</t>
-  </si>
-  <si>
-    <t>854961585532</t>
-  </si>
-  <si>
-    <t>894149003844</t>
-  </si>
-  <si>
-    <t>487455304651</t>
-  </si>
-  <si>
-    <t>563293681247</t>
-  </si>
-  <si>
-    <t>396822694369</t>
-  </si>
-  <si>
-    <t>773530278961</t>
-  </si>
-  <si>
-    <t>041381565943</t>
-  </si>
-  <si>
-    <t>531249141408</t>
-  </si>
-  <si>
-    <t>552219280076</t>
-  </si>
-  <si>
-    <t>702943006347</t>
-  </si>
-  <si>
-    <t>241572944654</t>
-  </si>
-  <si>
-    <t>653812224222</t>
-  </si>
-  <si>
-    <t>277513356036</t>
-  </si>
-  <si>
-    <t>091487785741</t>
-  </si>
-  <si>
-    <t>346701415628</t>
-  </si>
-  <si>
-    <t>803175723022</t>
-  </si>
-  <si>
-    <t>908253091114</t>
-  </si>
-  <si>
-    <t>755887011597</t>
-  </si>
-  <si>
-    <t>025726843815</t>
-  </si>
-  <si>
-    <t>390467262891</t>
-  </si>
-  <si>
-    <t>698513710516</t>
-  </si>
-  <si>
-    <t>210225792096</t>
-  </si>
-  <si>
-    <t>027089092114</t>
-  </si>
-  <si>
-    <t>236081354779</t>
-  </si>
-  <si>
-    <t>031095037040</t>
-  </si>
-  <si>
-    <t>475238809382</t>
-  </si>
-  <si>
-    <t>375695730319</t>
-  </si>
-  <si>
-    <t>034116501112</t>
-  </si>
-  <si>
-    <t>539701831198</t>
-  </si>
-  <si>
-    <t>977418648860</t>
-  </si>
-  <si>
-    <t>522096545218</t>
-  </si>
-  <si>
-    <t>145122332355</t>
-  </si>
-  <si>
-    <t>027004432467</t>
-  </si>
-  <si>
-    <t>051082712360</t>
-  </si>
-  <si>
-    <t>107983374271</t>
-  </si>
-  <si>
-    <t>950555922941</t>
-  </si>
-  <si>
-    <t>402353158118</t>
-  </si>
-  <si>
-    <t>624523215289</t>
-  </si>
-  <si>
-    <t>039826392824</t>
-  </si>
-  <si>
-    <t>663351577324</t>
-  </si>
-  <si>
-    <t>012644982486</t>
-  </si>
-  <si>
-    <t>295925841014</t>
-  </si>
-  <si>
-    <t>725225980601</t>
-  </si>
-  <si>
-    <t>762184971138</t>
-  </si>
-  <si>
-    <t>918879926148</t>
-  </si>
-  <si>
-    <t>323762289750</t>
-  </si>
-  <si>
-    <t>821774640185</t>
-  </si>
-  <si>
-    <t>208575422759</t>
-  </si>
-  <si>
-    <t>092249060904</t>
-  </si>
-  <si>
-    <t>876040921209</t>
-  </si>
-  <si>
-    <t>649631514161</t>
-  </si>
-  <si>
-    <t>661888781378</t>
-  </si>
-  <si>
-    <t>440433199188</t>
-  </si>
-  <si>
-    <t>278812186425</t>
-  </si>
-  <si>
-    <t>325295136715</t>
-  </si>
-  <si>
-    <t>944402409944</t>
-  </si>
-  <si>
-    <t>127143604068</t>
-  </si>
-  <si>
-    <t>424994102575</t>
-  </si>
-  <si>
-    <t>582157245460</t>
-  </si>
-  <si>
-    <t>195758177378</t>
-  </si>
-  <si>
-    <t>850822333473</t>
-  </si>
-  <si>
-    <t>514825287460</t>
-  </si>
-  <si>
-    <t>524667680870</t>
-  </si>
-  <si>
-    <t>611151000079</t>
-  </si>
-  <si>
-    <t>798363936543</t>
-  </si>
-  <si>
-    <t>458310604356</t>
-  </si>
-  <si>
-    <t>425981845560</t>
-  </si>
-  <si>
-    <t>014727677685</t>
-  </si>
-  <si>
-    <t>929925092184</t>
-  </si>
-  <si>
-    <t>667449437627</t>
-  </si>
-  <si>
-    <t>463797731523</t>
-  </si>
-  <si>
-    <t>886438632489</t>
-  </si>
-  <si>
-    <t>554714269509</t>
-  </si>
-  <si>
-    <t>583361023840</t>
-  </si>
-  <si>
-    <t>881852990252</t>
-  </si>
-  <si>
-    <t>054668491179</t>
-  </si>
-  <si>
-    <t>086955035645</t>
-  </si>
-  <si>
-    <t>245159474413</t>
-  </si>
-  <si>
-    <t>811969398426</t>
-  </si>
-  <si>
-    <t>525272423914</t>
-  </si>
-  <si>
-    <t>458920638555</t>
-  </si>
-  <si>
-    <t>895046587528</t>
-  </si>
-  <si>
-    <t>072374533316</t>
-  </si>
-  <si>
-    <t>304716643275</t>
-  </si>
-  <si>
-    <t>469207750058</t>
-  </si>
-  <si>
-    <t>298013853796</t>
-  </si>
-  <si>
-    <t>282718551402</t>
-  </si>
-  <si>
-    <t>665227625969</t>
-  </si>
-  <si>
-    <t>628019185534</t>
-  </si>
-  <si>
-    <t>629300446424</t>
-  </si>
-  <si>
-    <t>767090977916</t>
-  </si>
-  <si>
-    <t>551886008840</t>
-  </si>
-  <si>
-    <t>844502949893</t>
-  </si>
-  <si>
-    <t>432361234757</t>
-  </si>
-  <si>
-    <t>789562191371</t>
-  </si>
-  <si>
-    <t>945204637714</t>
-  </si>
-  <si>
-    <t>563497930775</t>
-  </si>
-  <si>
-    <t>388175711453</t>
-  </si>
-  <si>
-    <t>522355840708</t>
-  </si>
-  <si>
-    <t>991142701489</t>
-  </si>
-  <si>
-    <t>371877098958</t>
-  </si>
-  <si>
-    <t>484123184595</t>
-  </si>
-  <si>
-    <t>690016901422</t>
-  </si>
-  <si>
-    <t>985594238884</t>
-  </si>
-  <si>
-    <t>145764126822</t>
-  </si>
-  <si>
-    <t>397136695067</t>
-  </si>
-  <si>
-    <t>615121245410</t>
-  </si>
-  <si>
-    <t>183132026019</t>
-  </si>
-  <si>
-    <t>812669240430</t>
-  </si>
-  <si>
-    <t>440894350989</t>
-  </si>
-  <si>
-    <t>494283461844</t>
-  </si>
-  <si>
-    <t>040437804523</t>
-  </si>
-  <si>
-    <t>352438318934</t>
-  </si>
-  <si>
-    <t>037872833852</t>
-  </si>
-  <si>
-    <t>157676201780</t>
-  </si>
-  <si>
-    <t>102981748849</t>
-  </si>
-  <si>
-    <t>836251215863</t>
-  </si>
-  <si>
-    <t>494709456452</t>
-  </si>
-  <si>
-    <t>755004704128</t>
-  </si>
-  <si>
-    <t>743027148075</t>
-  </si>
-  <si>
-    <t>488527881679</t>
-  </si>
-  <si>
-    <t>307009100998</t>
-  </si>
-  <si>
-    <t>979270662682</t>
-  </si>
-  <si>
-    <t>203256338150</t>
-  </si>
-  <si>
-    <t>855727555145</t>
-  </si>
-  <si>
-    <t>927141147484</t>
-  </si>
-  <si>
-    <t>818258507200</t>
-  </si>
-  <si>
-    <t>475451994031</t>
-  </si>
-  <si>
-    <t>502996149103</t>
-  </si>
-  <si>
-    <t>654591230654</t>
-  </si>
-  <si>
-    <t>530826966563</t>
-  </si>
-  <si>
-    <t>591831583134</t>
-  </si>
-  <si>
-    <t>996873237659</t>
-  </si>
-  <si>
-    <t>495698530095</t>
-  </si>
-  <si>
-    <t>263864324891</t>
-  </si>
-  <si>
-    <t>408891031937</t>
-  </si>
-  <si>
-    <t>982443410167</t>
-  </si>
-  <si>
-    <t>198379868723</t>
-  </si>
-  <si>
-    <t>652338819288</t>
-  </si>
-  <si>
-    <t>195005441641</t>
-  </si>
-  <si>
-    <t>266948833646</t>
-  </si>
-  <si>
-    <t>113953946546</t>
-  </si>
-  <si>
-    <t>357244102804</t>
-  </si>
-  <si>
-    <t>573490693400</t>
-  </si>
-  <si>
-    <t>355088889023</t>
-  </si>
-  <si>
-    <t>629356430780</t>
-  </si>
-  <si>
-    <t>279897419121</t>
-  </si>
-  <si>
-    <t>588671257487</t>
-  </si>
-  <si>
-    <t>910535498565</t>
-  </si>
-  <si>
-    <t>321424250510</t>
-  </si>
-  <si>
-    <t>098300597609</t>
-  </si>
-  <si>
-    <t>745752990079</t>
-  </si>
-  <si>
-    <t>095993445363</t>
-  </si>
-  <si>
-    <t>203126929517</t>
-  </si>
-  <si>
-    <t>217673852353</t>
-  </si>
-  <si>
-    <t>618517885285</t>
-  </si>
-  <si>
-    <t>572006200291</t>
-  </si>
-  <si>
-    <t>345055798972</t>
-  </si>
-  <si>
-    <t>060990634280</t>
-  </si>
-  <si>
-    <t>894995597010</t>
-  </si>
-  <si>
-    <t>917203711157</t>
-  </si>
-  <si>
-    <t>647834396516</t>
-  </si>
-  <si>
-    <t>941366001225</t>
-  </si>
-  <si>
-    <t>416960873577</t>
-  </si>
-  <si>
-    <t>524161613019</t>
-  </si>
-  <si>
-    <t>245270763123</t>
-  </si>
-  <si>
-    <t>139890925779</t>
-  </si>
-  <si>
-    <t>419268501611</t>
-  </si>
-  <si>
-    <t>479233229620</t>
-  </si>
-  <si>
-    <t>435959721079</t>
-  </si>
-  <si>
-    <t>974012936477</t>
-  </si>
-  <si>
-    <t>267079824606</t>
-  </si>
-  <si>
-    <t>160799841353</t>
-  </si>
-  <si>
-    <t>296131116952</t>
-  </si>
-  <si>
-    <t>468167727597</t>
-  </si>
-  <si>
-    <t>106384633707</t>
-  </si>
-  <si>
-    <t>244588146728</t>
-  </si>
-  <si>
-    <t>907727655261</t>
-  </si>
-  <si>
-    <t>909646671656</t>
-  </si>
-  <si>
-    <t>802248116249</t>
-  </si>
-  <si>
-    <t>235170899610</t>
-  </si>
-  <si>
-    <t>502185672388</t>
-  </si>
-  <si>
-    <t>633638416440</t>
-  </si>
-  <si>
-    <t>195213578898</t>
-  </si>
-  <si>
-    <t>962853315934</t>
-  </si>
-  <si>
-    <t>541060919084</t>
-  </si>
-  <si>
-    <t>204920699582</t>
-  </si>
-  <si>
-    <t>474687255192</t>
-  </si>
-  <si>
-    <t>670678232235</t>
-  </si>
-  <si>
-    <t>416716217335</t>
-  </si>
-  <si>
-    <t>856013233244</t>
-  </si>
-  <si>
-    <t>305800019680</t>
-  </si>
-  <si>
-    <t>300091001119</t>
-  </si>
-  <si>
-    <t>042123549022</t>
-  </si>
-  <si>
-    <t>911826287028</t>
-  </si>
-  <si>
-    <t>385230772616</t>
-  </si>
-  <si>
-    <t>693656394540</t>
-  </si>
-  <si>
-    <t>519321623802</t>
-  </si>
-  <si>
-    <t>243258878725</t>
-  </si>
-  <si>
-    <t>381113122791</t>
-  </si>
-  <si>
-    <t>338329699538</t>
-  </si>
-  <si>
-    <t>190291196812</t>
-  </si>
-  <si>
-    <t>101472731178</t>
-  </si>
-  <si>
-    <t>417328061338</t>
-  </si>
-  <si>
-    <t>698369238136</t>
-  </si>
-  <si>
-    <t>664555589289</t>
-  </si>
-  <si>
-    <t>697751250871</t>
-  </si>
-  <si>
-    <t>410415192665</t>
-  </si>
-  <si>
-    <t>453436200871</t>
-  </si>
-  <si>
-    <t>921096784507</t>
-  </si>
-  <si>
-    <t>500905115988</t>
-  </si>
-  <si>
-    <t>234173637602</t>
-  </si>
-  <si>
-    <t>800465383927</t>
-  </si>
-  <si>
-    <t>546638590163</t>
-  </si>
-  <si>
-    <t>644321740770</t>
-  </si>
-  <si>
-    <t>367007212469</t>
-  </si>
-  <si>
-    <t>608730421315</t>
-  </si>
-  <si>
-    <t>443297752738</t>
-  </si>
-  <si>
-    <t>418761308533</t>
-  </si>
-  <si>
-    <t>431488989388</t>
-  </si>
-  <si>
-    <t>823909417371</t>
-  </si>
-  <si>
-    <t>261776378820</t>
-  </si>
-  <si>
-    <t>297740611987</t>
-  </si>
-  <si>
-    <t>982018141902</t>
-  </si>
-  <si>
-    <t>354445794599</t>
-  </si>
-  <si>
-    <t>074827590199</t>
-  </si>
-  <si>
-    <t>300092406130</t>
-  </si>
-  <si>
-    <t>898248249628</t>
-  </si>
-  <si>
-    <t>762145687389</t>
-  </si>
-  <si>
-    <t>350758949055</t>
-  </si>
-  <si>
-    <t>745196631561</t>
-  </si>
-  <si>
-    <t>495141433060</t>
-  </si>
-  <si>
-    <t>360820207997</t>
-  </si>
-  <si>
-    <t>045101669962</t>
-  </si>
-  <si>
-    <t>671970439097</t>
-  </si>
-  <si>
-    <t>057008693518</t>
-  </si>
-  <si>
-    <t>506806447538</t>
-  </si>
-  <si>
-    <t>614074978437</t>
-  </si>
-  <si>
-    <t>733648024301</t>
-  </si>
-  <si>
-    <t>726722132721</t>
-  </si>
-  <si>
-    <t>868286125027</t>
-  </si>
-  <si>
-    <t>833876204165</t>
-  </si>
-  <si>
-    <t>457014266126</t>
-  </si>
-  <si>
-    <t>692468292245</t>
-  </si>
-  <si>
-    <t>960475257430</t>
-  </si>
-  <si>
-    <t>103618244252</t>
-  </si>
-  <si>
-    <t>943435165855</t>
-  </si>
-  <si>
-    <t>823266320161</t>
-  </si>
-  <si>
-    <t>493089174899</t>
-  </si>
-  <si>
-    <t>672986731530</t>
-  </si>
-  <si>
-    <t>457464450746</t>
-  </si>
-  <si>
-    <t>431480755437</t>
-  </si>
-  <si>
-    <t>787556080335</t>
-  </si>
-  <si>
-    <t>122514405571</t>
-  </si>
-  <si>
-    <t>278183288003</t>
-  </si>
-  <si>
-    <t>533121739038</t>
-  </si>
-  <si>
-    <t>658520711375</t>
-  </si>
-  <si>
-    <t>583308830116</t>
-  </si>
-  <si>
-    <t>166610522756</t>
-  </si>
-  <si>
-    <t>374102152501</t>
-  </si>
-  <si>
-    <t>986232061132</t>
-  </si>
-  <si>
-    <t>681972712071</t>
-  </si>
-  <si>
-    <t>017253319382</t>
-  </si>
-  <si>
-    <t>223137278414</t>
-  </si>
-  <si>
-    <t>323694855482</t>
-  </si>
-  <si>
-    <t>061940067840</t>
-  </si>
-  <si>
-    <t>493038653137</t>
-  </si>
-  <si>
-    <t>279897701505</t>
-  </si>
-  <si>
-    <t>726630986630</t>
-  </si>
-  <si>
-    <t>195716506759</t>
-  </si>
-  <si>
-    <t>118771256698</t>
-  </si>
-  <si>
-    <t>470719467914</t>
-  </si>
-  <si>
-    <t>684439128445</t>
-  </si>
-  <si>
-    <t>351238049645</t>
-  </si>
-  <si>
-    <t>132557527443</t>
-  </si>
-  <si>
-    <t>405618138416</t>
-  </si>
-  <si>
-    <t>397514993932</t>
-  </si>
-  <si>
-    <t>096787095025</t>
-  </si>
-  <si>
-    <t>077711034522</t>
-  </si>
-  <si>
-    <t>908132246672</t>
-  </si>
-  <si>
-    <t>730263475228</t>
-  </si>
-  <si>
-    <t>794751734694</t>
-  </si>
-  <si>
-    <t>766732199597</t>
-  </si>
-  <si>
-    <t>980769853683</t>
-  </si>
-  <si>
-    <t>187605033478</t>
-  </si>
-  <si>
-    <t>471360173383</t>
-  </si>
-  <si>
-    <t>067690119617</t>
-  </si>
-  <si>
-    <t>850723880972</t>
-  </si>
-  <si>
-    <t>136162941149</t>
-  </si>
-  <si>
-    <t>766842213808</t>
-  </si>
-  <si>
-    <t>023050908183</t>
-  </si>
-  <si>
-    <t>644630987399</t>
-  </si>
-  <si>
-    <t>594095280065</t>
-  </si>
-  <si>
-    <t>286366040764</t>
-  </si>
-  <si>
-    <t>291355067361</t>
-  </si>
-  <si>
-    <t>506448021449</t>
-  </si>
-  <si>
-    <t>377466780553</t>
-  </si>
-  <si>
-    <t>899293293072</t>
-  </si>
-  <si>
-    <t>454611223808</t>
-  </si>
-  <si>
-    <t>013669511502</t>
-  </si>
-  <si>
-    <t>314002471878</t>
-  </si>
-  <si>
-    <t>715839835585</t>
-  </si>
-  <si>
-    <t>802442261460</t>
-  </si>
-  <si>
-    <t>939025519243</t>
-  </si>
-  <si>
-    <t>588065142449</t>
-  </si>
-  <si>
-    <t>473938735257</t>
-  </si>
-  <si>
-    <t>407389263574</t>
-  </si>
-  <si>
-    <t>210415150001</t>
-  </si>
-  <si>
-    <t>552092857990</t>
-  </si>
-  <si>
-    <t>778082929259</t>
-  </si>
-  <si>
-    <t>096799894016</t>
-  </si>
-  <si>
-    <t>469464157800</t>
-  </si>
-  <si>
-    <t>990767516645</t>
-  </si>
-  <si>
-    <t>945013845094</t>
-  </si>
-  <si>
-    <t>852993434386</t>
-  </si>
-  <si>
-    <t>055488820553</t>
-  </si>
-  <si>
-    <t>478508661653</t>
-  </si>
-  <si>
-    <t>060937638596</t>
-  </si>
-  <si>
-    <t>566440242507</t>
-  </si>
-  <si>
-    <t>143381070724</t>
-  </si>
-  <si>
-    <t>870972267838</t>
-  </si>
-  <si>
-    <t>631562083298</t>
-  </si>
-  <si>
-    <t>899255297331</t>
-  </si>
-  <si>
-    <t>263171750456</t>
-  </si>
-  <si>
-    <t>338782285708</t>
-  </si>
-  <si>
-    <t>721029522534</t>
-  </si>
-  <si>
-    <t>370165267392</t>
-  </si>
-  <si>
-    <t>033846833269</t>
-  </si>
-  <si>
-    <t>362768922677</t>
-  </si>
-  <si>
-    <t>792407033575</t>
-  </si>
-  <si>
-    <t>214254128288</t>
-  </si>
-  <si>
-    <t>411656944495</t>
-  </si>
-  <si>
-    <t>720392027361</t>
-  </si>
-  <si>
-    <t>146118882142</t>
-  </si>
-  <si>
-    <t>127540916329</t>
-  </si>
-  <si>
-    <t>814692123568</t>
-  </si>
-  <si>
-    <t>327216875925</t>
-  </si>
-  <si>
-    <t>244134337443</t>
-  </si>
-  <si>
-    <t>090736666151</t>
-  </si>
-  <si>
-    <t>103198540603</t>
-  </si>
-  <si>
-    <t>754429328657</t>
-  </si>
-  <si>
-    <t>814046914013</t>
-  </si>
-  <si>
-    <t>223824978034</t>
-  </si>
-  <si>
-    <t>608294797014</t>
-  </si>
-  <si>
-    <t>312667076078</t>
-  </si>
-  <si>
-    <t>934505734561</t>
-  </si>
-  <si>
-    <t>017540689149</t>
-  </si>
-  <si>
-    <t>949064105187</t>
-  </si>
-  <si>
-    <t>248282501282</t>
-  </si>
-  <si>
-    <t>871910853894</t>
-  </si>
-  <si>
-    <t>467417835032</t>
-  </si>
-  <si>
-    <t>716827613312</t>
-  </si>
-  <si>
-    <t>117419703741</t>
-  </si>
-  <si>
-    <t>530308721743</t>
-  </si>
-  <si>
-    <t>745566326860</t>
-  </si>
-  <si>
-    <t>790645216279</t>
-  </si>
-  <si>
-    <t>371658785422</t>
-  </si>
-  <si>
-    <t>828646824605</t>
-  </si>
-  <si>
-    <t>140785481470</t>
-  </si>
-  <si>
-    <t>640542708088</t>
-  </si>
-  <si>
-    <t>052916906165</t>
-  </si>
-  <si>
-    <t>062074295529</t>
-  </si>
-  <si>
-    <t>026561610911</t>
-  </si>
-  <si>
-    <t>614337112839</t>
-  </si>
-  <si>
-    <t>597790312022</t>
-  </si>
-  <si>
-    <t>757816051461</t>
-  </si>
-  <si>
-    <t>311009201771</t>
-  </si>
-  <si>
-    <t>560838889933</t>
-  </si>
-  <si>
-    <t>182623155689</t>
-  </si>
-  <si>
-    <t>856325997994</t>
-  </si>
-  <si>
-    <t>206717076732</t>
-  </si>
-  <si>
-    <t>556019829784</t>
-  </si>
-  <si>
-    <t>320983170200</t>
-  </si>
-  <si>
-    <t>962550102984</t>
-  </si>
-  <si>
-    <t>760860528283</t>
-  </si>
-  <si>
-    <t>030273806994</t>
-  </si>
-  <si>
-    <t>706027556187</t>
-  </si>
-  <si>
-    <t>739833517115</t>
-  </si>
-  <si>
-    <t>862819688916</t>
-  </si>
-  <si>
-    <t>213962636683</t>
-  </si>
-  <si>
-    <t>920449917316</t>
-  </si>
-  <si>
-    <t>368569663967</t>
-  </si>
-  <si>
-    <t>887113382819</t>
-  </si>
-  <si>
-    <t>616173705430</t>
-  </si>
-  <si>
-    <t>187188002916</t>
-  </si>
-  <si>
-    <t>757646636973</t>
-  </si>
-  <si>
-    <t>021841519558</t>
-  </si>
-  <si>
-    <t>347965150072</t>
-  </si>
-  <si>
-    <t>839484710019</t>
-  </si>
-  <si>
-    <t>734290765948</t>
-  </si>
-  <si>
-    <t>448902127191</t>
-  </si>
-  <si>
-    <t>157724903484</t>
-  </si>
-  <si>
-    <t>796505017981</t>
-  </si>
-  <si>
-    <t>266227284370</t>
-  </si>
-  <si>
-    <t>059642063878</t>
-  </si>
-  <si>
-    <t>244453568390</t>
-  </si>
-  <si>
-    <t>767959592972</t>
-  </si>
-  <si>
-    <t>351372261035</t>
-  </si>
-  <si>
-    <t>809495131697</t>
-  </si>
-  <si>
-    <t>235402872613</t>
-  </si>
-  <si>
-    <t>107290020647</t>
-  </si>
-  <si>
-    <t>378709599898</t>
-  </si>
-  <si>
-    <t>151605557371</t>
-  </si>
-  <si>
-    <t>470712054778</t>
-  </si>
-  <si>
-    <t>888172063678</t>
-  </si>
-  <si>
-    <t>302747242343</t>
-  </si>
-  <si>
-    <t>198630010231</t>
-  </si>
-  <si>
-    <t>103226002370</t>
-  </si>
-  <si>
-    <t>504958172586</t>
-  </si>
-  <si>
-    <t>008881919995</t>
-  </si>
-  <si>
-    <t>208367645377</t>
-  </si>
-  <si>
-    <t>628425976691</t>
-  </si>
-  <si>
-    <t>203432133655</t>
-  </si>
-  <si>
-    <t>446417709373</t>
-  </si>
-  <si>
-    <t>628457429554</t>
-  </si>
-  <si>
-    <t>619525546501</t>
-  </si>
-  <si>
-    <t>393619605560</t>
-  </si>
-  <si>
-    <t>548169883122</t>
-  </si>
-  <si>
-    <t>154910855236</t>
-  </si>
-  <si>
-    <t>305533047354</t>
-  </si>
-  <si>
-    <t>859480229937</t>
-  </si>
-  <si>
-    <t>546572380819</t>
-  </si>
-  <si>
-    <t>035038138815</t>
-  </si>
-  <si>
-    <t>232846795001</t>
-  </si>
-  <si>
-    <t>853195264149</t>
-  </si>
-  <si>
-    <t>856154334972</t>
-  </si>
-  <si>
-    <t>321194903244</t>
-  </si>
-  <si>
-    <t>952424639366</t>
-  </si>
-  <si>
-    <t>155347333156</t>
-  </si>
-  <si>
-    <t>342528626682</t>
-  </si>
-  <si>
-    <t>309990480873</t>
-  </si>
-  <si>
-    <t>696983346751</t>
-  </si>
-  <si>
-    <t>119728041598</t>
-  </si>
-  <si>
-    <t>999326578878</t>
-  </si>
-  <si>
-    <t>926183398206</t>
-  </si>
-  <si>
-    <t>620790364862</t>
-  </si>
-  <si>
-    <t>795318442708</t>
-  </si>
-  <si>
-    <t>298197775987</t>
+    <t>626795027467</t>
+  </si>
+  <si>
+    <t>777</t>
+  </si>
+  <si>
+    <t>274112058244</t>
+  </si>
+  <si>
+    <t>206918491446</t>
+  </si>
+  <si>
+    <t>011496041088</t>
+  </si>
+  <si>
+    <t>078836945386</t>
+  </si>
+  <si>
+    <t>663508155455</t>
+  </si>
+  <si>
+    <t>299700093568</t>
+  </si>
+  <si>
+    <t>758520957445</t>
+  </si>
+  <si>
+    <t>651370971299</t>
+  </si>
+  <si>
+    <t>004156591700</t>
+  </si>
+  <si>
+    <t>966064122359</t>
+  </si>
+  <si>
+    <t>658936556438</t>
+  </si>
+  <si>
+    <t>184707152274</t>
+  </si>
+  <si>
+    <t>892495423672</t>
+  </si>
+  <si>
+    <t>056727496112</t>
+  </si>
+  <si>
+    <t>008224496188</t>
+  </si>
+  <si>
+    <t>245169875098</t>
+  </si>
+  <si>
+    <t>184035627705</t>
+  </si>
+  <si>
+    <t>602927034283</t>
+  </si>
+  <si>
+    <t>601194483291</t>
+  </si>
+  <si>
+    <t>342497523676</t>
+  </si>
+  <si>
+    <t>583539469006</t>
+  </si>
+  <si>
+    <t>529837562530</t>
+  </si>
+  <si>
+    <t>857041137271</t>
+  </si>
+  <si>
+    <t>254856552767</t>
+  </si>
+  <si>
+    <t>323786964184</t>
+  </si>
+  <si>
+    <t>280175206053</t>
+  </si>
+  <si>
+    <t>174094377692</t>
+  </si>
+  <si>
+    <t>987283891485</t>
+  </si>
+  <si>
+    <t>800542894179</t>
+  </si>
+  <si>
+    <t>600907806637</t>
+  </si>
+  <si>
+    <t>845414779492</t>
+  </si>
+  <si>
+    <t>476051315409</t>
+  </si>
+  <si>
+    <t>084874794469</t>
+  </si>
+  <si>
+    <t>108373181740</t>
+  </si>
+  <si>
+    <t>947259937815</t>
+  </si>
+  <si>
+    <t>724686957952</t>
+  </si>
+  <si>
+    <t>536607621254</t>
+  </si>
+  <si>
+    <t>055617444932</t>
+  </si>
+  <si>
+    <t>900756507165</t>
+  </si>
+  <si>
+    <t>341158124138</t>
+  </si>
+  <si>
+    <t>168665376231</t>
+  </si>
+  <si>
+    <t>663378798673</t>
+  </si>
+  <si>
+    <t>289493533385</t>
+  </si>
+  <si>
+    <t>055624800583</t>
+  </si>
+  <si>
+    <t>640228114881</t>
+  </si>
+  <si>
+    <t>540377543726</t>
+  </si>
+  <si>
+    <t>400242127540</t>
+  </si>
+  <si>
+    <t>150156532215</t>
+  </si>
+  <si>
+    <t>531039219088</t>
+  </si>
+  <si>
+    <t>677051129870</t>
+  </si>
+  <si>
+    <t>362210673902</t>
+  </si>
+  <si>
+    <t>806981590255</t>
+  </si>
+  <si>
+    <t>045305042346</t>
+  </si>
+  <si>
+    <t>075624037155</t>
+  </si>
+  <si>
+    <t>653326239983</t>
+  </si>
+  <si>
+    <t>287681054969</t>
+  </si>
+  <si>
+    <t>849633432050</t>
+  </si>
+  <si>
+    <t>679795556290</t>
+  </si>
+  <si>
+    <t>762859751768</t>
+  </si>
+  <si>
+    <t>001905222257</t>
+  </si>
+  <si>
+    <t>131630087083</t>
+  </si>
+  <si>
+    <t>359117432016</t>
+  </si>
+  <si>
+    <t>019628634837</t>
+  </si>
+  <si>
+    <t>375893494222</t>
+  </si>
+  <si>
+    <t>625172702784</t>
+  </si>
+  <si>
+    <t>055398447403</t>
+  </si>
+  <si>
+    <t>810285436682</t>
+  </si>
+  <si>
+    <t>483202740683</t>
+  </si>
+  <si>
+    <t>154445522550</t>
+  </si>
+  <si>
+    <t>844338174579</t>
+  </si>
+  <si>
+    <t>273163220307</t>
+  </si>
+  <si>
+    <t>727987555222</t>
+  </si>
+  <si>
+    <t>137678707888</t>
+  </si>
+  <si>
+    <t>899368538884</t>
+  </si>
+  <si>
+    <t>440529896731</t>
+  </si>
+  <si>
+    <t>761000733729</t>
+  </si>
+  <si>
+    <t>362898123896</t>
+  </si>
+  <si>
+    <t>890308677020</t>
+  </si>
+  <si>
+    <t>888162523948</t>
+  </si>
+  <si>
+    <t>303403414460</t>
+  </si>
+  <si>
+    <t>415781161023</t>
+  </si>
+  <si>
+    <t>529611687661</t>
+  </si>
+  <si>
+    <t>471878334906</t>
+  </si>
+  <si>
+    <t>845898785894</t>
+  </si>
+  <si>
+    <t>959782654047</t>
+  </si>
+  <si>
+    <t>930080773308</t>
+  </si>
+  <si>
+    <t>252888249711</t>
+  </si>
+  <si>
+    <t>277951405950</t>
+  </si>
+  <si>
+    <t>889134031924</t>
+  </si>
+  <si>
+    <t>418667335371</t>
+  </si>
+  <si>
+    <t>486100046608</t>
+  </si>
+  <si>
+    <t>514696598872</t>
+  </si>
+  <si>
+    <t>125688823859</t>
+  </si>
+  <si>
+    <t>372750377906</t>
+  </si>
+  <si>
+    <t>507720565176</t>
+  </si>
+  <si>
+    <t>472819028264</t>
+  </si>
+  <si>
+    <t>593955127111</t>
+  </si>
+  <si>
+    <t>481049020155</t>
+  </si>
+  <si>
+    <t>482788643317</t>
+  </si>
+  <si>
+    <t>762727765697</t>
+  </si>
+  <si>
+    <t>247812137816</t>
+  </si>
+  <si>
+    <t>810785918670</t>
+  </si>
+  <si>
+    <t>602110619223</t>
+  </si>
+  <si>
+    <t>925516841307</t>
+  </si>
+  <si>
+    <t>960090839923</t>
+  </si>
+  <si>
+    <t>643172085860</t>
+  </si>
+  <si>
+    <t>948255082447</t>
+  </si>
+  <si>
+    <t>065632599673</t>
+  </si>
+  <si>
+    <t>588933772113</t>
+  </si>
+  <si>
+    <t>400730479998</t>
+  </si>
+  <si>
+    <t>889798600642</t>
+  </si>
+  <si>
+    <t>217309267613</t>
+  </si>
+  <si>
+    <t>912970781010</t>
+  </si>
+  <si>
+    <t>047825871396</t>
+  </si>
+  <si>
+    <t>993851726205</t>
+  </si>
+  <si>
+    <t>240049030127</t>
+  </si>
+  <si>
+    <t>402109481532</t>
+  </si>
+  <si>
+    <t>327765863019</t>
+  </si>
+  <si>
+    <t>077463146506</t>
+  </si>
+  <si>
+    <t>867903486431</t>
+  </si>
+  <si>
+    <t>378305122385</t>
+  </si>
+  <si>
+    <t>537795842398</t>
+  </si>
+  <si>
+    <t>132960930970</t>
+  </si>
+  <si>
+    <t>020749361912</t>
+  </si>
+  <si>
+    <t>942490712867</t>
+  </si>
+  <si>
+    <t>740776673171</t>
+  </si>
+  <si>
+    <t>730513300015</t>
+  </si>
+  <si>
+    <t>384883498557</t>
+  </si>
+  <si>
+    <t>612155843373</t>
+  </si>
+  <si>
+    <t>214497206046</t>
+  </si>
+  <si>
+    <t>053434728566</t>
+  </si>
+  <si>
+    <t>984537135142</t>
+  </si>
+  <si>
+    <t>025769888873</t>
+  </si>
+  <si>
+    <t>285070352209</t>
+  </si>
+  <si>
+    <t>652313652672</t>
+  </si>
+  <si>
+    <t>719906703096</t>
+  </si>
+  <si>
+    <t>314013158728</t>
+  </si>
+  <si>
+    <t>256693025336</t>
+  </si>
+  <si>
+    <t>240903734423</t>
+  </si>
+  <si>
+    <t>925892930778</t>
+  </si>
+  <si>
+    <t>719257115167</t>
+  </si>
+  <si>
+    <t>683028452245</t>
+  </si>
+  <si>
+    <t>138361690928</t>
+  </si>
+  <si>
+    <t>905745316115</t>
+  </si>
+  <si>
+    <t>327972054642</t>
+  </si>
+  <si>
+    <t>273929624090</t>
+  </si>
+  <si>
+    <t>729795769861</t>
+  </si>
+  <si>
+    <t>633959285169</t>
+  </si>
+  <si>
+    <t>922752116531</t>
+  </si>
+  <si>
+    <t>320171399918</t>
+  </si>
+  <si>
+    <t>232753766150</t>
+  </si>
+  <si>
+    <t>547832497721</t>
+  </si>
+  <si>
+    <t>110236322882</t>
+  </si>
+  <si>
+    <t>032492052135</t>
+  </si>
+  <si>
+    <t>386634734891</t>
+  </si>
+  <si>
+    <t>854598519974</t>
+  </si>
+  <si>
+    <t>375704152221</t>
+  </si>
+  <si>
+    <t>036716158583</t>
+  </si>
+  <si>
+    <t>630914669341</t>
+  </si>
+  <si>
+    <t>248738360553</t>
+  </si>
+  <si>
+    <t>756632943797</t>
+  </si>
+  <si>
+    <t>432554802225</t>
+  </si>
+  <si>
+    <t>802919980735</t>
+  </si>
+  <si>
+    <t>357535010016</t>
+  </si>
+  <si>
+    <t>506347764100</t>
+  </si>
+  <si>
+    <t>760270723235</t>
+  </si>
+  <si>
+    <t>400578403890</t>
+  </si>
+  <si>
+    <t>894415514757</t>
+  </si>
+  <si>
+    <t>239390119167</t>
+  </si>
+  <si>
+    <t>272291446775</t>
+  </si>
+  <si>
+    <t>085679019852</t>
+  </si>
+  <si>
+    <t>550871358261</t>
+  </si>
+  <si>
+    <t>195700772558</t>
+  </si>
+  <si>
+    <t>574594135630</t>
+  </si>
+  <si>
+    <t>956783808838</t>
+  </si>
+  <si>
+    <t>320016577230</t>
+  </si>
+  <si>
+    <t>109311152190</t>
+  </si>
+  <si>
+    <t>141580450714</t>
+  </si>
+  <si>
+    <t>722563781502</t>
+  </si>
+  <si>
+    <t>360956142816</t>
+  </si>
+  <si>
+    <t>672824759841</t>
+  </si>
+  <si>
+    <t>102625136058</t>
+  </si>
+  <si>
+    <t>305918269820</t>
+  </si>
+  <si>
+    <t>767521543730</t>
+  </si>
+  <si>
+    <t>575824038993</t>
+  </si>
+  <si>
+    <t>815444237335</t>
+  </si>
+  <si>
+    <t>530155867556</t>
+  </si>
+  <si>
+    <t>510181563078</t>
+  </si>
+  <si>
+    <t>072875389935</t>
+  </si>
+  <si>
+    <t>513722617822</t>
+  </si>
+  <si>
+    <t>615702545588</t>
+  </si>
+  <si>
+    <t>758179994035</t>
+  </si>
+  <si>
+    <t>624506754471</t>
+  </si>
+  <si>
+    <t>537511219864</t>
+  </si>
+  <si>
+    <t>249678514468</t>
+  </si>
+  <si>
+    <t>397705911838</t>
+  </si>
+  <si>
+    <t>474244280737</t>
+  </si>
+  <si>
+    <t>977351726266</t>
+  </si>
+  <si>
+    <t>850216469889</t>
+  </si>
+  <si>
+    <t>716396305790</t>
+  </si>
+  <si>
+    <t>208574739224</t>
+  </si>
+  <si>
+    <t>401362756840</t>
+  </si>
+  <si>
+    <t>542349628468</t>
+  </si>
+  <si>
+    <t>620379837265</t>
+  </si>
+  <si>
+    <t>883420134299</t>
+  </si>
+  <si>
+    <t>684591813986</t>
+  </si>
+  <si>
+    <t>356660422141</t>
+  </si>
+  <si>
+    <t>882658563798</t>
+  </si>
+  <si>
+    <t>257530903014</t>
+  </si>
+  <si>
+    <t>024128213867</t>
+  </si>
+  <si>
+    <t>711180599390</t>
+  </si>
+  <si>
+    <t>128988624104</t>
+  </si>
+  <si>
+    <t>141827126648</t>
+  </si>
+  <si>
+    <t>988882029299</t>
+  </si>
+  <si>
+    <t>692853423184</t>
+  </si>
+  <si>
+    <t>783344974540</t>
+  </si>
+  <si>
+    <t>054641861393</t>
+  </si>
+  <si>
+    <t>811180973987</t>
+  </si>
+  <si>
+    <t>391151592146</t>
+  </si>
+  <si>
+    <t>986664573457</t>
+  </si>
+  <si>
+    <t>709446044748</t>
+  </si>
+  <si>
+    <t>540798505855</t>
+  </si>
+  <si>
+    <t>324677251767</t>
+  </si>
+  <si>
+    <t>002191283830</t>
+  </si>
+  <si>
+    <t>225151213261</t>
+  </si>
+  <si>
+    <t>274705421229</t>
+  </si>
+  <si>
+    <t>868965707756</t>
+  </si>
+  <si>
+    <t>934892123798</t>
+  </si>
+  <si>
+    <t>595805746732</t>
+  </si>
+  <si>
+    <t>952144427150</t>
+  </si>
+  <si>
+    <t>808544142755</t>
+  </si>
+  <si>
+    <t>628399260440</t>
+  </si>
+  <si>
+    <t>295232977952</t>
+  </si>
+  <si>
+    <t>845776437338</t>
+  </si>
+  <si>
+    <t>940969289421</t>
+  </si>
+  <si>
+    <t>779194494314</t>
+  </si>
+  <si>
+    <t>541145327974</t>
+  </si>
+  <si>
+    <t>996894929355</t>
+  </si>
+  <si>
+    <t>853217010326</t>
+  </si>
+  <si>
+    <t>908635353880</t>
+  </si>
+  <si>
+    <t>066940311682</t>
+  </si>
+  <si>
+    <t>746008575338</t>
+  </si>
+  <si>
+    <t>456075311264</t>
+  </si>
+  <si>
+    <t>930593449832</t>
+  </si>
+  <si>
+    <t>333605810329</t>
+  </si>
+  <si>
+    <t>659461523275</t>
+  </si>
+  <si>
+    <t>924351605497</t>
+  </si>
+  <si>
+    <t>958411055879</t>
+  </si>
+  <si>
+    <t>163763675765</t>
+  </si>
+  <si>
+    <t>822016542726</t>
+  </si>
+  <si>
+    <t>457434154983</t>
+  </si>
+  <si>
+    <t>302891073034</t>
+  </si>
+  <si>
+    <t>374123748005</t>
+  </si>
+  <si>
+    <t>657043908827</t>
+  </si>
+  <si>
+    <t>846727132688</t>
+  </si>
+  <si>
+    <t>188961374013</t>
+  </si>
+  <si>
+    <t>513420238217</t>
+  </si>
+  <si>
+    <t>689518704584</t>
+  </si>
+  <si>
+    <t>348471510901</t>
+  </si>
+  <si>
+    <t>223582003252</t>
+  </si>
+  <si>
+    <t>305725837735</t>
+  </si>
+  <si>
+    <t>220032487721</t>
+  </si>
+  <si>
+    <t>641613388817</t>
+  </si>
+  <si>
+    <t>648993969048</t>
+  </si>
+  <si>
+    <t>172507542349</t>
+  </si>
+  <si>
+    <t>264034643087</t>
+  </si>
+  <si>
+    <t>790817773949</t>
+  </si>
+  <si>
+    <t>095463451344</t>
+  </si>
+  <si>
+    <t>324023243801</t>
+  </si>
+  <si>
+    <t>235458635608</t>
+  </si>
+  <si>
+    <t>194657935082</t>
+  </si>
+  <si>
+    <t>531250140624</t>
+  </si>
+  <si>
+    <t>477715697807</t>
+  </si>
+  <si>
+    <t>868835376828</t>
+  </si>
+  <si>
+    <t>599706071819</t>
+  </si>
+  <si>
+    <t>509234755337</t>
+  </si>
+  <si>
+    <t>562269994664</t>
+  </si>
+  <si>
+    <t>752693814430</t>
+  </si>
+  <si>
+    <t>986333782423</t>
+  </si>
+  <si>
+    <t>859079066160</t>
+  </si>
+  <si>
+    <t>179825947428</t>
+  </si>
+  <si>
+    <t>027509368791</t>
+  </si>
+  <si>
+    <t>036392075001</t>
+  </si>
+  <si>
+    <t>204013418703</t>
+  </si>
+  <si>
+    <t>773719242041</t>
+  </si>
+  <si>
+    <t>140440001854</t>
+  </si>
+  <si>
+    <t>908221106753</t>
+  </si>
+  <si>
+    <t>945990090327</t>
+  </si>
+  <si>
+    <t>644827858468</t>
+  </si>
+  <si>
+    <t>242528604228</t>
+  </si>
+  <si>
+    <t>744912106065</t>
+  </si>
+  <si>
+    <t>125121895261</t>
+  </si>
+  <si>
+    <t>505251701787</t>
+  </si>
+  <si>
+    <t>832455038482</t>
+  </si>
+  <si>
+    <t>160027449663</t>
+  </si>
+  <si>
+    <t>138635085608</t>
+  </si>
+  <si>
+    <t>242675048865</t>
+  </si>
+  <si>
+    <t>645386576617</t>
+  </si>
+  <si>
+    <t>843743305033</t>
+  </si>
+  <si>
+    <t>385975920199</t>
+  </si>
+  <si>
+    <t>527398021797</t>
+  </si>
+  <si>
+    <t>771319609430</t>
+  </si>
+  <si>
+    <t>649384728212</t>
+  </si>
+  <si>
+    <t>632933061409</t>
+  </si>
+  <si>
+    <t>625375767903</t>
+  </si>
+  <si>
+    <t>942567876453</t>
+  </si>
+  <si>
+    <t>358142609009</t>
+  </si>
+  <si>
+    <t>663326117417</t>
+  </si>
+  <si>
+    <t>384080297581</t>
+  </si>
+  <si>
+    <t>994179933323</t>
+  </si>
+  <si>
+    <t>441383058951</t>
+  </si>
+  <si>
+    <t>082971654028</t>
+  </si>
+  <si>
+    <t>262862240416</t>
+  </si>
+  <si>
+    <t>832368910286</t>
+  </si>
+  <si>
+    <t>483394378472</t>
+  </si>
+  <si>
+    <t>817504554163</t>
+  </si>
+  <si>
+    <t>756733454949</t>
+  </si>
+  <si>
+    <t>633038858926</t>
+  </si>
+  <si>
+    <t>419754768649</t>
+  </si>
+  <si>
+    <t>009195287162</t>
+  </si>
+  <si>
+    <t>625883978769</t>
+  </si>
+  <si>
+    <t>799948975818</t>
+  </si>
+  <si>
+    <t>524800767982</t>
+  </si>
+  <si>
+    <t>461947863583</t>
+  </si>
+  <si>
+    <t>516011323339</t>
+  </si>
+  <si>
+    <t>741673793954</t>
+  </si>
+  <si>
+    <t>556130739780</t>
+  </si>
+  <si>
+    <t>761848815367</t>
+  </si>
+  <si>
+    <t>809628457317</t>
+  </si>
+  <si>
+    <t>816387339182</t>
+  </si>
+  <si>
+    <t>535671315284</t>
+  </si>
+  <si>
+    <t>171615491496</t>
+  </si>
+  <si>
+    <t>174508760058</t>
+  </si>
+  <si>
+    <t>318745493629</t>
+  </si>
+  <si>
+    <t>009794453397</t>
+  </si>
+  <si>
+    <t>486997162844</t>
+  </si>
+  <si>
+    <t>284016316642</t>
+  </si>
+  <si>
+    <t>095821808990</t>
+  </si>
+  <si>
+    <t>360262845099</t>
+  </si>
+  <si>
+    <t>193997168849</t>
+  </si>
+  <si>
+    <t>706642203760</t>
+  </si>
+  <si>
+    <t>886308067435</t>
+  </si>
+  <si>
+    <t>985975941176</t>
+  </si>
+  <si>
+    <t>801976686738</t>
+  </si>
+  <si>
+    <t>049071606978</t>
+  </si>
+  <si>
+    <t>973754056369</t>
+  </si>
+  <si>
+    <t>025048769401</t>
+  </si>
+  <si>
+    <t>275445760753</t>
+  </si>
+  <si>
+    <t>757223994504</t>
+  </si>
+  <si>
+    <t>584592615059</t>
+  </si>
+  <si>
+    <t>355593059639</t>
+  </si>
+  <si>
+    <t>259336914134</t>
+  </si>
+  <si>
+    <t>449389281276</t>
+  </si>
+  <si>
+    <t>977506683425</t>
+  </si>
+  <si>
+    <t>188139013611</t>
+  </si>
+  <si>
+    <t>463247109695</t>
+  </si>
+  <si>
+    <t>893861086217</t>
+  </si>
+  <si>
+    <t>044830997767</t>
+  </si>
+  <si>
+    <t>399592009408</t>
+  </si>
+  <si>
+    <t>454513795647</t>
+  </si>
+  <si>
+    <t>024184221354</t>
+  </si>
+  <si>
+    <t>959902589047</t>
+  </si>
+  <si>
+    <t>646254489625</t>
+  </si>
+  <si>
+    <t>141125818137</t>
+  </si>
+  <si>
+    <t>085632670482</t>
+  </si>
+  <si>
+    <t>517719436267</t>
+  </si>
+  <si>
+    <t>712998924443</t>
+  </si>
+  <si>
+    <t>578330331225</t>
+  </si>
+  <si>
+    <t>412586665358</t>
+  </si>
+  <si>
+    <t>837458386177</t>
+  </si>
+  <si>
+    <t>079029955764</t>
+  </si>
+  <si>
+    <t>640739453531</t>
+  </si>
+  <si>
+    <t>304987207206</t>
+  </si>
+  <si>
+    <t>860053778519</t>
+  </si>
+  <si>
+    <t>903741369573</t>
+  </si>
+  <si>
+    <t>567405829278</t>
+  </si>
+  <si>
+    <t>109132290171</t>
+  </si>
+  <si>
+    <t>048140526046</t>
+  </si>
+  <si>
+    <t>323958991001</t>
+  </si>
+  <si>
+    <t>382715449205</t>
+  </si>
+  <si>
+    <t>352641430095</t>
+  </si>
+  <si>
+    <t>379485913691</t>
+  </si>
+  <si>
+    <t>109862551784</t>
+  </si>
+  <si>
+    <t>600097764068</t>
+  </si>
+  <si>
+    <t>460052240642</t>
+  </si>
+  <si>
+    <t>855438001075</t>
+  </si>
+  <si>
+    <t>679681959764</t>
+  </si>
+  <si>
+    <t>111348901628</t>
+  </si>
+  <si>
+    <t>061156972039</t>
+  </si>
+  <si>
+    <t>823461702810</t>
+  </si>
+  <si>
+    <t>412141171463</t>
+  </si>
+  <si>
+    <t>269648735367</t>
+  </si>
+  <si>
+    <t>524605769932</t>
+  </si>
+  <si>
+    <t>386685918580</t>
+  </si>
+  <si>
+    <t>825990389439</t>
+  </si>
+  <si>
+    <t>890941111110</t>
+  </si>
+  <si>
+    <t>652914329193</t>
+  </si>
+  <si>
+    <t>715809539626</t>
+  </si>
+  <si>
+    <t>318768764329</t>
+  </si>
+  <si>
+    <t>354956642031</t>
+  </si>
+  <si>
+    <t>616818251648</t>
+  </si>
+  <si>
+    <t>493520773672</t>
+  </si>
+  <si>
+    <t>869446582569</t>
+  </si>
+  <si>
+    <t>238738900156</t>
+  </si>
+  <si>
+    <t>987394513174</t>
+  </si>
+  <si>
+    <t>153961617673</t>
+  </si>
+  <si>
+    <t>802091487976</t>
+  </si>
+  <si>
+    <t>121410354132</t>
+  </si>
+  <si>
+    <t>527382061888</t>
+  </si>
+  <si>
+    <t>012716759294</t>
+  </si>
+  <si>
+    <t>822624744310</t>
+  </si>
+  <si>
+    <t>756597180464</t>
+  </si>
+  <si>
+    <t>345791028774</t>
+  </si>
+  <si>
+    <t>130074150248</t>
+  </si>
+  <si>
+    <t>106640003478</t>
+  </si>
+  <si>
+    <t>943488600404</t>
+  </si>
+  <si>
+    <t>727311574297</t>
+  </si>
+  <si>
+    <t>191129770200</t>
+  </si>
+  <si>
+    <t>952919953158</t>
+  </si>
+  <si>
+    <t>485025966158</t>
+  </si>
+  <si>
+    <t>877317883161</t>
+  </si>
+  <si>
+    <t>537629184299</t>
+  </si>
+  <si>
+    <t>837893055619</t>
+  </si>
+  <si>
+    <t>293809810273</t>
+  </si>
+  <si>
+    <t>589110267083</t>
+  </si>
+  <si>
+    <t>011415874295</t>
+  </si>
+  <si>
+    <t>240761755173</t>
+  </si>
+  <si>
+    <t>583771711328</t>
+  </si>
+  <si>
+    <t>765143149957</t>
+  </si>
+  <si>
+    <t>223775349788</t>
+  </si>
+  <si>
+    <t>254738936677</t>
+  </si>
+  <si>
+    <t>316536095203</t>
+  </si>
+  <si>
+    <t>405146542319</t>
+  </si>
+  <si>
+    <t>516701615094</t>
+  </si>
+  <si>
+    <t>650585080939</t>
+  </si>
+  <si>
+    <t>503242768252</t>
+  </si>
+  <si>
+    <t>166855623193</t>
+  </si>
+  <si>
+    <t>377849249032</t>
+  </si>
+  <si>
+    <t>112939748911</t>
+  </si>
+  <si>
+    <t>499833633659</t>
+  </si>
+  <si>
+    <t>589039399014</t>
+  </si>
+  <si>
+    <t>699741548210</t>
+  </si>
+  <si>
+    <t>785880710601</t>
+  </si>
+  <si>
+    <t>574504163854</t>
+  </si>
+  <si>
+    <t>536270394828</t>
+  </si>
+  <si>
+    <t>726020553903</t>
+  </si>
+  <si>
+    <t>020404454398</t>
+  </si>
+  <si>
+    <t>463174222506</t>
+  </si>
+  <si>
+    <t>797022189468</t>
+  </si>
+  <si>
+    <t>027209562636</t>
+  </si>
+  <si>
+    <t>249434558344</t>
+  </si>
+  <si>
+    <t>068879607798</t>
+  </si>
+  <si>
+    <t>719862268255</t>
+  </si>
+  <si>
+    <t>749487851788</t>
+  </si>
+  <si>
+    <t>894549546278</t>
+  </si>
+  <si>
+    <t>774094102303</t>
+  </si>
+  <si>
+    <t>240540306135</t>
+  </si>
+  <si>
+    <t>830982271669</t>
+  </si>
+  <si>
+    <t>277995401309</t>
+  </si>
+  <si>
+    <t>593091398023</t>
+  </si>
+  <si>
+    <t>885046462650</t>
+  </si>
+  <si>
+    <t>756423507156</t>
+  </si>
+  <si>
+    <t>419749570046</t>
+  </si>
+  <si>
+    <t>752125230651</t>
+  </si>
+  <si>
+    <t>871339062810</t>
+  </si>
+  <si>
+    <t>420849736294</t>
+  </si>
+  <si>
+    <t>180610548971</t>
+  </si>
+  <si>
+    <t>605742804696</t>
+  </si>
+  <si>
+    <t>073092003817</t>
+  </si>
+  <si>
+    <t>403682676172</t>
+  </si>
+  <si>
+    <t>130721137943</t>
+  </si>
+  <si>
+    <t>060254479572</t>
+  </si>
+  <si>
+    <t>578575054888</t>
+  </si>
+  <si>
+    <t>621346615784</t>
+  </si>
+  <si>
+    <t>196251779619</t>
+  </si>
+  <si>
+    <t>731092230570</t>
+  </si>
+  <si>
+    <t>851772330587</t>
+  </si>
+  <si>
+    <t>955653009791</t>
+  </si>
+  <si>
+    <t>570228918963</t>
+  </si>
+  <si>
+    <t>202725679544</t>
+  </si>
+  <si>
+    <t>328874137784</t>
+  </si>
+  <si>
+    <t>958432986259</t>
+  </si>
+  <si>
+    <t>244833088361</t>
+  </si>
+  <si>
+    <t>327674755287</t>
+  </si>
+  <si>
+    <t>897525922674</t>
+  </si>
+  <si>
+    <t>897885255804</t>
+  </si>
+  <si>
+    <t>300030457187</t>
+  </si>
+  <si>
+    <t>160105019571</t>
+  </si>
+  <si>
+    <t>044755931173</t>
+  </si>
+  <si>
+    <t>929434187994</t>
+  </si>
+  <si>
+    <t>253228064822</t>
+  </si>
+  <si>
+    <t>090427468177</t>
+  </si>
+  <si>
+    <t>658203079731</t>
+  </si>
+  <si>
+    <t>434130952008</t>
+  </si>
+  <si>
+    <t>439143705842</t>
+  </si>
+  <si>
+    <t>191382227678</t>
+  </si>
+  <si>
+    <t>919352006002</t>
+  </si>
+  <si>
+    <t>735894973346</t>
+  </si>
+  <si>
+    <t>344828645872</t>
   </si>
 </sst>
 </file>

--- a/uploadfile.xlsx
+++ b/uploadfile.xlsx
@@ -20,1507 +20,1507 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>626795027467</t>
-  </si>
-  <si>
-    <t>777</t>
-  </si>
-  <si>
-    <t>274112058244</t>
-  </si>
-  <si>
-    <t>206918491446</t>
-  </si>
-  <si>
-    <t>011496041088</t>
-  </si>
-  <si>
-    <t>078836945386</t>
-  </si>
-  <si>
-    <t>663508155455</t>
-  </si>
-  <si>
-    <t>299700093568</t>
-  </si>
-  <si>
-    <t>758520957445</t>
-  </si>
-  <si>
-    <t>651370971299</t>
-  </si>
-  <si>
-    <t>004156591700</t>
-  </si>
-  <si>
-    <t>966064122359</t>
-  </si>
-  <si>
-    <t>658936556438</t>
-  </si>
-  <si>
-    <t>184707152274</t>
-  </si>
-  <si>
-    <t>892495423672</t>
-  </si>
-  <si>
-    <t>056727496112</t>
-  </si>
-  <si>
-    <t>008224496188</t>
-  </si>
-  <si>
-    <t>245169875098</t>
-  </si>
-  <si>
-    <t>184035627705</t>
-  </si>
-  <si>
-    <t>602927034283</t>
-  </si>
-  <si>
-    <t>601194483291</t>
-  </si>
-  <si>
-    <t>342497523676</t>
-  </si>
-  <si>
-    <t>583539469006</t>
-  </si>
-  <si>
-    <t>529837562530</t>
-  </si>
-  <si>
-    <t>857041137271</t>
-  </si>
-  <si>
-    <t>254856552767</t>
-  </si>
-  <si>
-    <t>323786964184</t>
-  </si>
-  <si>
-    <t>280175206053</t>
-  </si>
-  <si>
-    <t>174094377692</t>
-  </si>
-  <si>
-    <t>987283891485</t>
-  </si>
-  <si>
-    <t>800542894179</t>
-  </si>
-  <si>
-    <t>600907806637</t>
-  </si>
-  <si>
-    <t>845414779492</t>
-  </si>
-  <si>
-    <t>476051315409</t>
-  </si>
-  <si>
-    <t>084874794469</t>
-  </si>
-  <si>
-    <t>108373181740</t>
-  </si>
-  <si>
-    <t>947259937815</t>
-  </si>
-  <si>
-    <t>724686957952</t>
-  </si>
-  <si>
-    <t>536607621254</t>
-  </si>
-  <si>
-    <t>055617444932</t>
-  </si>
-  <si>
-    <t>900756507165</t>
-  </si>
-  <si>
-    <t>341158124138</t>
-  </si>
-  <si>
-    <t>168665376231</t>
-  </si>
-  <si>
-    <t>663378798673</t>
-  </si>
-  <si>
-    <t>289493533385</t>
-  </si>
-  <si>
-    <t>055624800583</t>
-  </si>
-  <si>
-    <t>640228114881</t>
-  </si>
-  <si>
-    <t>540377543726</t>
-  </si>
-  <si>
-    <t>400242127540</t>
-  </si>
-  <si>
-    <t>150156532215</t>
-  </si>
-  <si>
-    <t>531039219088</t>
-  </si>
-  <si>
-    <t>677051129870</t>
-  </si>
-  <si>
-    <t>362210673902</t>
-  </si>
-  <si>
-    <t>806981590255</t>
-  </si>
-  <si>
-    <t>045305042346</t>
-  </si>
-  <si>
-    <t>075624037155</t>
-  </si>
-  <si>
-    <t>653326239983</t>
-  </si>
-  <si>
-    <t>287681054969</t>
-  </si>
-  <si>
-    <t>849633432050</t>
-  </si>
-  <si>
-    <t>679795556290</t>
-  </si>
-  <si>
-    <t>762859751768</t>
-  </si>
-  <si>
-    <t>001905222257</t>
-  </si>
-  <si>
-    <t>131630087083</t>
-  </si>
-  <si>
-    <t>359117432016</t>
-  </si>
-  <si>
-    <t>019628634837</t>
-  </si>
-  <si>
-    <t>375893494222</t>
-  </si>
-  <si>
-    <t>625172702784</t>
-  </si>
-  <si>
-    <t>055398447403</t>
-  </si>
-  <si>
-    <t>810285436682</t>
-  </si>
-  <si>
-    <t>483202740683</t>
-  </si>
-  <si>
-    <t>154445522550</t>
-  </si>
-  <si>
-    <t>844338174579</t>
-  </si>
-  <si>
-    <t>273163220307</t>
-  </si>
-  <si>
-    <t>727987555222</t>
-  </si>
-  <si>
-    <t>137678707888</t>
-  </si>
-  <si>
-    <t>899368538884</t>
-  </si>
-  <si>
-    <t>440529896731</t>
-  </si>
-  <si>
-    <t>761000733729</t>
-  </si>
-  <si>
-    <t>362898123896</t>
-  </si>
-  <si>
-    <t>890308677020</t>
-  </si>
-  <si>
-    <t>888162523948</t>
-  </si>
-  <si>
-    <t>303403414460</t>
-  </si>
-  <si>
-    <t>415781161023</t>
-  </si>
-  <si>
-    <t>529611687661</t>
-  </si>
-  <si>
-    <t>471878334906</t>
-  </si>
-  <si>
-    <t>845898785894</t>
-  </si>
-  <si>
-    <t>959782654047</t>
-  </si>
-  <si>
-    <t>930080773308</t>
-  </si>
-  <si>
-    <t>252888249711</t>
-  </si>
-  <si>
-    <t>277951405950</t>
-  </si>
-  <si>
-    <t>889134031924</t>
-  </si>
-  <si>
-    <t>418667335371</t>
-  </si>
-  <si>
-    <t>486100046608</t>
-  </si>
-  <si>
-    <t>514696598872</t>
-  </si>
-  <si>
-    <t>125688823859</t>
-  </si>
-  <si>
-    <t>372750377906</t>
-  </si>
-  <si>
-    <t>507720565176</t>
-  </si>
-  <si>
-    <t>472819028264</t>
-  </si>
-  <si>
-    <t>593955127111</t>
-  </si>
-  <si>
-    <t>481049020155</t>
-  </si>
-  <si>
-    <t>482788643317</t>
-  </si>
-  <si>
-    <t>762727765697</t>
-  </si>
-  <si>
-    <t>247812137816</t>
-  </si>
-  <si>
-    <t>810785918670</t>
-  </si>
-  <si>
-    <t>602110619223</t>
-  </si>
-  <si>
-    <t>925516841307</t>
-  </si>
-  <si>
-    <t>960090839923</t>
-  </si>
-  <si>
-    <t>643172085860</t>
-  </si>
-  <si>
-    <t>948255082447</t>
-  </si>
-  <si>
-    <t>065632599673</t>
-  </si>
-  <si>
-    <t>588933772113</t>
-  </si>
-  <si>
-    <t>400730479998</t>
-  </si>
-  <si>
-    <t>889798600642</t>
-  </si>
-  <si>
-    <t>217309267613</t>
-  </si>
-  <si>
-    <t>912970781010</t>
-  </si>
-  <si>
-    <t>047825871396</t>
-  </si>
-  <si>
-    <t>993851726205</t>
-  </si>
-  <si>
-    <t>240049030127</t>
-  </si>
-  <si>
-    <t>402109481532</t>
-  </si>
-  <si>
-    <t>327765863019</t>
-  </si>
-  <si>
-    <t>077463146506</t>
-  </si>
-  <si>
-    <t>867903486431</t>
-  </si>
-  <si>
-    <t>378305122385</t>
-  </si>
-  <si>
-    <t>537795842398</t>
-  </si>
-  <si>
-    <t>132960930970</t>
-  </si>
-  <si>
-    <t>020749361912</t>
-  </si>
-  <si>
-    <t>942490712867</t>
-  </si>
-  <si>
-    <t>740776673171</t>
-  </si>
-  <si>
-    <t>730513300015</t>
-  </si>
-  <si>
-    <t>384883498557</t>
-  </si>
-  <si>
-    <t>612155843373</t>
-  </si>
-  <si>
-    <t>214497206046</t>
-  </si>
-  <si>
-    <t>053434728566</t>
-  </si>
-  <si>
-    <t>984537135142</t>
-  </si>
-  <si>
-    <t>025769888873</t>
-  </si>
-  <si>
-    <t>285070352209</t>
-  </si>
-  <si>
-    <t>652313652672</t>
-  </si>
-  <si>
-    <t>719906703096</t>
-  </si>
-  <si>
-    <t>314013158728</t>
-  </si>
-  <si>
-    <t>256693025336</t>
-  </si>
-  <si>
-    <t>240903734423</t>
-  </si>
-  <si>
-    <t>925892930778</t>
-  </si>
-  <si>
-    <t>719257115167</t>
-  </si>
-  <si>
-    <t>683028452245</t>
-  </si>
-  <si>
-    <t>138361690928</t>
-  </si>
-  <si>
-    <t>905745316115</t>
-  </si>
-  <si>
-    <t>327972054642</t>
-  </si>
-  <si>
-    <t>273929624090</t>
-  </si>
-  <si>
-    <t>729795769861</t>
-  </si>
-  <si>
-    <t>633959285169</t>
-  </si>
-  <si>
-    <t>922752116531</t>
-  </si>
-  <si>
-    <t>320171399918</t>
-  </si>
-  <si>
-    <t>232753766150</t>
-  </si>
-  <si>
-    <t>547832497721</t>
-  </si>
-  <si>
-    <t>110236322882</t>
-  </si>
-  <si>
-    <t>032492052135</t>
-  </si>
-  <si>
-    <t>386634734891</t>
-  </si>
-  <si>
-    <t>854598519974</t>
-  </si>
-  <si>
-    <t>375704152221</t>
-  </si>
-  <si>
-    <t>036716158583</t>
-  </si>
-  <si>
-    <t>630914669341</t>
-  </si>
-  <si>
-    <t>248738360553</t>
-  </si>
-  <si>
-    <t>756632943797</t>
-  </si>
-  <si>
-    <t>432554802225</t>
-  </si>
-  <si>
-    <t>802919980735</t>
-  </si>
-  <si>
-    <t>357535010016</t>
-  </si>
-  <si>
-    <t>506347764100</t>
-  </si>
-  <si>
-    <t>760270723235</t>
-  </si>
-  <si>
-    <t>400578403890</t>
-  </si>
-  <si>
-    <t>894415514757</t>
-  </si>
-  <si>
-    <t>239390119167</t>
-  </si>
-  <si>
-    <t>272291446775</t>
-  </si>
-  <si>
-    <t>085679019852</t>
-  </si>
-  <si>
-    <t>550871358261</t>
-  </si>
-  <si>
-    <t>195700772558</t>
-  </si>
-  <si>
-    <t>574594135630</t>
-  </si>
-  <si>
-    <t>956783808838</t>
-  </si>
-  <si>
-    <t>320016577230</t>
-  </si>
-  <si>
-    <t>109311152190</t>
-  </si>
-  <si>
-    <t>141580450714</t>
-  </si>
-  <si>
-    <t>722563781502</t>
-  </si>
-  <si>
-    <t>360956142816</t>
-  </si>
-  <si>
-    <t>672824759841</t>
-  </si>
-  <si>
-    <t>102625136058</t>
-  </si>
-  <si>
-    <t>305918269820</t>
-  </si>
-  <si>
-    <t>767521543730</t>
-  </si>
-  <si>
-    <t>575824038993</t>
-  </si>
-  <si>
-    <t>815444237335</t>
-  </si>
-  <si>
-    <t>530155867556</t>
-  </si>
-  <si>
-    <t>510181563078</t>
-  </si>
-  <si>
-    <t>072875389935</t>
-  </si>
-  <si>
-    <t>513722617822</t>
-  </si>
-  <si>
-    <t>615702545588</t>
-  </si>
-  <si>
-    <t>758179994035</t>
-  </si>
-  <si>
-    <t>624506754471</t>
-  </si>
-  <si>
-    <t>537511219864</t>
-  </si>
-  <si>
-    <t>249678514468</t>
-  </si>
-  <si>
-    <t>397705911838</t>
-  </si>
-  <si>
-    <t>474244280737</t>
-  </si>
-  <si>
-    <t>977351726266</t>
-  </si>
-  <si>
-    <t>850216469889</t>
-  </si>
-  <si>
-    <t>716396305790</t>
-  </si>
-  <si>
-    <t>208574739224</t>
-  </si>
-  <si>
-    <t>401362756840</t>
-  </si>
-  <si>
-    <t>542349628468</t>
-  </si>
-  <si>
-    <t>620379837265</t>
-  </si>
-  <si>
-    <t>883420134299</t>
-  </si>
-  <si>
-    <t>684591813986</t>
-  </si>
-  <si>
-    <t>356660422141</t>
-  </si>
-  <si>
-    <t>882658563798</t>
-  </si>
-  <si>
-    <t>257530903014</t>
-  </si>
-  <si>
-    <t>024128213867</t>
-  </si>
-  <si>
-    <t>711180599390</t>
-  </si>
-  <si>
-    <t>128988624104</t>
-  </si>
-  <si>
-    <t>141827126648</t>
-  </si>
-  <si>
-    <t>988882029299</t>
-  </si>
-  <si>
-    <t>692853423184</t>
-  </si>
-  <si>
-    <t>783344974540</t>
-  </si>
-  <si>
-    <t>054641861393</t>
-  </si>
-  <si>
-    <t>811180973987</t>
-  </si>
-  <si>
-    <t>391151592146</t>
-  </si>
-  <si>
-    <t>986664573457</t>
-  </si>
-  <si>
-    <t>709446044748</t>
-  </si>
-  <si>
-    <t>540798505855</t>
-  </si>
-  <si>
-    <t>324677251767</t>
-  </si>
-  <si>
-    <t>002191283830</t>
-  </si>
-  <si>
-    <t>225151213261</t>
-  </si>
-  <si>
-    <t>274705421229</t>
-  </si>
-  <si>
-    <t>868965707756</t>
-  </si>
-  <si>
-    <t>934892123798</t>
-  </si>
-  <si>
-    <t>595805746732</t>
-  </si>
-  <si>
-    <t>952144427150</t>
-  </si>
-  <si>
-    <t>808544142755</t>
-  </si>
-  <si>
-    <t>628399260440</t>
-  </si>
-  <si>
-    <t>295232977952</t>
-  </si>
-  <si>
-    <t>845776437338</t>
-  </si>
-  <si>
-    <t>940969289421</t>
-  </si>
-  <si>
-    <t>779194494314</t>
-  </si>
-  <si>
-    <t>541145327974</t>
-  </si>
-  <si>
-    <t>996894929355</t>
-  </si>
-  <si>
-    <t>853217010326</t>
-  </si>
-  <si>
-    <t>908635353880</t>
-  </si>
-  <si>
-    <t>066940311682</t>
-  </si>
-  <si>
-    <t>746008575338</t>
-  </si>
-  <si>
-    <t>456075311264</t>
-  </si>
-  <si>
-    <t>930593449832</t>
-  </si>
-  <si>
-    <t>333605810329</t>
-  </si>
-  <si>
-    <t>659461523275</t>
-  </si>
-  <si>
-    <t>924351605497</t>
-  </si>
-  <si>
-    <t>958411055879</t>
-  </si>
-  <si>
-    <t>163763675765</t>
-  </si>
-  <si>
-    <t>822016542726</t>
-  </si>
-  <si>
-    <t>457434154983</t>
-  </si>
-  <si>
-    <t>302891073034</t>
-  </si>
-  <si>
-    <t>374123748005</t>
-  </si>
-  <si>
-    <t>657043908827</t>
-  </si>
-  <si>
-    <t>846727132688</t>
-  </si>
-  <si>
-    <t>188961374013</t>
-  </si>
-  <si>
-    <t>513420238217</t>
-  </si>
-  <si>
-    <t>689518704584</t>
-  </si>
-  <si>
-    <t>348471510901</t>
-  </si>
-  <si>
-    <t>223582003252</t>
-  </si>
-  <si>
-    <t>305725837735</t>
-  </si>
-  <si>
-    <t>220032487721</t>
-  </si>
-  <si>
-    <t>641613388817</t>
-  </si>
-  <si>
-    <t>648993969048</t>
-  </si>
-  <si>
-    <t>172507542349</t>
-  </si>
-  <si>
-    <t>264034643087</t>
-  </si>
-  <si>
-    <t>790817773949</t>
-  </si>
-  <si>
-    <t>095463451344</t>
-  </si>
-  <si>
-    <t>324023243801</t>
-  </si>
-  <si>
-    <t>235458635608</t>
-  </si>
-  <si>
-    <t>194657935082</t>
-  </si>
-  <si>
-    <t>531250140624</t>
-  </si>
-  <si>
-    <t>477715697807</t>
-  </si>
-  <si>
-    <t>868835376828</t>
-  </si>
-  <si>
-    <t>599706071819</t>
-  </si>
-  <si>
-    <t>509234755337</t>
-  </si>
-  <si>
-    <t>562269994664</t>
-  </si>
-  <si>
-    <t>752693814430</t>
-  </si>
-  <si>
-    <t>986333782423</t>
-  </si>
-  <si>
-    <t>859079066160</t>
-  </si>
-  <si>
-    <t>179825947428</t>
-  </si>
-  <si>
-    <t>027509368791</t>
-  </si>
-  <si>
-    <t>036392075001</t>
-  </si>
-  <si>
-    <t>204013418703</t>
-  </si>
-  <si>
-    <t>773719242041</t>
-  </si>
-  <si>
-    <t>140440001854</t>
-  </si>
-  <si>
-    <t>908221106753</t>
-  </si>
-  <si>
-    <t>945990090327</t>
-  </si>
-  <si>
-    <t>644827858468</t>
-  </si>
-  <si>
-    <t>242528604228</t>
-  </si>
-  <si>
-    <t>744912106065</t>
-  </si>
-  <si>
-    <t>125121895261</t>
-  </si>
-  <si>
-    <t>505251701787</t>
-  </si>
-  <si>
-    <t>832455038482</t>
-  </si>
-  <si>
-    <t>160027449663</t>
-  </si>
-  <si>
-    <t>138635085608</t>
-  </si>
-  <si>
-    <t>242675048865</t>
-  </si>
-  <si>
-    <t>645386576617</t>
-  </si>
-  <si>
-    <t>843743305033</t>
-  </si>
-  <si>
-    <t>385975920199</t>
-  </si>
-  <si>
-    <t>527398021797</t>
-  </si>
-  <si>
-    <t>771319609430</t>
-  </si>
-  <si>
-    <t>649384728212</t>
-  </si>
-  <si>
-    <t>632933061409</t>
-  </si>
-  <si>
-    <t>625375767903</t>
-  </si>
-  <si>
-    <t>942567876453</t>
-  </si>
-  <si>
-    <t>358142609009</t>
-  </si>
-  <si>
-    <t>663326117417</t>
-  </si>
-  <si>
-    <t>384080297581</t>
-  </si>
-  <si>
-    <t>994179933323</t>
-  </si>
-  <si>
-    <t>441383058951</t>
-  </si>
-  <si>
-    <t>082971654028</t>
-  </si>
-  <si>
-    <t>262862240416</t>
-  </si>
-  <si>
-    <t>832368910286</t>
-  </si>
-  <si>
-    <t>483394378472</t>
-  </si>
-  <si>
-    <t>817504554163</t>
-  </si>
-  <si>
-    <t>756733454949</t>
-  </si>
-  <si>
-    <t>633038858926</t>
-  </si>
-  <si>
-    <t>419754768649</t>
-  </si>
-  <si>
-    <t>009195287162</t>
-  </si>
-  <si>
-    <t>625883978769</t>
-  </si>
-  <si>
-    <t>799948975818</t>
-  </si>
-  <si>
-    <t>524800767982</t>
-  </si>
-  <si>
-    <t>461947863583</t>
-  </si>
-  <si>
-    <t>516011323339</t>
-  </si>
-  <si>
-    <t>741673793954</t>
-  </si>
-  <si>
-    <t>556130739780</t>
-  </si>
-  <si>
-    <t>761848815367</t>
-  </si>
-  <si>
-    <t>809628457317</t>
-  </si>
-  <si>
-    <t>816387339182</t>
-  </si>
-  <si>
-    <t>535671315284</t>
-  </si>
-  <si>
-    <t>171615491496</t>
-  </si>
-  <si>
-    <t>174508760058</t>
-  </si>
-  <si>
-    <t>318745493629</t>
-  </si>
-  <si>
-    <t>009794453397</t>
-  </si>
-  <si>
-    <t>486997162844</t>
-  </si>
-  <si>
-    <t>284016316642</t>
-  </si>
-  <si>
-    <t>095821808990</t>
-  </si>
-  <si>
-    <t>360262845099</t>
-  </si>
-  <si>
-    <t>193997168849</t>
-  </si>
-  <si>
-    <t>706642203760</t>
-  </si>
-  <si>
-    <t>886308067435</t>
-  </si>
-  <si>
-    <t>985975941176</t>
-  </si>
-  <si>
-    <t>801976686738</t>
-  </si>
-  <si>
-    <t>049071606978</t>
-  </si>
-  <si>
-    <t>973754056369</t>
-  </si>
-  <si>
-    <t>025048769401</t>
-  </si>
-  <si>
-    <t>275445760753</t>
-  </si>
-  <si>
-    <t>757223994504</t>
-  </si>
-  <si>
-    <t>584592615059</t>
-  </si>
-  <si>
-    <t>355593059639</t>
-  </si>
-  <si>
-    <t>259336914134</t>
-  </si>
-  <si>
-    <t>449389281276</t>
-  </si>
-  <si>
-    <t>977506683425</t>
-  </si>
-  <si>
-    <t>188139013611</t>
-  </si>
-  <si>
-    <t>463247109695</t>
-  </si>
-  <si>
-    <t>893861086217</t>
-  </si>
-  <si>
-    <t>044830997767</t>
-  </si>
-  <si>
-    <t>399592009408</t>
-  </si>
-  <si>
-    <t>454513795647</t>
-  </si>
-  <si>
-    <t>024184221354</t>
-  </si>
-  <si>
-    <t>959902589047</t>
-  </si>
-  <si>
-    <t>646254489625</t>
-  </si>
-  <si>
-    <t>141125818137</t>
-  </si>
-  <si>
-    <t>085632670482</t>
-  </si>
-  <si>
-    <t>517719436267</t>
-  </si>
-  <si>
-    <t>712998924443</t>
-  </si>
-  <si>
-    <t>578330331225</t>
-  </si>
-  <si>
-    <t>412586665358</t>
-  </si>
-  <si>
-    <t>837458386177</t>
-  </si>
-  <si>
-    <t>079029955764</t>
-  </si>
-  <si>
-    <t>640739453531</t>
-  </si>
-  <si>
-    <t>304987207206</t>
-  </si>
-  <si>
-    <t>860053778519</t>
-  </si>
-  <si>
-    <t>903741369573</t>
-  </si>
-  <si>
-    <t>567405829278</t>
-  </si>
-  <si>
-    <t>109132290171</t>
-  </si>
-  <si>
-    <t>048140526046</t>
-  </si>
-  <si>
-    <t>323958991001</t>
-  </si>
-  <si>
-    <t>382715449205</t>
-  </si>
-  <si>
-    <t>352641430095</t>
-  </si>
-  <si>
-    <t>379485913691</t>
-  </si>
-  <si>
-    <t>109862551784</t>
-  </si>
-  <si>
-    <t>600097764068</t>
-  </si>
-  <si>
-    <t>460052240642</t>
-  </si>
-  <si>
-    <t>855438001075</t>
-  </si>
-  <si>
-    <t>679681959764</t>
-  </si>
-  <si>
-    <t>111348901628</t>
-  </si>
-  <si>
-    <t>061156972039</t>
-  </si>
-  <si>
-    <t>823461702810</t>
-  </si>
-  <si>
-    <t>412141171463</t>
-  </si>
-  <si>
-    <t>269648735367</t>
-  </si>
-  <si>
-    <t>524605769932</t>
-  </si>
-  <si>
-    <t>386685918580</t>
-  </si>
-  <si>
-    <t>825990389439</t>
-  </si>
-  <si>
-    <t>890941111110</t>
-  </si>
-  <si>
-    <t>652914329193</t>
-  </si>
-  <si>
-    <t>715809539626</t>
-  </si>
-  <si>
-    <t>318768764329</t>
-  </si>
-  <si>
-    <t>354956642031</t>
-  </si>
-  <si>
-    <t>616818251648</t>
-  </si>
-  <si>
-    <t>493520773672</t>
-  </si>
-  <si>
-    <t>869446582569</t>
-  </si>
-  <si>
-    <t>238738900156</t>
-  </si>
-  <si>
-    <t>987394513174</t>
-  </si>
-  <si>
-    <t>153961617673</t>
-  </si>
-  <si>
-    <t>802091487976</t>
-  </si>
-  <si>
-    <t>121410354132</t>
-  </si>
-  <si>
-    <t>527382061888</t>
-  </si>
-  <si>
-    <t>012716759294</t>
-  </si>
-  <si>
-    <t>822624744310</t>
-  </si>
-  <si>
-    <t>756597180464</t>
-  </si>
-  <si>
-    <t>345791028774</t>
-  </si>
-  <si>
-    <t>130074150248</t>
-  </si>
-  <si>
-    <t>106640003478</t>
-  </si>
-  <si>
-    <t>943488600404</t>
-  </si>
-  <si>
-    <t>727311574297</t>
-  </si>
-  <si>
-    <t>191129770200</t>
-  </si>
-  <si>
-    <t>952919953158</t>
-  </si>
-  <si>
-    <t>485025966158</t>
-  </si>
-  <si>
-    <t>877317883161</t>
-  </si>
-  <si>
-    <t>537629184299</t>
-  </si>
-  <si>
-    <t>837893055619</t>
-  </si>
-  <si>
-    <t>293809810273</t>
-  </si>
-  <si>
-    <t>589110267083</t>
-  </si>
-  <si>
-    <t>011415874295</t>
-  </si>
-  <si>
-    <t>240761755173</t>
-  </si>
-  <si>
-    <t>583771711328</t>
-  </si>
-  <si>
-    <t>765143149957</t>
-  </si>
-  <si>
-    <t>223775349788</t>
-  </si>
-  <si>
-    <t>254738936677</t>
-  </si>
-  <si>
-    <t>316536095203</t>
-  </si>
-  <si>
-    <t>405146542319</t>
-  </si>
-  <si>
-    <t>516701615094</t>
-  </si>
-  <si>
-    <t>650585080939</t>
-  </si>
-  <si>
-    <t>503242768252</t>
-  </si>
-  <si>
-    <t>166855623193</t>
-  </si>
-  <si>
-    <t>377849249032</t>
-  </si>
-  <si>
-    <t>112939748911</t>
-  </si>
-  <si>
-    <t>499833633659</t>
-  </si>
-  <si>
-    <t>589039399014</t>
-  </si>
-  <si>
-    <t>699741548210</t>
-  </si>
-  <si>
-    <t>785880710601</t>
-  </si>
-  <si>
-    <t>574504163854</t>
-  </si>
-  <si>
-    <t>536270394828</t>
-  </si>
-  <si>
-    <t>726020553903</t>
-  </si>
-  <si>
-    <t>020404454398</t>
-  </si>
-  <si>
-    <t>463174222506</t>
-  </si>
-  <si>
-    <t>797022189468</t>
-  </si>
-  <si>
-    <t>027209562636</t>
-  </si>
-  <si>
-    <t>249434558344</t>
-  </si>
-  <si>
-    <t>068879607798</t>
-  </si>
-  <si>
-    <t>719862268255</t>
-  </si>
-  <si>
-    <t>749487851788</t>
-  </si>
-  <si>
-    <t>894549546278</t>
-  </si>
-  <si>
-    <t>774094102303</t>
-  </si>
-  <si>
-    <t>240540306135</t>
-  </si>
-  <si>
-    <t>830982271669</t>
-  </si>
-  <si>
-    <t>277995401309</t>
-  </si>
-  <si>
-    <t>593091398023</t>
-  </si>
-  <si>
-    <t>885046462650</t>
-  </si>
-  <si>
-    <t>756423507156</t>
-  </si>
-  <si>
-    <t>419749570046</t>
-  </si>
-  <si>
-    <t>752125230651</t>
-  </si>
-  <si>
-    <t>871339062810</t>
-  </si>
-  <si>
-    <t>420849736294</t>
-  </si>
-  <si>
-    <t>180610548971</t>
-  </si>
-  <si>
-    <t>605742804696</t>
-  </si>
-  <si>
-    <t>073092003817</t>
-  </si>
-  <si>
-    <t>403682676172</t>
-  </si>
-  <si>
-    <t>130721137943</t>
-  </si>
-  <si>
-    <t>060254479572</t>
-  </si>
-  <si>
-    <t>578575054888</t>
-  </si>
-  <si>
-    <t>621346615784</t>
-  </si>
-  <si>
-    <t>196251779619</t>
-  </si>
-  <si>
-    <t>731092230570</t>
-  </si>
-  <si>
-    <t>851772330587</t>
-  </si>
-  <si>
-    <t>955653009791</t>
-  </si>
-  <si>
-    <t>570228918963</t>
-  </si>
-  <si>
-    <t>202725679544</t>
-  </si>
-  <si>
-    <t>328874137784</t>
-  </si>
-  <si>
-    <t>958432986259</t>
-  </si>
-  <si>
-    <t>244833088361</t>
-  </si>
-  <si>
-    <t>327674755287</t>
-  </si>
-  <si>
-    <t>897525922674</t>
-  </si>
-  <si>
-    <t>897885255804</t>
-  </si>
-  <si>
-    <t>300030457187</t>
-  </si>
-  <si>
-    <t>160105019571</t>
-  </si>
-  <si>
-    <t>044755931173</t>
-  </si>
-  <si>
-    <t>929434187994</t>
-  </si>
-  <si>
-    <t>253228064822</t>
-  </si>
-  <si>
-    <t>090427468177</t>
-  </si>
-  <si>
-    <t>658203079731</t>
-  </si>
-  <si>
-    <t>434130952008</t>
-  </si>
-  <si>
-    <t>439143705842</t>
-  </si>
-  <si>
-    <t>191382227678</t>
-  </si>
-  <si>
-    <t>919352006002</t>
-  </si>
-  <si>
-    <t>735894973346</t>
-  </si>
-  <si>
-    <t>344828645872</t>
+    <t>039115569810</t>
+  </si>
+  <si>
+    <t>661</t>
+  </si>
+  <si>
+    <t>620160127607</t>
+  </si>
+  <si>
+    <t>643076748863</t>
+  </si>
+  <si>
+    <t>014299417087</t>
+  </si>
+  <si>
+    <t>230734334348</t>
+  </si>
+  <si>
+    <t>425065949295</t>
+  </si>
+  <si>
+    <t>442639865214</t>
+  </si>
+  <si>
+    <t>821210172356</t>
+  </si>
+  <si>
+    <t>909729305604</t>
+  </si>
+  <si>
+    <t>823157130944</t>
+  </si>
+  <si>
+    <t>279908509703</t>
+  </si>
+  <si>
+    <t>175204920928</t>
+  </si>
+  <si>
+    <t>073062832282</t>
+  </si>
+  <si>
+    <t>582665528476</t>
+  </si>
+  <si>
+    <t>319534907127</t>
+  </si>
+  <si>
+    <t>245769043332</t>
+  </si>
+  <si>
+    <t>755227506860</t>
+  </si>
+  <si>
+    <t>514484040493</t>
+  </si>
+  <si>
+    <t>748452311075</t>
+  </si>
+  <si>
+    <t>147292177736</t>
+  </si>
+  <si>
+    <t>874322509714</t>
+  </si>
+  <si>
+    <t>588785036738</t>
+  </si>
+  <si>
+    <t>996592913384</t>
+  </si>
+  <si>
+    <t>263120787528</t>
+  </si>
+  <si>
+    <t>250770016397</t>
+  </si>
+  <si>
+    <t>052916581050</t>
+  </si>
+  <si>
+    <t>144515419100</t>
+  </si>
+  <si>
+    <t>250166808376</t>
+  </si>
+  <si>
+    <t>218614342471</t>
+  </si>
+  <si>
+    <t>034924712580</t>
+  </si>
+  <si>
+    <t>414189853806</t>
+  </si>
+  <si>
+    <t>970341896396</t>
+  </si>
+  <si>
+    <t>596253668270</t>
+  </si>
+  <si>
+    <t>604536843493</t>
+  </si>
+  <si>
+    <t>119852639443</t>
+  </si>
+  <si>
+    <t>650246693229</t>
+  </si>
+  <si>
+    <t>981335359595</t>
+  </si>
+  <si>
+    <t>096662635511</t>
+  </si>
+  <si>
+    <t>212253540832</t>
+  </si>
+  <si>
+    <t>625690659095</t>
+  </si>
+  <si>
+    <t>970827899134</t>
+  </si>
+  <si>
+    <t>943832601278</t>
+  </si>
+  <si>
+    <t>577161902558</t>
+  </si>
+  <si>
+    <t>395590989439</t>
+  </si>
+  <si>
+    <t>572164041233</t>
+  </si>
+  <si>
+    <t>263688052570</t>
+  </si>
+  <si>
+    <t>234920315763</t>
+  </si>
+  <si>
+    <t>053716318967</t>
+  </si>
+  <si>
+    <t>663888910277</t>
+  </si>
+  <si>
+    <t>584180605410</t>
+  </si>
+  <si>
+    <t>131065701287</t>
+  </si>
+  <si>
+    <t>861130916884</t>
+  </si>
+  <si>
+    <t>796998723010</t>
+  </si>
+  <si>
+    <t>646226860514</t>
+  </si>
+  <si>
+    <t>665180511214</t>
+  </si>
+  <si>
+    <t>098143877441</t>
+  </si>
+  <si>
+    <t>426019596079</t>
+  </si>
+  <si>
+    <t>643720713001</t>
+  </si>
+  <si>
+    <t>819086228280</t>
+  </si>
+  <si>
+    <t>250109516845</t>
+  </si>
+  <si>
+    <t>805499248836</t>
+  </si>
+  <si>
+    <t>279156224329</t>
+  </si>
+  <si>
+    <t>854961585532</t>
+  </si>
+  <si>
+    <t>894149003844</t>
+  </si>
+  <si>
+    <t>487455304651</t>
+  </si>
+  <si>
+    <t>563293681247</t>
+  </si>
+  <si>
+    <t>396822694369</t>
+  </si>
+  <si>
+    <t>773530278961</t>
+  </si>
+  <si>
+    <t>041381565943</t>
+  </si>
+  <si>
+    <t>531249141408</t>
+  </si>
+  <si>
+    <t>552219280076</t>
+  </si>
+  <si>
+    <t>702943006347</t>
+  </si>
+  <si>
+    <t>241572944654</t>
+  </si>
+  <si>
+    <t>653812224222</t>
+  </si>
+  <si>
+    <t>277513356036</t>
+  </si>
+  <si>
+    <t>091487785741</t>
+  </si>
+  <si>
+    <t>346701415628</t>
+  </si>
+  <si>
+    <t>803175723022</t>
+  </si>
+  <si>
+    <t>908253091114</t>
+  </si>
+  <si>
+    <t>755887011597</t>
+  </si>
+  <si>
+    <t>025726843815</t>
+  </si>
+  <si>
+    <t>390467262891</t>
+  </si>
+  <si>
+    <t>698513710516</t>
+  </si>
+  <si>
+    <t>210225792096</t>
+  </si>
+  <si>
+    <t>027089092114</t>
+  </si>
+  <si>
+    <t>236081354779</t>
+  </si>
+  <si>
+    <t>031095037040</t>
+  </si>
+  <si>
+    <t>475238809382</t>
+  </si>
+  <si>
+    <t>375695730319</t>
+  </si>
+  <si>
+    <t>034116501112</t>
+  </si>
+  <si>
+    <t>539701831198</t>
+  </si>
+  <si>
+    <t>977418648860</t>
+  </si>
+  <si>
+    <t>522096545218</t>
+  </si>
+  <si>
+    <t>145122332355</t>
+  </si>
+  <si>
+    <t>027004432467</t>
+  </si>
+  <si>
+    <t>051082712360</t>
+  </si>
+  <si>
+    <t>107983374271</t>
+  </si>
+  <si>
+    <t>950555922941</t>
+  </si>
+  <si>
+    <t>402353158118</t>
+  </si>
+  <si>
+    <t>624523215289</t>
+  </si>
+  <si>
+    <t>039826392824</t>
+  </si>
+  <si>
+    <t>663351577324</t>
+  </si>
+  <si>
+    <t>012644982486</t>
+  </si>
+  <si>
+    <t>295925841014</t>
+  </si>
+  <si>
+    <t>725225980601</t>
+  </si>
+  <si>
+    <t>762184971138</t>
+  </si>
+  <si>
+    <t>918879926148</t>
+  </si>
+  <si>
+    <t>323762289750</t>
+  </si>
+  <si>
+    <t>821774640185</t>
+  </si>
+  <si>
+    <t>208575422759</t>
+  </si>
+  <si>
+    <t>092249060904</t>
+  </si>
+  <si>
+    <t>876040921209</t>
+  </si>
+  <si>
+    <t>649631514161</t>
+  </si>
+  <si>
+    <t>661888781378</t>
+  </si>
+  <si>
+    <t>440433199188</t>
+  </si>
+  <si>
+    <t>278812186425</t>
+  </si>
+  <si>
+    <t>325295136715</t>
+  </si>
+  <si>
+    <t>944402409944</t>
+  </si>
+  <si>
+    <t>127143604068</t>
+  </si>
+  <si>
+    <t>424994102575</t>
+  </si>
+  <si>
+    <t>582157245460</t>
+  </si>
+  <si>
+    <t>195758177378</t>
+  </si>
+  <si>
+    <t>850822333473</t>
+  </si>
+  <si>
+    <t>514825287460</t>
+  </si>
+  <si>
+    <t>524667680870</t>
+  </si>
+  <si>
+    <t>611151000079</t>
+  </si>
+  <si>
+    <t>798363936543</t>
+  </si>
+  <si>
+    <t>458310604356</t>
+  </si>
+  <si>
+    <t>425981845560</t>
+  </si>
+  <si>
+    <t>014727677685</t>
+  </si>
+  <si>
+    <t>929925092184</t>
+  </si>
+  <si>
+    <t>667449437627</t>
+  </si>
+  <si>
+    <t>463797731523</t>
+  </si>
+  <si>
+    <t>886438632489</t>
+  </si>
+  <si>
+    <t>554714269509</t>
+  </si>
+  <si>
+    <t>583361023840</t>
+  </si>
+  <si>
+    <t>881852990252</t>
+  </si>
+  <si>
+    <t>054668491179</t>
+  </si>
+  <si>
+    <t>086955035645</t>
+  </si>
+  <si>
+    <t>245159474413</t>
+  </si>
+  <si>
+    <t>811969398426</t>
+  </si>
+  <si>
+    <t>525272423914</t>
+  </si>
+  <si>
+    <t>458920638555</t>
+  </si>
+  <si>
+    <t>895046587528</t>
+  </si>
+  <si>
+    <t>072374533316</t>
+  </si>
+  <si>
+    <t>304716643275</t>
+  </si>
+  <si>
+    <t>469207750058</t>
+  </si>
+  <si>
+    <t>298013853796</t>
+  </si>
+  <si>
+    <t>282718551402</t>
+  </si>
+  <si>
+    <t>665227625969</t>
+  </si>
+  <si>
+    <t>628019185534</t>
+  </si>
+  <si>
+    <t>629300446424</t>
+  </si>
+  <si>
+    <t>767090977916</t>
+  </si>
+  <si>
+    <t>551886008840</t>
+  </si>
+  <si>
+    <t>844502949893</t>
+  </si>
+  <si>
+    <t>432361234757</t>
+  </si>
+  <si>
+    <t>789562191371</t>
+  </si>
+  <si>
+    <t>945204637714</t>
+  </si>
+  <si>
+    <t>563497930775</t>
+  </si>
+  <si>
+    <t>388175711453</t>
+  </si>
+  <si>
+    <t>522355840708</t>
+  </si>
+  <si>
+    <t>991142701489</t>
+  </si>
+  <si>
+    <t>371877098958</t>
+  </si>
+  <si>
+    <t>484123184595</t>
+  </si>
+  <si>
+    <t>690016901422</t>
+  </si>
+  <si>
+    <t>985594238884</t>
+  </si>
+  <si>
+    <t>145764126822</t>
+  </si>
+  <si>
+    <t>397136695067</t>
+  </si>
+  <si>
+    <t>615121245410</t>
+  </si>
+  <si>
+    <t>183132026019</t>
+  </si>
+  <si>
+    <t>812669240430</t>
+  </si>
+  <si>
+    <t>440894350989</t>
+  </si>
+  <si>
+    <t>494283461844</t>
+  </si>
+  <si>
+    <t>040437804523</t>
+  </si>
+  <si>
+    <t>352438318934</t>
+  </si>
+  <si>
+    <t>037872833852</t>
+  </si>
+  <si>
+    <t>157676201780</t>
+  </si>
+  <si>
+    <t>102981748849</t>
+  </si>
+  <si>
+    <t>836251215863</t>
+  </si>
+  <si>
+    <t>494709456452</t>
+  </si>
+  <si>
+    <t>755004704128</t>
+  </si>
+  <si>
+    <t>743027148075</t>
+  </si>
+  <si>
+    <t>488527881679</t>
+  </si>
+  <si>
+    <t>307009100998</t>
+  </si>
+  <si>
+    <t>979270662682</t>
+  </si>
+  <si>
+    <t>203256338150</t>
+  </si>
+  <si>
+    <t>855727555145</t>
+  </si>
+  <si>
+    <t>927141147484</t>
+  </si>
+  <si>
+    <t>818258507200</t>
+  </si>
+  <si>
+    <t>475451994031</t>
+  </si>
+  <si>
+    <t>502996149103</t>
+  </si>
+  <si>
+    <t>654591230654</t>
+  </si>
+  <si>
+    <t>530826966563</t>
+  </si>
+  <si>
+    <t>591831583134</t>
+  </si>
+  <si>
+    <t>996873237659</t>
+  </si>
+  <si>
+    <t>495698530095</t>
+  </si>
+  <si>
+    <t>263864324891</t>
+  </si>
+  <si>
+    <t>408891031937</t>
+  </si>
+  <si>
+    <t>982443410167</t>
+  </si>
+  <si>
+    <t>198379868723</t>
+  </si>
+  <si>
+    <t>652338819288</t>
+  </si>
+  <si>
+    <t>195005441641</t>
+  </si>
+  <si>
+    <t>266948833646</t>
+  </si>
+  <si>
+    <t>113953946546</t>
+  </si>
+  <si>
+    <t>357244102804</t>
+  </si>
+  <si>
+    <t>573490693400</t>
+  </si>
+  <si>
+    <t>355088889023</t>
+  </si>
+  <si>
+    <t>629356430780</t>
+  </si>
+  <si>
+    <t>279897419121</t>
+  </si>
+  <si>
+    <t>588671257487</t>
+  </si>
+  <si>
+    <t>910535498565</t>
+  </si>
+  <si>
+    <t>321424250510</t>
+  </si>
+  <si>
+    <t>098300597609</t>
+  </si>
+  <si>
+    <t>745752990079</t>
+  </si>
+  <si>
+    <t>095993445363</t>
+  </si>
+  <si>
+    <t>203126929517</t>
+  </si>
+  <si>
+    <t>217673852353</t>
+  </si>
+  <si>
+    <t>618517885285</t>
+  </si>
+  <si>
+    <t>572006200291</t>
+  </si>
+  <si>
+    <t>345055798972</t>
+  </si>
+  <si>
+    <t>060990634280</t>
+  </si>
+  <si>
+    <t>894995597010</t>
+  </si>
+  <si>
+    <t>917203711157</t>
+  </si>
+  <si>
+    <t>647834396516</t>
+  </si>
+  <si>
+    <t>941366001225</t>
+  </si>
+  <si>
+    <t>416960873577</t>
+  </si>
+  <si>
+    <t>524161613019</t>
+  </si>
+  <si>
+    <t>245270763123</t>
+  </si>
+  <si>
+    <t>139890925779</t>
+  </si>
+  <si>
+    <t>419268501611</t>
+  </si>
+  <si>
+    <t>479233229620</t>
+  </si>
+  <si>
+    <t>435959721079</t>
+  </si>
+  <si>
+    <t>974012936477</t>
+  </si>
+  <si>
+    <t>267079824606</t>
+  </si>
+  <si>
+    <t>160799841353</t>
+  </si>
+  <si>
+    <t>296131116952</t>
+  </si>
+  <si>
+    <t>468167727597</t>
+  </si>
+  <si>
+    <t>106384633707</t>
+  </si>
+  <si>
+    <t>244588146728</t>
+  </si>
+  <si>
+    <t>907727655261</t>
+  </si>
+  <si>
+    <t>909646671656</t>
+  </si>
+  <si>
+    <t>802248116249</t>
+  </si>
+  <si>
+    <t>235170899610</t>
+  </si>
+  <si>
+    <t>502185672388</t>
+  </si>
+  <si>
+    <t>633638416440</t>
+  </si>
+  <si>
+    <t>195213578898</t>
+  </si>
+  <si>
+    <t>962853315934</t>
+  </si>
+  <si>
+    <t>541060919084</t>
+  </si>
+  <si>
+    <t>204920699582</t>
+  </si>
+  <si>
+    <t>474687255192</t>
+  </si>
+  <si>
+    <t>670678232235</t>
+  </si>
+  <si>
+    <t>416716217335</t>
+  </si>
+  <si>
+    <t>856013233244</t>
+  </si>
+  <si>
+    <t>305800019680</t>
+  </si>
+  <si>
+    <t>300091001119</t>
+  </si>
+  <si>
+    <t>042123549022</t>
+  </si>
+  <si>
+    <t>911826287028</t>
+  </si>
+  <si>
+    <t>385230772616</t>
+  </si>
+  <si>
+    <t>693656394540</t>
+  </si>
+  <si>
+    <t>519321623802</t>
+  </si>
+  <si>
+    <t>243258878725</t>
+  </si>
+  <si>
+    <t>381113122791</t>
+  </si>
+  <si>
+    <t>338329699538</t>
+  </si>
+  <si>
+    <t>190291196812</t>
+  </si>
+  <si>
+    <t>101472731178</t>
+  </si>
+  <si>
+    <t>417328061338</t>
+  </si>
+  <si>
+    <t>698369238136</t>
+  </si>
+  <si>
+    <t>664555589289</t>
+  </si>
+  <si>
+    <t>697751250871</t>
+  </si>
+  <si>
+    <t>410415192665</t>
+  </si>
+  <si>
+    <t>453436200871</t>
+  </si>
+  <si>
+    <t>921096784507</t>
+  </si>
+  <si>
+    <t>500905115988</t>
+  </si>
+  <si>
+    <t>234173637602</t>
+  </si>
+  <si>
+    <t>800465383927</t>
+  </si>
+  <si>
+    <t>546638590163</t>
+  </si>
+  <si>
+    <t>644321740770</t>
+  </si>
+  <si>
+    <t>367007212469</t>
+  </si>
+  <si>
+    <t>608730421315</t>
+  </si>
+  <si>
+    <t>443297752738</t>
+  </si>
+  <si>
+    <t>418761308533</t>
+  </si>
+  <si>
+    <t>431488989388</t>
+  </si>
+  <si>
+    <t>823909417371</t>
+  </si>
+  <si>
+    <t>261776378820</t>
+  </si>
+  <si>
+    <t>297740611987</t>
+  </si>
+  <si>
+    <t>982018141902</t>
+  </si>
+  <si>
+    <t>354445794599</t>
+  </si>
+  <si>
+    <t>074827590199</t>
+  </si>
+  <si>
+    <t>300092406130</t>
+  </si>
+  <si>
+    <t>898248249628</t>
+  </si>
+  <si>
+    <t>762145687389</t>
+  </si>
+  <si>
+    <t>350758949055</t>
+  </si>
+  <si>
+    <t>745196631561</t>
+  </si>
+  <si>
+    <t>495141433060</t>
+  </si>
+  <si>
+    <t>360820207997</t>
+  </si>
+  <si>
+    <t>045101669962</t>
+  </si>
+  <si>
+    <t>671970439097</t>
+  </si>
+  <si>
+    <t>057008693518</t>
+  </si>
+  <si>
+    <t>506806447538</t>
+  </si>
+  <si>
+    <t>614074978437</t>
+  </si>
+  <si>
+    <t>733648024301</t>
+  </si>
+  <si>
+    <t>726722132721</t>
+  </si>
+  <si>
+    <t>868286125027</t>
+  </si>
+  <si>
+    <t>833876204165</t>
+  </si>
+  <si>
+    <t>457014266126</t>
+  </si>
+  <si>
+    <t>692468292245</t>
+  </si>
+  <si>
+    <t>960475257430</t>
+  </si>
+  <si>
+    <t>103618244252</t>
+  </si>
+  <si>
+    <t>943435165855</t>
+  </si>
+  <si>
+    <t>823266320161</t>
+  </si>
+  <si>
+    <t>493089174899</t>
+  </si>
+  <si>
+    <t>672986731530</t>
+  </si>
+  <si>
+    <t>457464450746</t>
+  </si>
+  <si>
+    <t>431480755437</t>
+  </si>
+  <si>
+    <t>787556080335</t>
+  </si>
+  <si>
+    <t>122514405571</t>
+  </si>
+  <si>
+    <t>278183288003</t>
+  </si>
+  <si>
+    <t>533121739038</t>
+  </si>
+  <si>
+    <t>658520711375</t>
+  </si>
+  <si>
+    <t>583308830116</t>
+  </si>
+  <si>
+    <t>166610522756</t>
+  </si>
+  <si>
+    <t>374102152501</t>
+  </si>
+  <si>
+    <t>986232061132</t>
+  </si>
+  <si>
+    <t>681972712071</t>
+  </si>
+  <si>
+    <t>017253319382</t>
+  </si>
+  <si>
+    <t>223137278414</t>
+  </si>
+  <si>
+    <t>323694855482</t>
+  </si>
+  <si>
+    <t>061940067840</t>
+  </si>
+  <si>
+    <t>493038653137</t>
+  </si>
+  <si>
+    <t>279897701505</t>
+  </si>
+  <si>
+    <t>726630986630</t>
+  </si>
+  <si>
+    <t>195716506759</t>
+  </si>
+  <si>
+    <t>118771256698</t>
+  </si>
+  <si>
+    <t>470719467914</t>
+  </si>
+  <si>
+    <t>684439128445</t>
+  </si>
+  <si>
+    <t>351238049645</t>
+  </si>
+  <si>
+    <t>132557527443</t>
+  </si>
+  <si>
+    <t>405618138416</t>
+  </si>
+  <si>
+    <t>397514993932</t>
+  </si>
+  <si>
+    <t>096787095025</t>
+  </si>
+  <si>
+    <t>077711034522</t>
+  </si>
+  <si>
+    <t>908132246672</t>
+  </si>
+  <si>
+    <t>730263475228</t>
+  </si>
+  <si>
+    <t>794751734694</t>
+  </si>
+  <si>
+    <t>766732199597</t>
+  </si>
+  <si>
+    <t>980769853683</t>
+  </si>
+  <si>
+    <t>187605033478</t>
+  </si>
+  <si>
+    <t>471360173383</t>
+  </si>
+  <si>
+    <t>067690119617</t>
+  </si>
+  <si>
+    <t>850723880972</t>
+  </si>
+  <si>
+    <t>136162941149</t>
+  </si>
+  <si>
+    <t>766842213808</t>
+  </si>
+  <si>
+    <t>023050908183</t>
+  </si>
+  <si>
+    <t>644630987399</t>
+  </si>
+  <si>
+    <t>594095280065</t>
+  </si>
+  <si>
+    <t>286366040764</t>
+  </si>
+  <si>
+    <t>291355067361</t>
+  </si>
+  <si>
+    <t>506448021449</t>
+  </si>
+  <si>
+    <t>377466780553</t>
+  </si>
+  <si>
+    <t>899293293072</t>
+  </si>
+  <si>
+    <t>454611223808</t>
+  </si>
+  <si>
+    <t>013669511502</t>
+  </si>
+  <si>
+    <t>314002471878</t>
+  </si>
+  <si>
+    <t>715839835585</t>
+  </si>
+  <si>
+    <t>802442261460</t>
+  </si>
+  <si>
+    <t>939025519243</t>
+  </si>
+  <si>
+    <t>588065142449</t>
+  </si>
+  <si>
+    <t>473938735257</t>
+  </si>
+  <si>
+    <t>407389263574</t>
+  </si>
+  <si>
+    <t>210415150001</t>
+  </si>
+  <si>
+    <t>552092857990</t>
+  </si>
+  <si>
+    <t>778082929259</t>
+  </si>
+  <si>
+    <t>096799894016</t>
+  </si>
+  <si>
+    <t>469464157800</t>
+  </si>
+  <si>
+    <t>990767516645</t>
+  </si>
+  <si>
+    <t>945013845094</t>
+  </si>
+  <si>
+    <t>852993434386</t>
+  </si>
+  <si>
+    <t>055488820553</t>
+  </si>
+  <si>
+    <t>478508661653</t>
+  </si>
+  <si>
+    <t>060937638596</t>
+  </si>
+  <si>
+    <t>566440242507</t>
+  </si>
+  <si>
+    <t>143381070724</t>
+  </si>
+  <si>
+    <t>870972267838</t>
+  </si>
+  <si>
+    <t>631562083298</t>
+  </si>
+  <si>
+    <t>899255297331</t>
+  </si>
+  <si>
+    <t>263171750456</t>
+  </si>
+  <si>
+    <t>338782285708</t>
+  </si>
+  <si>
+    <t>721029522534</t>
+  </si>
+  <si>
+    <t>370165267392</t>
+  </si>
+  <si>
+    <t>033846833269</t>
+  </si>
+  <si>
+    <t>362768922677</t>
+  </si>
+  <si>
+    <t>792407033575</t>
+  </si>
+  <si>
+    <t>214254128288</t>
+  </si>
+  <si>
+    <t>411656944495</t>
+  </si>
+  <si>
+    <t>720392027361</t>
+  </si>
+  <si>
+    <t>146118882142</t>
+  </si>
+  <si>
+    <t>127540916329</t>
+  </si>
+  <si>
+    <t>814692123568</t>
+  </si>
+  <si>
+    <t>327216875925</t>
+  </si>
+  <si>
+    <t>244134337443</t>
+  </si>
+  <si>
+    <t>090736666151</t>
+  </si>
+  <si>
+    <t>103198540603</t>
+  </si>
+  <si>
+    <t>754429328657</t>
+  </si>
+  <si>
+    <t>814046914013</t>
+  </si>
+  <si>
+    <t>223824978034</t>
+  </si>
+  <si>
+    <t>608294797014</t>
+  </si>
+  <si>
+    <t>312667076078</t>
+  </si>
+  <si>
+    <t>934505734561</t>
+  </si>
+  <si>
+    <t>017540689149</t>
+  </si>
+  <si>
+    <t>949064105187</t>
+  </si>
+  <si>
+    <t>248282501282</t>
+  </si>
+  <si>
+    <t>871910853894</t>
+  </si>
+  <si>
+    <t>467417835032</t>
+  </si>
+  <si>
+    <t>716827613312</t>
+  </si>
+  <si>
+    <t>117419703741</t>
+  </si>
+  <si>
+    <t>530308721743</t>
+  </si>
+  <si>
+    <t>745566326860</t>
+  </si>
+  <si>
+    <t>790645216279</t>
+  </si>
+  <si>
+    <t>371658785422</t>
+  </si>
+  <si>
+    <t>828646824605</t>
+  </si>
+  <si>
+    <t>140785481470</t>
+  </si>
+  <si>
+    <t>640542708088</t>
+  </si>
+  <si>
+    <t>052916906165</t>
+  </si>
+  <si>
+    <t>062074295529</t>
+  </si>
+  <si>
+    <t>026561610911</t>
+  </si>
+  <si>
+    <t>614337112839</t>
+  </si>
+  <si>
+    <t>597790312022</t>
+  </si>
+  <si>
+    <t>757816051461</t>
+  </si>
+  <si>
+    <t>311009201771</t>
+  </si>
+  <si>
+    <t>560838889933</t>
+  </si>
+  <si>
+    <t>182623155689</t>
+  </si>
+  <si>
+    <t>856325997994</t>
+  </si>
+  <si>
+    <t>206717076732</t>
+  </si>
+  <si>
+    <t>556019829784</t>
+  </si>
+  <si>
+    <t>320983170200</t>
+  </si>
+  <si>
+    <t>962550102984</t>
+  </si>
+  <si>
+    <t>760860528283</t>
+  </si>
+  <si>
+    <t>030273806994</t>
+  </si>
+  <si>
+    <t>706027556187</t>
+  </si>
+  <si>
+    <t>739833517115</t>
+  </si>
+  <si>
+    <t>862819688916</t>
+  </si>
+  <si>
+    <t>213962636683</t>
+  </si>
+  <si>
+    <t>920449917316</t>
+  </si>
+  <si>
+    <t>368569663967</t>
+  </si>
+  <si>
+    <t>887113382819</t>
+  </si>
+  <si>
+    <t>616173705430</t>
+  </si>
+  <si>
+    <t>187188002916</t>
+  </si>
+  <si>
+    <t>757646636973</t>
+  </si>
+  <si>
+    <t>021841519558</t>
+  </si>
+  <si>
+    <t>347965150072</t>
+  </si>
+  <si>
+    <t>839484710019</t>
+  </si>
+  <si>
+    <t>734290765948</t>
+  </si>
+  <si>
+    <t>448902127191</t>
+  </si>
+  <si>
+    <t>157724903484</t>
+  </si>
+  <si>
+    <t>796505017981</t>
+  </si>
+  <si>
+    <t>266227284370</t>
+  </si>
+  <si>
+    <t>059642063878</t>
+  </si>
+  <si>
+    <t>244453568390</t>
+  </si>
+  <si>
+    <t>767959592972</t>
+  </si>
+  <si>
+    <t>351372261035</t>
+  </si>
+  <si>
+    <t>809495131697</t>
+  </si>
+  <si>
+    <t>235402872613</t>
+  </si>
+  <si>
+    <t>107290020647</t>
+  </si>
+  <si>
+    <t>378709599898</t>
+  </si>
+  <si>
+    <t>151605557371</t>
+  </si>
+  <si>
+    <t>470712054778</t>
+  </si>
+  <si>
+    <t>888172063678</t>
+  </si>
+  <si>
+    <t>302747242343</t>
+  </si>
+  <si>
+    <t>198630010231</t>
+  </si>
+  <si>
+    <t>103226002370</t>
+  </si>
+  <si>
+    <t>504958172586</t>
+  </si>
+  <si>
+    <t>008881919995</t>
+  </si>
+  <si>
+    <t>208367645377</t>
+  </si>
+  <si>
+    <t>628425976691</t>
+  </si>
+  <si>
+    <t>203432133655</t>
+  </si>
+  <si>
+    <t>446417709373</t>
+  </si>
+  <si>
+    <t>628457429554</t>
+  </si>
+  <si>
+    <t>619525546501</t>
+  </si>
+  <si>
+    <t>393619605560</t>
+  </si>
+  <si>
+    <t>548169883122</t>
+  </si>
+  <si>
+    <t>154910855236</t>
+  </si>
+  <si>
+    <t>305533047354</t>
+  </si>
+  <si>
+    <t>859480229937</t>
+  </si>
+  <si>
+    <t>546572380819</t>
+  </si>
+  <si>
+    <t>035038138815</t>
+  </si>
+  <si>
+    <t>232846795001</t>
+  </si>
+  <si>
+    <t>853195264149</t>
+  </si>
+  <si>
+    <t>856154334972</t>
+  </si>
+  <si>
+    <t>321194903244</t>
+  </si>
+  <si>
+    <t>952424639366</t>
+  </si>
+  <si>
+    <t>155347333156</t>
+  </si>
+  <si>
+    <t>342528626682</t>
+  </si>
+  <si>
+    <t>309990480873</t>
+  </si>
+  <si>
+    <t>696983346751</t>
+  </si>
+  <si>
+    <t>119728041598</t>
+  </si>
+  <si>
+    <t>999326578878</t>
+  </si>
+  <si>
+    <t>926183398206</t>
+  </si>
+  <si>
+    <t>620790364862</t>
+  </si>
+  <si>
+    <t>795318442708</t>
+  </si>
+  <si>
+    <t>298197775987</t>
   </si>
 </sst>
 </file>
